--- a/ADEK-BN01-IO POINT SCHEDULE_as_per_site.xlsx
+++ b/ADEK-BN01-IO POINT SCHEDULE_as_per_site.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\K&amp;P Projects - 25-26 Fahad\RCC-ADEK School\IO\ASBUILT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\personal\ControlSystems\automatex-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2846" uniqueCount="478">
   <si>
     <t>Quantity</t>
   </si>
@@ -1612,6 +1612,12 @@
   <si>
     <t xml:space="preserve">
  </t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>SMDB Not avaialble at site</t>
   </si>
 </sst>
 </file>
@@ -1873,7 +1879,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1923,6 +1929,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1983,7 +1995,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -2243,24 +2255,6 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2276,13 +2270,70 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -8737,8 +8788,9 @@
     <col min="5" max="5" width="9.44140625" style="70" customWidth="1"/>
     <col min="6" max="6" width="9.44140625" style="71" customWidth="1"/>
     <col min="7" max="7" width="11.33203125" style="72" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" style="72" customWidth="1"/>
-    <col min="9" max="10" width="18.33203125" style="72" customWidth="1"/>
+    <col min="8" max="8" width="18" style="72" customWidth="1"/>
+    <col min="9" max="9" width="19.44140625" style="72" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" style="72" customWidth="1"/>
     <col min="11" max="11" width="15.44140625" style="72" customWidth="1"/>
     <col min="12" max="12" width="72.33203125" style="71" customWidth="1"/>
     <col min="13" max="16384" width="9.109375" style="15"/>
@@ -8933,13 +8985,13 @@
       <c r="B11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="90" t="s">
+      <c r="C11" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="90"/>
-      <c r="E11" s="90"/>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
       <c r="H11" s="77"/>
       <c r="I11" s="77"/>
       <c r="J11" s="77"/>
@@ -8957,7 +9009,7 @@
       <c r="B12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="98" t="s">
+      <c r="C12" s="92" t="s">
         <v>469</v>
       </c>
       <c r="D12" s="41" t="s">
@@ -8969,19 +9021,19 @@
       <c r="F12" s="42" t="s">
         <v>472</v>
       </c>
-      <c r="G12" s="99" t="s">
+      <c r="G12" s="93" t="s">
         <v>473</v>
       </c>
-      <c r="H12" s="96" t="s">
+      <c r="H12" s="90" t="s">
         <v>464</v>
       </c>
-      <c r="I12" s="96" t="s">
+      <c r="I12" s="90" t="s">
         <v>465</v>
       </c>
-      <c r="J12" s="96" t="s">
+      <c r="J12" s="90" t="s">
         <v>466</v>
       </c>
-      <c r="K12" s="96" t="s">
+      <c r="K12" s="90" t="s">
         <v>468</v>
       </c>
       <c r="L12" s="88" t="s">
@@ -9033,13 +9085,13 @@
         <v>6</v>
       </c>
       <c r="F15" s="10"/>
-      <c r="H15" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I15" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J15" s="97" t="s">
+      <c r="H15" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I15" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J15" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K15" s="11"/>
@@ -9057,13 +9109,13 @@
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="21"/>
-      <c r="H16" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I16" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J16" s="97" t="s">
+      <c r="H16" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I16" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J16" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K16" s="11"/>
@@ -9080,13 +9132,13 @@
         <v>3</v>
       </c>
       <c r="F17" s="10"/>
-      <c r="H17" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I17" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J17" s="97" t="s">
+      <c r="H17" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I17" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J17" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K17" s="11"/>
@@ -9105,13 +9157,13 @@
       <c r="E18" s="21"/>
       <c r="F18" s="10"/>
       <c r="G18" s="21"/>
-      <c r="H18" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I18" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J18" s="97" t="s">
+      <c r="H18" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I18" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J18" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K18" s="11"/>
@@ -9130,13 +9182,13 @@
       <c r="E19" s="21"/>
       <c r="F19" s="22"/>
       <c r="G19" s="21"/>
-      <c r="H19" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I19" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J19" s="97" t="s">
+      <c r="H19" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I19" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J19" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K19" s="11"/>
@@ -9155,13 +9207,13 @@
       <c r="E20" s="21"/>
       <c r="F20" s="22"/>
       <c r="G20" s="21"/>
-      <c r="H20" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I20" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J20" s="97" t="s">
+      <c r="H20" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I20" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J20" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K20" s="11"/>
@@ -9180,13 +9232,13 @@
       <c r="E21" s="21"/>
       <c r="F21" s="22"/>
       <c r="G21" s="21"/>
-      <c r="H21" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I21" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J21" s="97" t="s">
+      <c r="H21" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I21" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J21" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K21" s="11"/>
@@ -9208,13 +9260,13 @@
         <v>3</v>
       </c>
       <c r="G22" s="21"/>
-      <c r="H22" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I22" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J22" s="97" t="s">
+      <c r="H22" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I22" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J22" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K22" s="11"/>
@@ -9233,13 +9285,13 @@
       </c>
       <c r="F23" s="22"/>
       <c r="G23" s="21"/>
-      <c r="H23" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I23" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J23" s="97" t="s">
+      <c r="H23" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I23" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J23" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K23" s="11"/>
@@ -9306,13 +9358,13 @@
       <c r="E27" s="42"/>
       <c r="F27" s="43"/>
       <c r="G27" s="21"/>
-      <c r="H27" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I27" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J27" s="97" t="s">
+      <c r="H27" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I27" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J27" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K27" s="11"/>
@@ -9331,13 +9383,13 @@
       <c r="E28" s="42"/>
       <c r="F28" s="43"/>
       <c r="G28" s="11"/>
-      <c r="H28" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I28" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J28" s="97" t="s">
+      <c r="H28" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I28" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J28" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K28" s="11"/>
@@ -9401,13 +9453,13 @@
       <c r="E32" s="42"/>
       <c r="F32" s="43"/>
       <c r="G32" s="11"/>
-      <c r="H32" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I32" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J32" s="97" t="s">
+      <c r="H32" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I32" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J32" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K32" s="11"/>
@@ -9493,24 +9545,24 @@
       <c r="B37" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C37" s="90" t="s">
+      <c r="C37" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="90"/>
-      <c r="E37" s="90"/>
-      <c r="F37" s="90"/>
-      <c r="G37" s="90"/>
-      <c r="H37" s="95"/>
-      <c r="I37" s="95"/>
-      <c r="J37" s="95"/>
-      <c r="K37" s="95"/>
+      <c r="D37" s="98"/>
+      <c r="E37" s="98"/>
+      <c r="F37" s="98"/>
+      <c r="G37" s="98"/>
+      <c r="H37" s="89"/>
+      <c r="I37" s="89"/>
+      <c r="J37" s="89"/>
+      <c r="K37" s="89"/>
     </row>
     <row r="38" spans="1:12" s="12" customFormat="1" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C38" s="98" t="s">
+      <c r="C38" s="92" t="s">
         <v>469</v>
       </c>
       <c r="D38" s="41" t="s">
@@ -9522,19 +9574,19 @@
       <c r="F38" s="42" t="s">
         <v>472</v>
       </c>
-      <c r="G38" s="99" t="s">
+      <c r="G38" s="93" t="s">
         <v>473</v>
       </c>
-      <c r="H38" s="96" t="s">
+      <c r="H38" s="90" t="s">
         <v>464</v>
       </c>
-      <c r="I38" s="96" t="s">
+      <c r="I38" s="90" t="s">
         <v>465</v>
       </c>
-      <c r="J38" s="96" t="s">
+      <c r="J38" s="90" t="s">
         <v>466</v>
       </c>
-      <c r="K38" s="96" t="s">
+      <c r="K38" s="90" t="s">
         <v>468</v>
       </c>
       <c r="L38" s="10"/>
@@ -9584,13 +9636,13 @@
         <v>6</v>
       </c>
       <c r="F41" s="10"/>
-      <c r="H41" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I41" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J41" s="97" t="s">
+      <c r="H41" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I41" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J41" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K41" s="11"/>
@@ -9608,13 +9660,13 @@
       </c>
       <c r="F42" s="10"/>
       <c r="G42" s="21"/>
-      <c r="H42" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I42" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J42" s="97" t="s">
+      <c r="H42" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I42" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J42" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K42" s="11"/>
@@ -9631,13 +9683,13 @@
         <v>3</v>
       </c>
       <c r="F43" s="10"/>
-      <c r="H43" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I43" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J43" s="97" t="s">
+      <c r="H43" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I43" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J43" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K43" s="11"/>
@@ -9656,13 +9708,13 @@
       <c r="E44" s="21"/>
       <c r="F44" s="22"/>
       <c r="G44" s="21"/>
-      <c r="H44" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I44" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J44" s="97" t="s">
+      <c r="H44" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I44" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J44" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K44" s="11"/>
@@ -9681,13 +9733,13 @@
       <c r="E45" s="21"/>
       <c r="F45" s="22"/>
       <c r="G45" s="21"/>
-      <c r="H45" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I45" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J45" s="97" t="s">
+      <c r="H45" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I45" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J45" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K45" s="11"/>
@@ -9706,13 +9758,13 @@
       <c r="E46" s="21"/>
       <c r="F46" s="22"/>
       <c r="G46" s="21"/>
-      <c r="H46" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I46" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J46" s="97" t="s">
+      <c r="H46" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I46" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J46" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K46" s="11"/>
@@ -9731,13 +9783,13 @@
       <c r="E47" s="21"/>
       <c r="F47" s="22"/>
       <c r="G47" s="21"/>
-      <c r="H47" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I47" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J47" s="97" t="s">
+      <c r="H47" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I47" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J47" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K47" s="11"/>
@@ -9759,13 +9811,13 @@
         <v>3</v>
       </c>
       <c r="G48" s="21"/>
-      <c r="H48" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I48" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J48" s="97" t="s">
+      <c r="H48" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I48" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J48" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K48" s="11"/>
@@ -9784,13 +9836,13 @@
       </c>
       <c r="F49" s="22"/>
       <c r="G49" s="21"/>
-      <c r="H49" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I49" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J49" s="97" t="s">
+      <c r="H49" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I49" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J49" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K49" s="11"/>
@@ -9857,13 +9909,13 @@
       </c>
       <c r="F53" s="43"/>
       <c r="G53" s="11"/>
-      <c r="H53" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I53" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J53" s="97" t="s">
+      <c r="H53" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I53" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J53" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K53" s="11"/>
@@ -9881,13 +9933,13 @@
       <c r="E54" s="42"/>
       <c r="F54" s="43"/>
       <c r="G54" s="11"/>
-      <c r="H54" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I54" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J54" s="97" t="s">
+      <c r="H54" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I54" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J54" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K54" s="11"/>
@@ -9905,13 +9957,13 @@
       <c r="E55" s="42"/>
       <c r="F55" s="43"/>
       <c r="G55" s="11"/>
-      <c r="H55" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I55" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J55" s="97" t="s">
+      <c r="H55" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I55" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J55" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K55" s="11"/>
@@ -9976,13 +10028,13 @@
       <c r="E59" s="42"/>
       <c r="F59" s="43"/>
       <c r="G59" s="11"/>
-      <c r="H59" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I59" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J59" s="97" t="s">
+      <c r="H59" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I59" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J59" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K59" s="11"/>
@@ -10000,13 +10052,13 @@
       <c r="E60" s="42"/>
       <c r="F60" s="43"/>
       <c r="G60" s="11"/>
-      <c r="H60" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I60" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J60" s="97" t="s">
+      <c r="H60" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I60" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J60" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K60" s="11"/>
@@ -10068,13 +10120,13 @@
       <c r="E64" s="42"/>
       <c r="F64" s="43"/>
       <c r="G64" s="11"/>
-      <c r="H64" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I64" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J64" s="97" t="s">
+      <c r="H64" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I64" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J64" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K64" s="11"/>
@@ -10091,13 +10143,13 @@
       <c r="E65" s="42"/>
       <c r="F65" s="43"/>
       <c r="G65" s="11"/>
-      <c r="H65" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I65" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J65" s="97" t="s">
+      <c r="H65" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I65" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J65" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K65" s="11"/>
@@ -10167,17 +10219,17 @@
       <c r="B69" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C69" s="90" t="s">
+      <c r="C69" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D69" s="90"/>
-      <c r="E69" s="90"/>
-      <c r="F69" s="90"/>
-      <c r="G69" s="90"/>
-      <c r="H69" s="95"/>
-      <c r="I69" s="95"/>
-      <c r="J69" s="95"/>
-      <c r="K69" s="95"/>
+      <c r="D69" s="98"/>
+      <c r="E69" s="98"/>
+      <c r="F69" s="98"/>
+      <c r="G69" s="98"/>
+      <c r="H69" s="89"/>
+      <c r="I69" s="89"/>
+      <c r="J69" s="89"/>
+      <c r="K69" s="89"/>
     </row>
     <row r="70" spans="1:12" s="24" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
@@ -10665,17 +10717,17 @@
       <c r="B98" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C98" s="90" t="s">
+      <c r="C98" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D98" s="90"/>
-      <c r="E98" s="90"/>
-      <c r="F98" s="90"/>
-      <c r="G98" s="90"/>
-      <c r="H98" s="95"/>
-      <c r="I98" s="95"/>
-      <c r="J98" s="95"/>
-      <c r="K98" s="95"/>
+      <c r="D98" s="98"/>
+      <c r="E98" s="98"/>
+      <c r="F98" s="98"/>
+      <c r="G98" s="98"/>
+      <c r="H98" s="89"/>
+      <c r="I98" s="89"/>
+      <c r="J98" s="89"/>
+      <c r="K98" s="89"/>
     </row>
     <row r="99" spans="1:12" s="24" customFormat="1" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
@@ -11163,17 +11215,17 @@
       <c r="B126" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C126" s="90" t="s">
+      <c r="C126" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D126" s="90"/>
-      <c r="E126" s="90"/>
-      <c r="F126" s="90"/>
-      <c r="G126" s="90"/>
-      <c r="H126" s="95"/>
-      <c r="I126" s="95"/>
-      <c r="J126" s="95"/>
-      <c r="K126" s="95"/>
+      <c r="D126" s="98"/>
+      <c r="E126" s="98"/>
+      <c r="F126" s="98"/>
+      <c r="G126" s="98"/>
+      <c r="H126" s="89"/>
+      <c r="I126" s="89"/>
+      <c r="J126" s="89"/>
+      <c r="K126" s="89"/>
     </row>
     <row r="127" spans="1:12" customFormat="1" ht="103.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
@@ -11854,25 +11906,25 @@
       <c r="B166" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C166" s="90" t="s">
+      <c r="C166" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D166" s="90"/>
-      <c r="E166" s="90"/>
-      <c r="F166" s="90"/>
-      <c r="G166" s="90"/>
-      <c r="H166" s="100"/>
-      <c r="I166" s="101"/>
-      <c r="J166" s="101"/>
-      <c r="K166" s="101"/>
-      <c r="L166" s="102"/>
+      <c r="D166" s="98"/>
+      <c r="E166" s="98"/>
+      <c r="F166" s="98"/>
+      <c r="G166" s="98"/>
+      <c r="H166" s="95"/>
+      <c r="I166" s="96"/>
+      <c r="J166" s="96"/>
+      <c r="K166" s="96"/>
+      <c r="L166" s="94"/>
     </row>
     <row r="167" spans="1:12" s="24" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C167" s="98" t="s">
+      <c r="C167" s="92" t="s">
         <v>469</v>
       </c>
       <c r="D167" s="41" t="s">
@@ -11884,19 +11936,19 @@
       <c r="F167" s="42" t="s">
         <v>472</v>
       </c>
-      <c r="G167" s="99" t="s">
+      <c r="G167" s="93" t="s">
         <v>473</v>
       </c>
-      <c r="H167" s="96" t="s">
+      <c r="H167" s="90" t="s">
         <v>464</v>
       </c>
-      <c r="I167" s="96" t="s">
+      <c r="I167" s="90" t="s">
         <v>465</v>
       </c>
-      <c r="J167" s="96" t="s">
+      <c r="J167" s="90" t="s">
         <v>466</v>
       </c>
-      <c r="K167" s="96" t="s">
+      <c r="K167" s="90" t="s">
         <v>468</v>
       </c>
       <c r="L167" s="10"/>
@@ -11947,13 +11999,13 @@
       <c r="E170" s="42"/>
       <c r="F170" s="43"/>
       <c r="G170" s="10"/>
-      <c r="H170" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I170" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J170" s="97" t="s">
+      <c r="H170" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I170" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J170" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K170" s="10"/>
@@ -11971,13 +12023,13 @@
       <c r="E171" s="42"/>
       <c r="F171" s="43"/>
       <c r="G171" s="10"/>
-      <c r="H171" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I171" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J171" s="97" t="s">
+      <c r="H171" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I171" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J171" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K171" s="10"/>
@@ -12043,13 +12095,13 @@
       <c r="E175" s="42"/>
       <c r="F175" s="43"/>
       <c r="G175" s="10"/>
-      <c r="H175" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I175" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J175" s="97" t="s">
+      <c r="H175" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I175" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J175" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K175" s="10"/>
@@ -12066,13 +12118,13 @@
       <c r="E176" s="42"/>
       <c r="F176" s="43"/>
       <c r="G176" s="10"/>
-      <c r="H176" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I176" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J176" s="97" t="s">
+      <c r="H176" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I176" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J176" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K176" s="10"/>
@@ -12136,13 +12188,13 @@
       <c r="E180" s="42"/>
       <c r="F180" s="43"/>
       <c r="G180" s="10"/>
-      <c r="H180" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I180" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J180" s="97" t="s">
+      <c r="H180" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I180" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J180" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K180" s="10"/>
@@ -12160,13 +12212,13 @@
       <c r="E181" s="42"/>
       <c r="F181" s="43"/>
       <c r="G181" s="10"/>
-      <c r="H181" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I181" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J181" s="97" t="s">
+      <c r="H181" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I181" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J181" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K181" s="10"/>
@@ -12184,13 +12236,13 @@
       <c r="E182" s="42"/>
       <c r="F182" s="43"/>
       <c r="G182" s="10"/>
-      <c r="H182" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I182" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J182" s="97" t="s">
+      <c r="H182" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I182" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J182" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K182" s="10"/>
@@ -12257,13 +12309,13 @@
       </c>
       <c r="F186" s="43"/>
       <c r="G186" s="10"/>
-      <c r="H186" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I186" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J186" s="97" t="s">
+      <c r="H186" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I186" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J186" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K186" s="10"/>
@@ -12282,13 +12334,13 @@
       <c r="E187" s="42"/>
       <c r="F187" s="43"/>
       <c r="G187" s="10"/>
-      <c r="H187" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I187" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J187" s="97" t="s">
+      <c r="H187" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I187" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J187" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K187" s="10"/>
@@ -12307,13 +12359,13 @@
       <c r="E188" s="42"/>
       <c r="F188" s="43"/>
       <c r="G188" s="10"/>
-      <c r="H188" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I188" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J188" s="97" t="s">
+      <c r="H188" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I188" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J188" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K188" s="10"/>
@@ -12385,20 +12437,20 @@
       <c r="B192" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C192" s="90" t="s">
+      <c r="C192" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D192" s="90"/>
-      <c r="E192" s="90"/>
-      <c r="F192" s="90"/>
-      <c r="G192" s="90"/>
-      <c r="H192" s="100" t="s">
+      <c r="D192" s="98"/>
+      <c r="E192" s="98"/>
+      <c r="F192" s="98"/>
+      <c r="G192" s="98"/>
+      <c r="H192" s="95" t="s">
         <v>474</v>
       </c>
-      <c r="I192" s="101"/>
-      <c r="J192" s="101"/>
-      <c r="K192" s="101"/>
-      <c r="L192" s="102" t="s">
+      <c r="I192" s="96"/>
+      <c r="J192" s="96"/>
+      <c r="K192" s="96"/>
+      <c r="L192" s="94" t="s">
         <v>460</v>
       </c>
     </row>
@@ -12407,7 +12459,7 @@
       <c r="B193" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C193" s="98" t="s">
+      <c r="C193" s="92" t="s">
         <v>469</v>
       </c>
       <c r="D193" s="41" t="s">
@@ -12419,19 +12471,19 @@
       <c r="F193" s="42" t="s">
         <v>472</v>
       </c>
-      <c r="G193" s="99" t="s">
+      <c r="G193" s="93" t="s">
         <v>473</v>
       </c>
-      <c r="H193" s="96" t="s">
+      <c r="H193" s="90" t="s">
         <v>464</v>
       </c>
-      <c r="I193" s="96" t="s">
+      <c r="I193" s="90" t="s">
         <v>465</v>
       </c>
-      <c r="J193" s="96" t="s">
+      <c r="J193" s="90" t="s">
         <v>466</v>
       </c>
-      <c r="K193" s="96" t="s">
+      <c r="K193" s="90" t="s">
         <v>468</v>
       </c>
       <c r="L193" s="10"/>
@@ -12481,13 +12533,13 @@
       <c r="E196" s="42"/>
       <c r="F196" s="43"/>
       <c r="G196" s="11"/>
-      <c r="H196" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I196" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J196" s="97" t="s">
+      <c r="H196" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I196" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J196" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K196" s="11"/>
@@ -12540,13 +12592,13 @@
       <c r="E199" s="42"/>
       <c r="F199" s="43"/>
       <c r="G199" s="11"/>
-      <c r="H199" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I199" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J199" s="97" t="s">
+      <c r="H199" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I199" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J199" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K199" s="11"/>
@@ -12564,13 +12616,13 @@
       <c r="E200" s="42"/>
       <c r="F200" s="43"/>
       <c r="G200" s="11"/>
-      <c r="H200" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I200" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J200" s="97" t="s">
+      <c r="H200" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I200" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J200" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K200" s="11"/>
@@ -12635,13 +12687,13 @@
       <c r="E204" s="42"/>
       <c r="F204" s="43"/>
       <c r="G204" s="11"/>
-      <c r="H204" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I204" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J204" s="97" t="s">
+      <c r="H204" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I204" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J204" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K204" s="11"/>
@@ -12660,13 +12712,13 @@
       <c r="E205" s="42"/>
       <c r="F205" s="43"/>
       <c r="G205" s="11"/>
-      <c r="H205" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I205" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J205" s="97" t="s">
+      <c r="H205" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I205" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J205" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K205" s="11"/>
@@ -12730,13 +12782,13 @@
       <c r="E209" s="42"/>
       <c r="F209" s="43"/>
       <c r="G209" s="11"/>
-      <c r="H209" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I209" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J209" s="97" t="s">
+      <c r="H209" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I209" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J209" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K209" s="11"/>
@@ -12754,13 +12806,13 @@
       <c r="E210" s="42"/>
       <c r="F210" s="43"/>
       <c r="G210" s="11"/>
-      <c r="H210" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I210" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J210" s="97" t="s">
+      <c r="H210" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I210" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J210" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K210" s="11"/>
@@ -12778,13 +12830,13 @@
       <c r="E211" s="42"/>
       <c r="F211" s="43"/>
       <c r="G211" s="11"/>
-      <c r="H211" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="I211" s="97" t="s">
-        <v>467</v>
-      </c>
-      <c r="J211" s="97" t="s">
+      <c r="H211" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I211" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J211" s="91" t="s">
         <v>467</v>
       </c>
       <c r="K211" s="11"/>
@@ -12856,17 +12908,17 @@
       <c r="B215" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C215" s="90" t="s">
+      <c r="C215" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D215" s="90"/>
-      <c r="E215" s="90"/>
-      <c r="F215" s="90"/>
-      <c r="G215" s="90"/>
-      <c r="H215" s="95"/>
-      <c r="I215" s="95"/>
-      <c r="J215" s="95"/>
-      <c r="K215" s="95"/>
+      <c r="D215" s="98"/>
+      <c r="E215" s="98"/>
+      <c r="F215" s="98"/>
+      <c r="G215" s="98"/>
+      <c r="H215" s="89"/>
+      <c r="I215" s="89"/>
+      <c r="J215" s="89"/>
+      <c r="K215" s="89"/>
     </row>
     <row r="216" spans="1:12" s="24" customFormat="1" ht="93.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
@@ -12937,10 +12989,16 @@
         <v>2</v>
       </c>
       <c r="F219" s="57"/>
-      <c r="G219" s="23"/>
-      <c r="H219" s="23"/>
-      <c r="I219" s="23"/>
-      <c r="J219" s="23"/>
+      <c r="G219" s="11"/>
+      <c r="H219" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I219" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J219" s="91" t="s">
+        <v>467</v>
+      </c>
       <c r="K219" s="23"/>
       <c r="L219" s="57"/>
     </row>
@@ -12954,7 +13012,7 @@
         <v>1</v>
       </c>
       <c r="F220" s="57"/>
-      <c r="G220" s="23"/>
+      <c r="G220" s="11"/>
       <c r="H220" s="23"/>
       <c r="I220" s="23"/>
       <c r="J220" s="23"/>
@@ -12971,7 +13029,7 @@
         <v>2</v>
       </c>
       <c r="F221" s="57"/>
-      <c r="G221" s="23"/>
+      <c r="G221" s="11"/>
       <c r="H221" s="23"/>
       <c r="I221" s="23"/>
       <c r="J221" s="23"/>
@@ -12989,7 +13047,7 @@
       </c>
       <c r="E222" s="56"/>
       <c r="F222" s="57"/>
-      <c r="G222" s="23"/>
+      <c r="G222" s="11"/>
       <c r="H222" s="23"/>
       <c r="I222" s="23"/>
       <c r="J222" s="23"/>
@@ -13007,7 +13065,7 @@
       <c r="D223" s="55"/>
       <c r="E223" s="56"/>
       <c r="F223" s="57"/>
-      <c r="G223" s="23"/>
+      <c r="G223" s="11"/>
       <c r="H223" s="23"/>
       <c r="I223" s="23"/>
       <c r="J223" s="23"/>
@@ -13025,7 +13083,7 @@
       <c r="D224" s="55"/>
       <c r="E224" s="56"/>
       <c r="F224" s="57"/>
-      <c r="G224" s="23"/>
+      <c r="G224" s="11"/>
       <c r="H224" s="23"/>
       <c r="I224" s="23"/>
       <c r="J224" s="23"/>
@@ -13043,7 +13101,7 @@
       <c r="D225" s="55"/>
       <c r="E225" s="56"/>
       <c r="F225" s="57"/>
-      <c r="G225" s="23"/>
+      <c r="G225" s="11"/>
       <c r="H225" s="23"/>
       <c r="I225" s="23"/>
       <c r="J225" s="23"/>
@@ -13061,7 +13119,7 @@
       <c r="D226" s="55"/>
       <c r="E226" s="56"/>
       <c r="F226" s="57"/>
-      <c r="G226" s="23"/>
+      <c r="G226" s="11"/>
       <c r="H226" s="23"/>
       <c r="I226" s="23"/>
       <c r="J226" s="23"/>
@@ -13081,7 +13139,7 @@
       <c r="F227" s="57">
         <v>1</v>
       </c>
-      <c r="G227" s="23"/>
+      <c r="G227" s="11"/>
       <c r="H227" s="23"/>
       <c r="I227" s="23"/>
       <c r="J227" s="23"/>
@@ -13099,7 +13157,7 @@
       <c r="D228" s="55"/>
       <c r="E228" s="56"/>
       <c r="F228" s="57"/>
-      <c r="G228" s="23"/>
+      <c r="G228" s="11"/>
       <c r="H228" s="23"/>
       <c r="I228" s="23"/>
       <c r="J228" s="23"/>
@@ -13117,7 +13175,7 @@
       <c r="D229" s="55"/>
       <c r="E229" s="56"/>
       <c r="F229" s="57"/>
-      <c r="G229" s="23"/>
+      <c r="G229" s="11"/>
       <c r="H229" s="23"/>
       <c r="I229" s="23"/>
       <c r="J229" s="23"/>
@@ -13137,7 +13195,7 @@
       <c r="F230" s="57">
         <v>1</v>
       </c>
-      <c r="G230" s="23"/>
+      <c r="G230" s="11"/>
       <c r="H230" s="23"/>
       <c r="I230" s="23"/>
       <c r="J230" s="23"/>
@@ -13155,7 +13213,7 @@
         <v>1</v>
       </c>
       <c r="F231" s="57"/>
-      <c r="G231" s="23"/>
+      <c r="G231" s="11"/>
       <c r="H231" s="23"/>
       <c r="I231" s="23"/>
       <c r="J231" s="23"/>
@@ -13170,7 +13228,7 @@
       <c r="C232" s="54"/>
       <c r="D232" s="55"/>
       <c r="F232" s="57"/>
-      <c r="G232" s="23">
+      <c r="G232" s="11">
         <v>1</v>
       </c>
       <c r="H232" s="23"/>
@@ -13192,7 +13250,7 @@
       <c r="F233" s="57">
         <v>1</v>
       </c>
-      <c r="G233" s="23"/>
+      <c r="G233" s="11"/>
       <c r="H233" s="23"/>
       <c r="I233" s="23"/>
       <c r="J233" s="23"/>
@@ -13210,7 +13268,7 @@
       </c>
       <c r="E234" s="56"/>
       <c r="F234" s="57"/>
-      <c r="G234" s="23"/>
+      <c r="G234" s="11"/>
       <c r="H234" s="23"/>
       <c r="I234" s="23"/>
       <c r="J234" s="23"/>
@@ -13228,7 +13286,7 @@
       <c r="D235" s="55"/>
       <c r="E235" s="56"/>
       <c r="F235" s="57"/>
-      <c r="G235" s="23"/>
+      <c r="G235" s="11"/>
       <c r="H235" s="23"/>
       <c r="I235" s="23"/>
       <c r="J235" s="23"/>
@@ -13246,7 +13304,7 @@
       <c r="D236" s="55"/>
       <c r="E236" s="56"/>
       <c r="F236" s="57"/>
-      <c r="G236" s="23"/>
+      <c r="G236" s="11"/>
       <c r="H236" s="23"/>
       <c r="I236" s="23"/>
       <c r="J236" s="23"/>
@@ -13264,7 +13322,7 @@
       <c r="D237" s="55"/>
       <c r="E237" s="56"/>
       <c r="F237" s="57"/>
-      <c r="G237" s="23"/>
+      <c r="G237" s="11"/>
       <c r="H237" s="23"/>
       <c r="I237" s="23"/>
       <c r="J237" s="23"/>
@@ -13282,7 +13340,7 @@
       <c r="D238" s="55"/>
       <c r="E238" s="56"/>
       <c r="F238" s="57"/>
-      <c r="G238" s="23"/>
+      <c r="G238" s="11"/>
       <c r="H238" s="23"/>
       <c r="I238" s="23"/>
       <c r="J238" s="23"/>
@@ -13300,7 +13358,7 @@
         <v>2</v>
       </c>
       <c r="F239" s="57"/>
-      <c r="G239" s="23"/>
+      <c r="G239" s="11"/>
       <c r="H239" s="23"/>
       <c r="I239" s="23"/>
       <c r="J239" s="23"/>
@@ -13318,7 +13376,7 @@
       </c>
       <c r="E240" s="56"/>
       <c r="F240" s="57"/>
-      <c r="G240" s="23"/>
+      <c r="G240" s="11"/>
       <c r="H240" s="23"/>
       <c r="I240" s="23"/>
       <c r="J240" s="23"/>
@@ -13336,7 +13394,7 @@
       <c r="D241" s="55"/>
       <c r="E241" s="56"/>
       <c r="F241" s="57"/>
-      <c r="G241" s="23"/>
+      <c r="G241" s="11"/>
       <c r="H241" s="23"/>
       <c r="I241" s="23"/>
       <c r="J241" s="23"/>
@@ -13354,7 +13412,7 @@
       <c r="D242" s="55"/>
       <c r="E242" s="56"/>
       <c r="F242" s="57"/>
-      <c r="G242" s="23"/>
+      <c r="G242" s="11"/>
       <c r="H242" s="23"/>
       <c r="I242" s="23"/>
       <c r="J242" s="23"/>
@@ -13372,7 +13430,7 @@
         <v>2</v>
       </c>
       <c r="F243" s="57"/>
-      <c r="G243" s="23"/>
+      <c r="G243" s="11"/>
       <c r="H243" s="23"/>
       <c r="I243" s="23"/>
       <c r="J243" s="23"/>
@@ -13390,7 +13448,7 @@
         <v>1</v>
       </c>
       <c r="F244" s="57"/>
-      <c r="G244" s="23"/>
+      <c r="G244" s="11"/>
       <c r="H244" s="23"/>
       <c r="I244" s="23"/>
       <c r="J244" s="23"/>
@@ -13408,7 +13466,7 @@
         <v>1</v>
       </c>
       <c r="F245" s="57"/>
-      <c r="G245" s="23"/>
+      <c r="G245" s="11"/>
       <c r="H245" s="23"/>
       <c r="I245" s="23"/>
       <c r="J245" s="23"/>
@@ -13426,7 +13484,7 @@
         <v>4</v>
       </c>
       <c r="F246" s="57"/>
-      <c r="G246" s="23"/>
+      <c r="G246" s="11"/>
       <c r="H246" s="23"/>
       <c r="I246" s="23"/>
       <c r="J246" s="23"/>
@@ -13444,7 +13502,7 @@
         <v>1</v>
       </c>
       <c r="F247" s="57"/>
-      <c r="G247" s="23"/>
+      <c r="G247" s="11"/>
       <c r="H247" s="23"/>
       <c r="I247" s="23"/>
       <c r="J247" s="23"/>
@@ -13464,7 +13522,7 @@
       <c r="F248" s="57">
         <v>1</v>
       </c>
-      <c r="G248" s="23"/>
+      <c r="G248" s="11"/>
       <c r="H248" s="23"/>
       <c r="I248" s="23"/>
       <c r="J248" s="23"/>
@@ -13478,7 +13536,7 @@
       <c r="D249" s="55"/>
       <c r="E249" s="56"/>
       <c r="F249" s="57"/>
-      <c r="G249" s="57"/>
+      <c r="G249" s="11"/>
       <c r="H249" s="57"/>
       <c r="I249" s="57"/>
       <c r="J249" s="57"/>
@@ -13530,7 +13588,7 @@
       <c r="D252" s="41"/>
       <c r="E252" s="42"/>
       <c r="F252" s="43"/>
-      <c r="G252" s="23"/>
+      <c r="G252" s="11"/>
       <c r="H252" s="23"/>
       <c r="I252" s="23"/>
       <c r="J252" s="23"/>
@@ -13547,7 +13605,7 @@
       <c r="D253" s="41"/>
       <c r="E253" s="42"/>
       <c r="F253" s="43"/>
-      <c r="G253" s="23"/>
+      <c r="G253" s="11"/>
       <c r="H253" s="23"/>
       <c r="I253" s="23"/>
       <c r="J253" s="23"/>
@@ -13561,7 +13619,7 @@
       <c r="D254" s="29"/>
       <c r="E254" s="30"/>
       <c r="F254" s="31"/>
-      <c r="G254" s="32"/>
+      <c r="G254" s="11"/>
       <c r="H254" s="32"/>
       <c r="I254" s="32"/>
       <c r="J254" s="32"/>
@@ -13611,7 +13669,7 @@
         <v>2</v>
       </c>
       <c r="F257" s="57"/>
-      <c r="G257" s="23"/>
+      <c r="G257" s="11"/>
       <c r="H257" s="23"/>
       <c r="I257" s="23"/>
       <c r="J257" s="23"/>
@@ -13628,7 +13686,7 @@
         <v>1</v>
       </c>
       <c r="F258" s="57"/>
-      <c r="G258" s="23"/>
+      <c r="G258" s="11"/>
       <c r="H258" s="23"/>
       <c r="I258" s="23"/>
       <c r="J258" s="23"/>
@@ -13645,7 +13703,7 @@
         <v>2</v>
       </c>
       <c r="F259" s="57"/>
-      <c r="G259" s="23"/>
+      <c r="G259" s="11"/>
       <c r="H259" s="23"/>
       <c r="I259" s="23"/>
       <c r="J259" s="23"/>
@@ -13663,7 +13721,7 @@
       </c>
       <c r="E260" s="56"/>
       <c r="F260" s="57"/>
-      <c r="G260" s="23"/>
+      <c r="G260" s="11"/>
       <c r="H260" s="23"/>
       <c r="I260" s="23"/>
       <c r="J260" s="23"/>
@@ -13681,7 +13739,7 @@
       <c r="D261" s="55"/>
       <c r="E261" s="56"/>
       <c r="F261" s="57"/>
-      <c r="G261" s="23"/>
+      <c r="G261" s="11"/>
       <c r="H261" s="23"/>
       <c r="I261" s="23"/>
       <c r="J261" s="23"/>
@@ -13699,7 +13757,7 @@
       <c r="D262" s="55"/>
       <c r="E262" s="56"/>
       <c r="F262" s="57"/>
-      <c r="G262" s="23"/>
+      <c r="G262" s="11"/>
       <c r="H262" s="23"/>
       <c r="I262" s="23"/>
       <c r="J262" s="23"/>
@@ -13717,7 +13775,7 @@
       <c r="D263" s="55"/>
       <c r="E263" s="56"/>
       <c r="F263" s="57"/>
-      <c r="G263" s="23"/>
+      <c r="G263" s="11"/>
       <c r="H263" s="23"/>
       <c r="I263" s="23"/>
       <c r="J263" s="23"/>
@@ -13735,7 +13793,7 @@
       <c r="D264" s="55"/>
       <c r="E264" s="56"/>
       <c r="F264" s="57"/>
-      <c r="G264" s="23"/>
+      <c r="G264" s="11"/>
       <c r="H264" s="23"/>
       <c r="I264" s="23"/>
       <c r="J264" s="23"/>
@@ -13755,7 +13813,7 @@
       <c r="F265" s="57">
         <v>1</v>
       </c>
-      <c r="G265" s="23"/>
+      <c r="G265" s="11"/>
       <c r="H265" s="23"/>
       <c r="I265" s="23"/>
       <c r="J265" s="23"/>
@@ -13773,7 +13831,7 @@
       <c r="D266" s="55"/>
       <c r="E266" s="56"/>
       <c r="F266" s="57"/>
-      <c r="G266" s="23"/>
+      <c r="G266" s="11"/>
       <c r="H266" s="23"/>
       <c r="I266" s="23"/>
       <c r="J266" s="23"/>
@@ -13791,7 +13849,7 @@
       <c r="D267" s="55"/>
       <c r="E267" s="56"/>
       <c r="F267" s="57"/>
-      <c r="G267" s="23"/>
+      <c r="G267" s="11"/>
       <c r="H267" s="23"/>
       <c r="I267" s="23"/>
       <c r="J267" s="23"/>
@@ -13811,7 +13869,7 @@
       <c r="F268" s="57">
         <v>1</v>
       </c>
-      <c r="G268" s="23"/>
+      <c r="G268" s="11"/>
       <c r="H268" s="23"/>
       <c r="I268" s="23"/>
       <c r="J268" s="23"/>
@@ -13829,7 +13887,7 @@
         <v>1</v>
       </c>
       <c r="F269" s="57"/>
-      <c r="G269" s="23"/>
+      <c r="G269" s="11"/>
       <c r="H269" s="23"/>
       <c r="I269" s="23"/>
       <c r="J269" s="23"/>
@@ -13844,7 +13902,7 @@
       <c r="C270" s="54"/>
       <c r="D270" s="55"/>
       <c r="F270" s="57"/>
-      <c r="G270" s="23"/>
+      <c r="G270" s="11"/>
       <c r="H270" s="23"/>
       <c r="I270" s="23"/>
       <c r="J270" s="23"/>
@@ -13864,7 +13922,7 @@
       <c r="F271" s="57">
         <v>1</v>
       </c>
-      <c r="G271" s="23"/>
+      <c r="G271" s="11"/>
       <c r="H271" s="23"/>
       <c r="I271" s="23"/>
       <c r="J271" s="23"/>
@@ -13882,7 +13940,7 @@
       </c>
       <c r="E272" s="56"/>
       <c r="F272" s="57"/>
-      <c r="G272" s="23"/>
+      <c r="G272" s="11"/>
       <c r="H272" s="23"/>
       <c r="I272" s="23"/>
       <c r="J272" s="23"/>
@@ -13900,7 +13958,7 @@
       <c r="D273" s="55"/>
       <c r="E273" s="56"/>
       <c r="F273" s="57"/>
-      <c r="G273" s="23">
+      <c r="G273" s="11">
         <v>1</v>
       </c>
       <c r="H273" s="23"/>
@@ -13920,7 +13978,7 @@
       <c r="D274" s="55"/>
       <c r="E274" s="56"/>
       <c r="F274" s="57"/>
-      <c r="G274" s="23"/>
+      <c r="G274" s="11"/>
       <c r="H274" s="23"/>
       <c r="I274" s="23"/>
       <c r="J274" s="23"/>
@@ -13938,7 +13996,7 @@
       <c r="D275" s="55"/>
       <c r="E275" s="56"/>
       <c r="F275" s="57"/>
-      <c r="G275" s="23"/>
+      <c r="G275" s="11"/>
       <c r="H275" s="23"/>
       <c r="I275" s="23"/>
       <c r="J275" s="23"/>
@@ -13956,7 +14014,7 @@
       <c r="D276" s="55"/>
       <c r="E276" s="56"/>
       <c r="F276" s="57"/>
-      <c r="G276" s="23"/>
+      <c r="G276" s="11"/>
       <c r="H276" s="23"/>
       <c r="I276" s="23"/>
       <c r="J276" s="23"/>
@@ -13974,7 +14032,7 @@
         <v>2</v>
       </c>
       <c r="F277" s="57"/>
-      <c r="G277" s="23"/>
+      <c r="G277" s="11"/>
       <c r="H277" s="23"/>
       <c r="I277" s="23"/>
       <c r="J277" s="23"/>
@@ -13992,7 +14050,7 @@
       </c>
       <c r="E278" s="56"/>
       <c r="F278" s="57"/>
-      <c r="G278" s="23"/>
+      <c r="G278" s="11"/>
       <c r="H278" s="23"/>
       <c r="I278" s="23"/>
       <c r="J278" s="23"/>
@@ -14010,7 +14068,7 @@
       <c r="D279" s="55"/>
       <c r="E279" s="56"/>
       <c r="F279" s="57"/>
-      <c r="G279" s="23"/>
+      <c r="G279" s="11"/>
       <c r="H279" s="23"/>
       <c r="I279" s="23"/>
       <c r="J279" s="23"/>
@@ -14028,7 +14086,7 @@
       <c r="D280" s="55"/>
       <c r="E280" s="56"/>
       <c r="F280" s="57"/>
-      <c r="G280" s="23"/>
+      <c r="G280" s="11"/>
       <c r="H280" s="23"/>
       <c r="I280" s="23"/>
       <c r="J280" s="23"/>
@@ -14046,7 +14104,7 @@
         <v>2</v>
       </c>
       <c r="F281" s="57"/>
-      <c r="G281" s="23"/>
+      <c r="G281" s="11"/>
       <c r="H281" s="23"/>
       <c r="I281" s="23"/>
       <c r="J281" s="23"/>
@@ -14064,7 +14122,7 @@
         <v>1</v>
       </c>
       <c r="F282" s="57"/>
-      <c r="G282" s="23"/>
+      <c r="G282" s="11"/>
       <c r="H282" s="23"/>
       <c r="I282" s="23"/>
       <c r="J282" s="23"/>
@@ -14082,7 +14140,7 @@
         <v>1</v>
       </c>
       <c r="F283" s="57"/>
-      <c r="G283" s="23"/>
+      <c r="G283" s="11"/>
       <c r="H283" s="23"/>
       <c r="I283" s="23"/>
       <c r="J283" s="23"/>
@@ -14100,7 +14158,7 @@
         <v>4</v>
       </c>
       <c r="F284" s="57"/>
-      <c r="G284" s="23"/>
+      <c r="G284" s="11"/>
       <c r="H284" s="23"/>
       <c r="I284" s="23"/>
       <c r="J284" s="23"/>
@@ -14118,7 +14176,7 @@
         <v>1</v>
       </c>
       <c r="F285" s="57"/>
-      <c r="G285" s="23"/>
+      <c r="G285" s="11"/>
       <c r="H285" s="23"/>
       <c r="I285" s="23"/>
       <c r="J285" s="23"/>
@@ -14138,7 +14196,7 @@
       <c r="F286" s="57">
         <v>1</v>
       </c>
-      <c r="G286" s="23"/>
+      <c r="G286" s="11"/>
       <c r="H286" s="23"/>
       <c r="I286" s="23"/>
       <c r="J286" s="23"/>
@@ -14152,7 +14210,7 @@
       <c r="D287" s="55"/>
       <c r="E287" s="56"/>
       <c r="F287" s="57"/>
-      <c r="G287" s="23"/>
+      <c r="G287" s="11"/>
       <c r="H287" s="23"/>
       <c r="I287" s="23"/>
       <c r="J287" s="23"/>
@@ -14205,7 +14263,7 @@
       <c r="D290" s="41"/>
       <c r="E290" s="42"/>
       <c r="F290" s="43"/>
-      <c r="G290" s="23">
+      <c r="G290" s="11">
         <v>2</v>
       </c>
       <c r="H290" s="23"/>
@@ -14225,7 +14283,7 @@
       <c r="D291" s="41"/>
       <c r="E291" s="42"/>
       <c r="F291" s="43"/>
-      <c r="G291" s="23"/>
+      <c r="G291" s="11"/>
       <c r="H291" s="23"/>
       <c r="I291" s="23"/>
       <c r="J291" s="23"/>
@@ -14241,7 +14299,7 @@
       <c r="D292" s="41"/>
       <c r="E292" s="42"/>
       <c r="F292" s="43"/>
-      <c r="G292" s="23">
+      <c r="G292" s="11">
         <v>2</v>
       </c>
       <c r="H292" s="23"/>
@@ -14259,7 +14317,7 @@
       <c r="D293" s="41"/>
       <c r="E293" s="42"/>
       <c r="F293" s="43"/>
-      <c r="G293" s="23">
+      <c r="G293" s="11">
         <v>2</v>
       </c>
       <c r="H293" s="23"/>
@@ -14280,7 +14338,7 @@
       <c r="D294" s="41"/>
       <c r="E294" s="42"/>
       <c r="F294" s="43"/>
-      <c r="G294" s="23"/>
+      <c r="G294" s="11"/>
       <c r="H294" s="23"/>
       <c r="I294" s="23"/>
       <c r="J294" s="23"/>
@@ -14294,7 +14352,7 @@
       <c r="D295" s="29"/>
       <c r="E295" s="30"/>
       <c r="F295" s="31"/>
-      <c r="G295" s="32"/>
+      <c r="G295" s="11"/>
       <c r="H295" s="32"/>
       <c r="I295" s="32"/>
       <c r="J295" s="32"/>
@@ -14344,7 +14402,7 @@
       <c r="D298" s="41"/>
       <c r="E298" s="9"/>
       <c r="F298" s="43"/>
-      <c r="G298" s="23">
+      <c r="G298" s="11">
         <v>1</v>
       </c>
       <c r="H298" s="23"/>
@@ -14361,7 +14419,7 @@
       <c r="D299" s="41"/>
       <c r="E299" s="9"/>
       <c r="F299" s="43"/>
-      <c r="G299" s="23">
+      <c r="G299" s="11">
         <v>1</v>
       </c>
       <c r="H299" s="23"/>
@@ -14380,7 +14438,7 @@
       <c r="D300" s="41"/>
       <c r="E300" s="9"/>
       <c r="F300" s="43"/>
-      <c r="G300" s="23">
+      <c r="G300" s="11">
         <v>1</v>
       </c>
       <c r="H300" s="23"/>
@@ -14400,7 +14458,7 @@
       <c r="D301" s="41"/>
       <c r="E301" s="42"/>
       <c r="F301" s="43"/>
-      <c r="G301" s="23"/>
+      <c r="G301" s="11"/>
       <c r="H301" s="23"/>
       <c r="I301" s="23"/>
       <c r="J301" s="23"/>
@@ -14418,7 +14476,7 @@
       <c r="D302" s="41"/>
       <c r="E302" s="42"/>
       <c r="F302" s="43"/>
-      <c r="G302" s="23"/>
+      <c r="G302" s="11"/>
       <c r="H302" s="23"/>
       <c r="I302" s="23"/>
       <c r="J302" s="23"/>
@@ -14432,7 +14490,7 @@
       <c r="D303" s="29"/>
       <c r="E303" s="30"/>
       <c r="F303" s="31"/>
-      <c r="G303" s="32"/>
+      <c r="G303" s="11"/>
       <c r="H303" s="32"/>
       <c r="I303" s="32"/>
       <c r="J303" s="32"/>
@@ -14483,7 +14541,7 @@
       <c r="D306" s="41"/>
       <c r="E306" s="42"/>
       <c r="F306" s="43"/>
-      <c r="G306" s="23"/>
+      <c r="G306" s="11"/>
       <c r="H306" s="23"/>
       <c r="I306" s="23"/>
       <c r="J306" s="23"/>
@@ -14497,7 +14555,7 @@
       <c r="D307" s="41"/>
       <c r="E307" s="42"/>
       <c r="F307" s="43"/>
-      <c r="G307" s="23"/>
+      <c r="G307" s="11"/>
       <c r="H307" s="23"/>
       <c r="I307" s="23"/>
       <c r="J307" s="23"/>
@@ -14556,42 +14614,50 @@
       <c r="B310" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C310" s="90" t="s">
+      <c r="C310" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D310" s="90"/>
-      <c r="E310" s="90"/>
-      <c r="F310" s="90"/>
-      <c r="G310" s="90"/>
-      <c r="H310" s="95"/>
-      <c r="I310" s="95"/>
-      <c r="J310" s="95"/>
-      <c r="K310" s="95"/>
+      <c r="D310" s="98"/>
+      <c r="E310" s="98"/>
+      <c r="F310" s="98"/>
+      <c r="G310" s="98"/>
+      <c r="H310" s="89"/>
+      <c r="I310" s="89"/>
+      <c r="J310" s="89"/>
+      <c r="K310" s="89"/>
     </row>
     <row r="311" spans="1:12" s="24" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C311" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D311" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E311" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F311" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G311" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="H311" s="11"/>
-      <c r="I311" s="11"/>
-      <c r="J311" s="11"/>
-      <c r="K311" s="11"/>
+      <c r="C311" s="92" t="s">
+        <v>469</v>
+      </c>
+      <c r="D311" s="41" t="s">
+        <v>470</v>
+      </c>
+      <c r="E311" s="42" t="s">
+        <v>471</v>
+      </c>
+      <c r="F311" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="G311" s="93" t="s">
+        <v>473</v>
+      </c>
+      <c r="H311" s="90" t="s">
+        <v>464</v>
+      </c>
+      <c r="I311" s="90" t="s">
+        <v>465</v>
+      </c>
+      <c r="J311" s="90" t="s">
+        <v>466</v>
+      </c>
+      <c r="K311" s="90" t="s">
+        <v>468</v>
+      </c>
       <c r="L311" s="10"/>
     </row>
     <row r="312" spans="1:12" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14639,11 +14705,17 @@
         <v>2</v>
       </c>
       <c r="F314" s="22"/>
-      <c r="G314" s="23"/>
-      <c r="H314" s="23"/>
-      <c r="I314" s="23"/>
-      <c r="J314" s="23"/>
-      <c r="K314" s="23"/>
+      <c r="G314" s="11"/>
+      <c r="H314" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I314" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J314" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K314" s="11"/>
       <c r="L314" s="22"/>
     </row>
     <row r="315" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -14656,11 +14728,17 @@
         <v>2</v>
       </c>
       <c r="F315" s="22"/>
-      <c r="G315" s="23"/>
-      <c r="H315" s="23"/>
-      <c r="I315" s="23"/>
-      <c r="J315" s="23"/>
-      <c r="K315" s="23"/>
+      <c r="G315" s="11"/>
+      <c r="H315" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I315" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J315" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K315" s="11"/>
       <c r="L315" s="22"/>
     </row>
     <row r="316" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -14673,11 +14751,17 @@
         <v>2</v>
       </c>
       <c r="F316" s="22"/>
-      <c r="G316" s="23"/>
-      <c r="H316" s="23"/>
-      <c r="I316" s="23"/>
-      <c r="J316" s="23"/>
-      <c r="K316" s="23"/>
+      <c r="G316" s="11"/>
+      <c r="H316" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I316" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J316" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K316" s="11"/>
       <c r="L316" s="22"/>
     </row>
     <row r="317" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14691,11 +14775,17 @@
         <v>1</v>
       </c>
       <c r="F317" s="22"/>
-      <c r="G317" s="23"/>
-      <c r="H317" s="23"/>
-      <c r="I317" s="23"/>
-      <c r="J317" s="23"/>
-      <c r="K317" s="23"/>
+      <c r="G317" s="11"/>
+      <c r="H317" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I317" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J317" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K317" s="11"/>
       <c r="L317" s="22"/>
     </row>
     <row r="318" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14709,11 +14799,17 @@
         <v>1</v>
       </c>
       <c r="F318" s="22"/>
-      <c r="G318" s="23"/>
-      <c r="H318" s="23"/>
-      <c r="I318" s="23"/>
-      <c r="J318" s="23"/>
-      <c r="K318" s="23"/>
+      <c r="G318" s="11"/>
+      <c r="H318" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I318" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J318" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K318" s="11"/>
       <c r="L318" s="22"/>
     </row>
     <row r="319" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14727,11 +14823,17 @@
         <v>2</v>
       </c>
       <c r="F319" s="22"/>
-      <c r="G319" s="23"/>
-      <c r="H319" s="23"/>
-      <c r="I319" s="23"/>
-      <c r="J319" s="23"/>
-      <c r="K319" s="23"/>
+      <c r="G319" s="11"/>
+      <c r="H319" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I319" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J319" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K319" s="11"/>
       <c r="L319" s="22"/>
     </row>
     <row r="320" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14745,11 +14847,17 @@
         <v>1</v>
       </c>
       <c r="F320" s="22"/>
-      <c r="G320" s="23"/>
-      <c r="H320" s="23"/>
-      <c r="I320" s="23"/>
-      <c r="J320" s="23"/>
-      <c r="K320" s="23"/>
+      <c r="G320" s="11"/>
+      <c r="H320" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I320" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J320" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K320" s="11"/>
       <c r="L320" s="22"/>
     </row>
     <row r="321" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14763,11 +14871,17 @@
       </c>
       <c r="E321" s="21"/>
       <c r="F321" s="22"/>
-      <c r="G321" s="23"/>
-      <c r="H321" s="23"/>
-      <c r="I321" s="23"/>
-      <c r="J321" s="23"/>
-      <c r="K321" s="23"/>
+      <c r="G321" s="11"/>
+      <c r="H321" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I321" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J321" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K321" s="11"/>
       <c r="L321" s="22"/>
     </row>
     <row r="322" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14781,11 +14895,17 @@
       <c r="D322" s="20"/>
       <c r="E322" s="21"/>
       <c r="F322" s="22"/>
-      <c r="G322" s="23"/>
-      <c r="H322" s="23"/>
-      <c r="I322" s="23"/>
-      <c r="J322" s="23"/>
-      <c r="K322" s="23"/>
+      <c r="G322" s="11"/>
+      <c r="H322" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I322" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J322" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K322" s="11"/>
       <c r="L322" s="22"/>
     </row>
     <row r="323" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14799,11 +14919,17 @@
       <c r="D323" s="20"/>
       <c r="E323" s="21"/>
       <c r="F323" s="22"/>
-      <c r="G323" s="23"/>
-      <c r="H323" s="23"/>
-      <c r="I323" s="23"/>
-      <c r="J323" s="23"/>
-      <c r="K323" s="23"/>
+      <c r="G323" s="11"/>
+      <c r="H323" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I323" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J323" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K323" s="11"/>
       <c r="L323" s="22"/>
     </row>
     <row r="324" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14817,11 +14943,17 @@
       <c r="D324" s="20"/>
       <c r="E324" s="21"/>
       <c r="F324" s="22"/>
-      <c r="G324" s="23"/>
-      <c r="H324" s="23"/>
-      <c r="I324" s="23"/>
-      <c r="J324" s="23"/>
-      <c r="K324" s="23"/>
+      <c r="G324" s="11"/>
+      <c r="H324" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I324" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J324" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K324" s="11"/>
       <c r="L324" s="22"/>
     </row>
     <row r="325" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14835,11 +14967,17 @@
       <c r="D325" s="20"/>
       <c r="E325" s="21"/>
       <c r="F325" s="22"/>
-      <c r="G325" s="23"/>
-      <c r="H325" s="23"/>
-      <c r="I325" s="23"/>
-      <c r="J325" s="23"/>
-      <c r="K325" s="23"/>
+      <c r="G325" s="11"/>
+      <c r="H325" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I325" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J325" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K325" s="11"/>
       <c r="L325" s="22"/>
     </row>
     <row r="326" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14855,11 +14993,17 @@
       <c r="F326" s="22">
         <v>1</v>
       </c>
-      <c r="G326" s="23"/>
-      <c r="H326" s="23"/>
-      <c r="I326" s="23"/>
-      <c r="J326" s="23"/>
-      <c r="K326" s="23"/>
+      <c r="G326" s="11"/>
+      <c r="H326" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I326" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J326" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K326" s="11"/>
       <c r="L326" s="22"/>
     </row>
     <row r="327" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14873,11 +15017,17 @@
         <v>1</v>
       </c>
       <c r="F327" s="22"/>
-      <c r="G327" s="23"/>
-      <c r="H327" s="23"/>
-      <c r="I327" s="23"/>
-      <c r="J327" s="23"/>
-      <c r="K327" s="23"/>
+      <c r="G327" s="11"/>
+      <c r="H327" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I327" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J327" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K327" s="11"/>
       <c r="L327" s="22"/>
     </row>
     <row r="328" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14891,11 +15041,17 @@
         <v>1</v>
       </c>
       <c r="F328" s="22"/>
-      <c r="G328" s="23"/>
-      <c r="H328" s="23"/>
-      <c r="I328" s="23"/>
-      <c r="J328" s="23"/>
-      <c r="K328" s="23"/>
+      <c r="G328" s="11"/>
+      <c r="H328" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I328" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J328" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K328" s="11"/>
       <c r="L328" s="22"/>
     </row>
     <row r="329" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14909,11 +15065,17 @@
         <v>1</v>
       </c>
       <c r="F329" s="22"/>
-      <c r="G329" s="23"/>
-      <c r="H329" s="23"/>
-      <c r="I329" s="23"/>
-      <c r="J329" s="23"/>
-      <c r="K329" s="23"/>
+      <c r="G329" s="11"/>
+      <c r="H329" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I329" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J329" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K329" s="11"/>
       <c r="L329" s="22"/>
     </row>
     <row r="330" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14921,7 +15083,6 @@
       <c r="B330" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="C330" s="19"/>
       <c r="D330" s="20">
         <v>1</v>
       </c>
@@ -14929,11 +15090,17 @@
       <c r="F330" s="64">
         <v>1</v>
       </c>
-      <c r="G330" s="23"/>
-      <c r="H330" s="23"/>
-      <c r="I330" s="23"/>
-      <c r="J330" s="23"/>
-      <c r="K330" s="23"/>
+      <c r="G330" s="11"/>
+      <c r="H330" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I330" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J330" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K330" s="11"/>
       <c r="L330" s="64"/>
     </row>
     <row r="331" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14947,11 +15114,17 @@
       <c r="D331" s="20"/>
       <c r="E331" s="21"/>
       <c r="F331" s="64"/>
-      <c r="G331" s="23"/>
-      <c r="H331" s="23"/>
-      <c r="I331" s="23"/>
-      <c r="J331" s="23"/>
-      <c r="K331" s="23"/>
+      <c r="G331" s="11"/>
+      <c r="H331" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I331" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J331" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K331" s="11"/>
       <c r="L331" s="64"/>
     </row>
     <row r="332" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14965,11 +15138,17 @@
       <c r="D332" s="20"/>
       <c r="E332" s="21"/>
       <c r="F332" s="64"/>
-      <c r="G332" s="23"/>
-      <c r="H332" s="23"/>
-      <c r="I332" s="23"/>
-      <c r="J332" s="23"/>
-      <c r="K332" s="23"/>
+      <c r="G332" s="11"/>
+      <c r="H332" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I332" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J332" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K332" s="11"/>
       <c r="L332" s="64"/>
     </row>
     <row r="333" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14983,11 +15162,17 @@
       <c r="D333" s="20"/>
       <c r="E333" s="21"/>
       <c r="F333" s="64"/>
-      <c r="G333" s="23"/>
-      <c r="H333" s="23"/>
-      <c r="I333" s="23"/>
-      <c r="J333" s="23"/>
-      <c r="K333" s="23"/>
+      <c r="G333" s="11"/>
+      <c r="H333" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I333" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J333" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K333" s="11"/>
       <c r="L333" s="64"/>
     </row>
     <row r="334" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15003,11 +15188,17 @@
       <c r="F334" s="64">
         <v>1</v>
       </c>
-      <c r="G334" s="23"/>
-      <c r="H334" s="23"/>
-      <c r="I334" s="23"/>
-      <c r="J334" s="23"/>
-      <c r="K334" s="23"/>
+      <c r="G334" s="11"/>
+      <c r="H334" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I334" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J334" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K334" s="11"/>
       <c r="L334" s="64"/>
     </row>
     <row r="335" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15021,11 +15212,17 @@
       <c r="D335" s="20"/>
       <c r="E335" s="21"/>
       <c r="F335" s="22"/>
-      <c r="G335" s="23"/>
-      <c r="H335" s="23"/>
-      <c r="I335" s="23"/>
-      <c r="J335" s="23"/>
-      <c r="K335" s="23"/>
+      <c r="G335" s="11"/>
+      <c r="H335" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I335" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J335" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K335" s="11"/>
       <c r="L335" s="22"/>
     </row>
     <row r="336" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15039,11 +15236,17 @@
       <c r="D336" s="20"/>
       <c r="E336" s="21"/>
       <c r="F336" s="22"/>
-      <c r="G336" s="23"/>
-      <c r="H336" s="23"/>
-      <c r="I336" s="23"/>
-      <c r="J336" s="23"/>
-      <c r="K336" s="23"/>
+      <c r="G336" s="11"/>
+      <c r="H336" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I336" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J336" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K336" s="11"/>
       <c r="L336" s="22"/>
     </row>
     <row r="337" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15057,27 +15260,31 @@
       <c r="D337" s="20"/>
       <c r="E337" s="21"/>
       <c r="F337" s="22"/>
-      <c r="G337" s="23"/>
-      <c r="H337" s="23"/>
-      <c r="I337" s="23"/>
-      <c r="J337" s="23"/>
-      <c r="K337" s="23"/>
+      <c r="G337" s="11"/>
+      <c r="H337" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I337" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J337" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K337" s="11"/>
       <c r="L337" s="22"/>
     </row>
     <row r="338" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="16"/>
       <c r="B338" s="28"/>
-      <c r="C338" s="19">
-        <v>1</v>
-      </c>
+      <c r="C338" s="19"/>
       <c r="D338" s="20"/>
       <c r="E338" s="21"/>
       <c r="F338" s="22"/>
-      <c r="G338" s="23"/>
-      <c r="H338" s="23"/>
-      <c r="I338" s="23"/>
-      <c r="J338" s="23"/>
-      <c r="K338" s="23"/>
+      <c r="G338" s="11"/>
+      <c r="H338" s="11"/>
+      <c r="I338" s="11"/>
+      <c r="J338" s="11"/>
+      <c r="K338" s="11"/>
       <c r="L338" s="22"/>
     </row>
     <row r="339" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15125,13 +15332,19 @@
       <c r="D341" s="41"/>
       <c r="E341" s="42"/>
       <c r="F341" s="43"/>
-      <c r="G341" s="23">
-        <v>1</v>
-      </c>
-      <c r="H341" s="23"/>
-      <c r="I341" s="23"/>
-      <c r="J341" s="23"/>
-      <c r="K341" s="23"/>
+      <c r="G341" s="64">
+        <v>1</v>
+      </c>
+      <c r="H341" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I341" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J341" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K341" s="11"/>
       <c r="L341" s="43"/>
     </row>
     <row r="342" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -15144,11 +15357,17 @@
       <c r="D342" s="41"/>
       <c r="E342" s="42"/>
       <c r="F342" s="43"/>
-      <c r="G342" s="23"/>
-      <c r="H342" s="23"/>
-      <c r="I342" s="23"/>
-      <c r="J342" s="23"/>
-      <c r="K342" s="23"/>
+      <c r="G342" s="11"/>
+      <c r="H342" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I342" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J342" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K342" s="11"/>
       <c r="L342" s="43"/>
     </row>
     <row r="343" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15160,13 +15379,19 @@
       <c r="D343" s="41"/>
       <c r="E343" s="42"/>
       <c r="F343" s="43"/>
-      <c r="G343" s="23">
-        <v>1</v>
-      </c>
-      <c r="H343" s="23"/>
-      <c r="I343" s="23"/>
-      <c r="J343" s="23"/>
-      <c r="K343" s="23"/>
+      <c r="G343" s="64">
+        <v>1</v>
+      </c>
+      <c r="H343" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="I343" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="J343" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="K343" s="11"/>
       <c r="L343" s="43"/>
     </row>
     <row r="344" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15180,11 +15405,17 @@
       <c r="D344" s="41"/>
       <c r="E344" s="42"/>
       <c r="F344" s="43"/>
-      <c r="G344" s="23"/>
-      <c r="H344" s="23"/>
-      <c r="I344" s="23"/>
-      <c r="J344" s="23"/>
-      <c r="K344" s="23"/>
+      <c r="G344" s="11"/>
+      <c r="H344" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I344" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J344" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K344" s="11"/>
       <c r="L344" s="43"/>
     </row>
     <row r="345" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15194,11 +15425,11 @@
       <c r="D345" s="29"/>
       <c r="E345" s="30"/>
       <c r="F345" s="31"/>
-      <c r="G345" s="32"/>
-      <c r="H345" s="32"/>
-      <c r="I345" s="32"/>
-      <c r="J345" s="32"/>
-      <c r="K345" s="32"/>
+      <c r="G345" s="11"/>
+      <c r="H345" s="11"/>
+      <c r="I345" s="11"/>
+      <c r="J345" s="11"/>
+      <c r="K345" s="11"/>
       <c r="L345" s="31"/>
     </row>
     <row r="346" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15244,13 +15475,13 @@
       <c r="D348" s="41"/>
       <c r="E348" s="9"/>
       <c r="F348" s="43"/>
-      <c r="G348" s="23">
-        <v>1</v>
-      </c>
-      <c r="H348" s="23"/>
-      <c r="I348" s="23"/>
-      <c r="J348" s="23"/>
-      <c r="K348" s="23"/>
+      <c r="G348" s="64">
+        <v>1</v>
+      </c>
+      <c r="H348" s="11"/>
+      <c r="I348" s="11"/>
+      <c r="J348" s="11"/>
+      <c r="K348" s="11"/>
       <c r="L348" s="43"/>
     </row>
     <row r="349" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -15261,13 +15492,13 @@
       <c r="D349" s="41"/>
       <c r="E349" s="9"/>
       <c r="F349" s="43"/>
-      <c r="G349" s="23">
-        <v>1</v>
-      </c>
-      <c r="H349" s="23"/>
-      <c r="I349" s="23"/>
-      <c r="J349" s="23"/>
-      <c r="K349" s="23"/>
+      <c r="G349" s="64">
+        <v>1</v>
+      </c>
+      <c r="H349" s="11"/>
+      <c r="I349" s="11"/>
+      <c r="J349" s="11"/>
+      <c r="K349" s="11"/>
       <c r="L349" s="43"/>
     </row>
     <row r="350" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -15280,13 +15511,17 @@
       <c r="D350" s="41"/>
       <c r="E350" s="9"/>
       <c r="F350" s="43"/>
-      <c r="G350" s="23">
-        <v>1</v>
-      </c>
-      <c r="H350" s="23"/>
-      <c r="I350" s="23"/>
-      <c r="J350" s="23"/>
-      <c r="K350" s="23"/>
+      <c r="G350" s="11"/>
+      <c r="H350" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I350" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J350" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K350" s="11"/>
       <c r="L350" s="43"/>
     </row>
     <row r="351" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15300,11 +15535,17 @@
       <c r="D351" s="41"/>
       <c r="E351" s="42"/>
       <c r="F351" s="43"/>
-      <c r="G351" s="23"/>
-      <c r="H351" s="23"/>
-      <c r="I351" s="23"/>
-      <c r="J351" s="23"/>
-      <c r="K351" s="23"/>
+      <c r="G351" s="11"/>
+      <c r="H351" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I351" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J351" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K351" s="11"/>
       <c r="L351" s="43"/>
     </row>
     <row r="352" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15318,11 +15559,17 @@
       <c r="D352" s="41"/>
       <c r="E352" s="42"/>
       <c r="F352" s="43"/>
-      <c r="G352" s="23"/>
-      <c r="H352" s="23"/>
-      <c r="I352" s="23"/>
-      <c r="J352" s="23"/>
-      <c r="K352" s="23"/>
+      <c r="G352" s="11"/>
+      <c r="H352" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I352" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J352" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K352" s="11"/>
       <c r="L352" s="43"/>
     </row>
     <row r="353" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15332,24 +15579,24 @@
       <c r="D353" s="41"/>
       <c r="E353" s="42"/>
       <c r="F353" s="43"/>
-      <c r="G353" s="23"/>
-      <c r="H353" s="23"/>
-      <c r="I353" s="23"/>
-      <c r="J353" s="23"/>
-      <c r="K353" s="23"/>
+      <c r="G353" s="11"/>
+      <c r="H353" s="11"/>
+      <c r="I353" s="11"/>
+      <c r="J353" s="11"/>
+      <c r="K353" s="11"/>
       <c r="L353" s="43"/>
     </row>
     <row r="354" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A354" s="13">
-        <v>1</v>
-      </c>
-      <c r="B354" s="14" t="s">
+      <c r="A354" s="103">
+        <v>1</v>
+      </c>
+      <c r="B354" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="C354" s="7"/>
-      <c r="D354" s="8"/>
-      <c r="E354" s="9"/>
-      <c r="F354" s="10"/>
+      <c r="C354" s="105"/>
+      <c r="D354" s="106"/>
+      <c r="E354" s="107"/>
+      <c r="F354" s="108"/>
       <c r="G354" s="11"/>
       <c r="H354" s="11"/>
       <c r="I354" s="11"/>
@@ -15358,14 +15605,14 @@
       <c r="L354" s="10"/>
     </row>
     <row r="355" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="16"/>
-      <c r="B355" s="14" t="s">
+      <c r="A355" s="109"/>
+      <c r="B355" s="104" t="s">
         <v>122</v>
       </c>
-      <c r="C355" s="7"/>
-      <c r="D355" s="8"/>
-      <c r="E355" s="9"/>
-      <c r="F355" s="10"/>
+      <c r="C355" s="105"/>
+      <c r="D355" s="106"/>
+      <c r="E355" s="107"/>
+      <c r="F355" s="108"/>
       <c r="G355" s="11"/>
       <c r="H355" s="11"/>
       <c r="I355" s="11"/>
@@ -15374,39 +15621,53 @@
       <c r="L355" s="10"/>
     </row>
     <row r="356" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="17"/>
-      <c r="B356" s="38" t="s">
+      <c r="A356" s="110"/>
+      <c r="B356" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="C356" s="40">
-        <v>1</v>
-      </c>
-      <c r="D356" s="41"/>
-      <c r="E356" s="42"/>
-      <c r="F356" s="43"/>
-      <c r="G356" s="23"/>
-      <c r="H356" s="23"/>
-      <c r="I356" s="23"/>
-      <c r="J356" s="23"/>
-      <c r="K356" s="23"/>
-      <c r="L356" s="43"/>
+      <c r="C356" s="112">
+        <v>1</v>
+      </c>
+      <c r="D356" s="113"/>
+      <c r="E356" s="114"/>
+      <c r="F356" s="115"/>
+      <c r="G356" s="11"/>
+      <c r="H356" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="I356" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="J356" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="K356" s="11"/>
+      <c r="L356" s="43" t="s">
+        <v>477</v>
+      </c>
     </row>
     <row r="357" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A357" s="17"/>
-      <c r="B357" s="38" t="s">
+      <c r="A357" s="110"/>
+      <c r="B357" s="111" t="s">
         <v>27</v>
       </c>
-      <c r="C357" s="40">
-        <v>1</v>
-      </c>
-      <c r="D357" s="41"/>
-      <c r="E357" s="42"/>
-      <c r="F357" s="43"/>
-      <c r="G357" s="23"/>
-      <c r="H357" s="23"/>
-      <c r="I357" s="23"/>
-      <c r="J357" s="23"/>
-      <c r="K357" s="23"/>
+      <c r="C357" s="112">
+        <v>1</v>
+      </c>
+      <c r="D357" s="113"/>
+      <c r="E357" s="114"/>
+      <c r="F357" s="115"/>
+      <c r="G357" s="11"/>
+      <c r="H357" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="I357" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="J357" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="K357" s="11"/>
       <c r="L357" s="43"/>
     </row>
     <row r="358" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15416,11 +15677,11 @@
       <c r="D358" s="41"/>
       <c r="E358" s="42"/>
       <c r="F358" s="43"/>
-      <c r="G358" s="23"/>
-      <c r="H358" s="23"/>
-      <c r="I358" s="23"/>
-      <c r="J358" s="23"/>
-      <c r="K358" s="23"/>
+      <c r="G358" s="11"/>
+      <c r="H358" s="11"/>
+      <c r="I358" s="11"/>
+      <c r="J358" s="11"/>
+      <c r="K358" s="11"/>
       <c r="L358" s="43"/>
     </row>
     <row r="359" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15466,11 +15727,17 @@
       <c r="D361" s="41"/>
       <c r="E361" s="42"/>
       <c r="F361" s="43"/>
-      <c r="G361" s="23"/>
-      <c r="H361" s="23"/>
-      <c r="I361" s="23"/>
-      <c r="J361" s="23"/>
-      <c r="K361" s="23"/>
+      <c r="G361" s="11"/>
+      <c r="H361" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I361" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J361" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K361" s="11"/>
       <c r="L361" s="43"/>
     </row>
     <row r="362" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15484,11 +15751,17 @@
       <c r="D362" s="41"/>
       <c r="E362" s="42"/>
       <c r="F362" s="43"/>
-      <c r="G362" s="23"/>
-      <c r="H362" s="23"/>
-      <c r="I362" s="23"/>
-      <c r="J362" s="23"/>
-      <c r="K362" s="23"/>
+      <c r="G362" s="11"/>
+      <c r="H362" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I362" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J362" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K362" s="11"/>
       <c r="L362" s="43"/>
     </row>
     <row r="363" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15502,11 +15775,17 @@
       <c r="D363" s="41"/>
       <c r="E363" s="42"/>
       <c r="F363" s="43"/>
-      <c r="G363" s="23"/>
-      <c r="H363" s="23"/>
-      <c r="I363" s="23"/>
-      <c r="J363" s="23"/>
-      <c r="K363" s="23"/>
+      <c r="G363" s="11"/>
+      <c r="H363" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I363" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J363" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K363" s="11"/>
       <c r="L363" s="43"/>
     </row>
     <row r="364" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15516,11 +15795,11 @@
       <c r="D364" s="29"/>
       <c r="E364" s="30"/>
       <c r="F364" s="31"/>
-      <c r="G364" s="32"/>
-      <c r="H364" s="32"/>
-      <c r="I364" s="32"/>
-      <c r="J364" s="32"/>
-      <c r="K364" s="32"/>
+      <c r="G364" s="11"/>
+      <c r="H364" s="11"/>
+      <c r="I364" s="11"/>
+      <c r="J364" s="11"/>
+      <c r="K364" s="11"/>
       <c r="L364" s="31"/>
     </row>
     <row r="365" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15530,7 +15809,7 @@
       </c>
       <c r="C365" s="46">
         <f>SUM(C314:C364)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D365" s="46">
         <f>SUM(D314:D364)</f>
@@ -15546,7 +15825,7 @@
       </c>
       <c r="G365" s="46">
         <f>SUM(G314:G352)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H365" s="46"/>
       <c r="I365" s="46"/>
@@ -15575,42 +15854,51 @@
       <c r="B367" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C367" s="90" t="s">
+      <c r="C367" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D367" s="90"/>
-      <c r="E367" s="90"/>
-      <c r="F367" s="90"/>
-      <c r="G367" s="90"/>
-      <c r="H367" s="95"/>
-      <c r="I367" s="95"/>
-      <c r="J367" s="95"/>
-      <c r="K367" s="95"/>
+      <c r="D367" s="98"/>
+      <c r="E367" s="98"/>
+      <c r="F367" s="98"/>
+      <c r="G367" s="98"/>
+      <c r="H367" s="89"/>
+      <c r="I367" s="89"/>
+      <c r="J367" s="89"/>
+      <c r="K367" s="89"/>
+      <c r="L367" s="89"/>
     </row>
     <row r="368" spans="1:12" s="24" customFormat="1" ht="117.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C368" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D368" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E368" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F368" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G368" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="H368" s="11"/>
-      <c r="I368" s="11"/>
-      <c r="J368" s="11"/>
-      <c r="K368" s="11"/>
+      <c r="C368" s="92" t="s">
+        <v>469</v>
+      </c>
+      <c r="D368" s="41" t="s">
+        <v>470</v>
+      </c>
+      <c r="E368" s="42" t="s">
+        <v>471</v>
+      </c>
+      <c r="F368" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="G368" s="93" t="s">
+        <v>473</v>
+      </c>
+      <c r="H368" s="90" t="s">
+        <v>464</v>
+      </c>
+      <c r="I368" s="90" t="s">
+        <v>465</v>
+      </c>
+      <c r="J368" s="90" t="s">
+        <v>466</v>
+      </c>
+      <c r="K368" s="90" t="s">
+        <v>468</v>
+      </c>
       <c r="L368" s="10"/>
     </row>
     <row r="369" spans="1:12" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15658,11 +15946,17 @@
         <v>2</v>
       </c>
       <c r="F371" s="22"/>
-      <c r="G371" s="23"/>
-      <c r="H371" s="23"/>
-      <c r="I371" s="23"/>
-      <c r="J371" s="23"/>
-      <c r="K371" s="23"/>
+      <c r="G371" s="11"/>
+      <c r="H371" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I371" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J371" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K371" s="11"/>
       <c r="L371" s="22"/>
     </row>
     <row r="372" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -15675,11 +15969,17 @@
         <v>2</v>
       </c>
       <c r="F372" s="22"/>
-      <c r="G372" s="23"/>
-      <c r="H372" s="23"/>
-      <c r="I372" s="23"/>
-      <c r="J372" s="23"/>
-      <c r="K372" s="23"/>
+      <c r="G372" s="11"/>
+      <c r="H372" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I372" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J372" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K372" s="11"/>
       <c r="L372" s="22"/>
     </row>
     <row r="373" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -15692,11 +15992,17 @@
         <v>2</v>
       </c>
       <c r="F373" s="22"/>
-      <c r="G373" s="23"/>
-      <c r="H373" s="23"/>
-      <c r="I373" s="23"/>
-      <c r="J373" s="23"/>
-      <c r="K373" s="23"/>
+      <c r="G373" s="11"/>
+      <c r="H373" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I373" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J373" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K373" s="11"/>
       <c r="L373" s="22"/>
     </row>
     <row r="374" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15710,11 +16016,17 @@
         <v>2</v>
       </c>
       <c r="F374" s="22"/>
-      <c r="G374" s="23"/>
-      <c r="H374" s="23"/>
-      <c r="I374" s="23"/>
-      <c r="J374" s="23"/>
-      <c r="K374" s="23"/>
+      <c r="G374" s="11"/>
+      <c r="H374" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I374" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J374" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K374" s="11"/>
       <c r="L374" s="22"/>
     </row>
     <row r="375" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15728,11 +16040,17 @@
         <v>2</v>
       </c>
       <c r="F375" s="22"/>
-      <c r="G375" s="23"/>
-      <c r="H375" s="23"/>
-      <c r="I375" s="23"/>
-      <c r="J375" s="23"/>
-      <c r="K375" s="23"/>
+      <c r="G375" s="11"/>
+      <c r="H375" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I375" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J375" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K375" s="11"/>
       <c r="L375" s="22"/>
     </row>
     <row r="376" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15746,11 +16064,17 @@
         <v>1</v>
       </c>
       <c r="F376" s="22"/>
-      <c r="G376" s="23"/>
-      <c r="H376" s="23"/>
-      <c r="I376" s="23"/>
-      <c r="J376" s="23"/>
-      <c r="K376" s="23"/>
+      <c r="G376" s="11"/>
+      <c r="H376" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I376" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J376" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K376" s="11"/>
       <c r="L376" s="22"/>
     </row>
     <row r="377" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15764,11 +16088,17 @@
       </c>
       <c r="E377" s="21"/>
       <c r="F377" s="22"/>
-      <c r="G377" s="23"/>
-      <c r="H377" s="23"/>
-      <c r="I377" s="23"/>
-      <c r="J377" s="23"/>
-      <c r="K377" s="23"/>
+      <c r="G377" s="11"/>
+      <c r="H377" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I377" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J377" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K377" s="11"/>
       <c r="L377" s="22"/>
     </row>
     <row r="378" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15782,11 +16112,17 @@
       <c r="D378" s="20"/>
       <c r="E378" s="21"/>
       <c r="F378" s="22"/>
-      <c r="G378" s="23"/>
-      <c r="H378" s="23"/>
-      <c r="I378" s="23"/>
-      <c r="J378" s="23"/>
-      <c r="K378" s="23"/>
+      <c r="G378" s="11"/>
+      <c r="H378" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I378" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J378" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K378" s="11"/>
       <c r="L378" s="22"/>
     </row>
     <row r="379" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15800,11 +16136,17 @@
       <c r="D379" s="20"/>
       <c r="E379" s="21"/>
       <c r="F379" s="22"/>
-      <c r="G379" s="23"/>
-      <c r="H379" s="23"/>
-      <c r="I379" s="23"/>
-      <c r="J379" s="23"/>
-      <c r="K379" s="23"/>
+      <c r="G379" s="11"/>
+      <c r="H379" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I379" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J379" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K379" s="11"/>
       <c r="L379" s="22"/>
     </row>
     <row r="380" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15818,11 +16160,17 @@
       <c r="D380" s="20"/>
       <c r="E380" s="21"/>
       <c r="F380" s="22"/>
-      <c r="G380" s="23"/>
-      <c r="H380" s="23"/>
-      <c r="I380" s="23"/>
-      <c r="J380" s="23"/>
-      <c r="K380" s="23"/>
+      <c r="G380" s="11"/>
+      <c r="H380" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I380" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J380" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K380" s="11"/>
       <c r="L380" s="22"/>
     </row>
     <row r="381" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15836,11 +16184,17 @@
       <c r="D381" s="20"/>
       <c r="E381" s="21"/>
       <c r="F381" s="22"/>
-      <c r="G381" s="23"/>
-      <c r="H381" s="23"/>
-      <c r="I381" s="23"/>
-      <c r="J381" s="23"/>
-      <c r="K381" s="23"/>
+      <c r="G381" s="11"/>
+      <c r="H381" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I381" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J381" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K381" s="11"/>
       <c r="L381" s="22"/>
     </row>
     <row r="382" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15854,11 +16208,17 @@
       <c r="D382" s="20"/>
       <c r="E382" s="21"/>
       <c r="F382" s="22"/>
-      <c r="G382" s="23"/>
-      <c r="H382" s="23"/>
-      <c r="I382" s="23"/>
-      <c r="J382" s="23"/>
-      <c r="K382" s="23"/>
+      <c r="G382" s="11"/>
+      <c r="H382" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I382" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J382" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K382" s="11"/>
       <c r="L382" s="22"/>
     </row>
     <row r="383" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15874,11 +16234,17 @@
       <c r="F383" s="22">
         <v>1</v>
       </c>
-      <c r="G383" s="23"/>
-      <c r="H383" s="23"/>
-      <c r="I383" s="23"/>
-      <c r="J383" s="23"/>
-      <c r="K383" s="23"/>
+      <c r="G383" s="11"/>
+      <c r="H383" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I383" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J383" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K383" s="11"/>
       <c r="L383" s="22"/>
     </row>
     <row r="384" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15892,11 +16258,17 @@
         <v>1</v>
       </c>
       <c r="F384" s="22"/>
-      <c r="G384" s="23"/>
-      <c r="H384" s="23"/>
-      <c r="I384" s="23"/>
-      <c r="J384" s="23"/>
-      <c r="K384" s="23"/>
+      <c r="G384" s="11"/>
+      <c r="H384" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I384" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J384" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K384" s="11"/>
       <c r="L384" s="22"/>
     </row>
     <row r="385" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15910,11 +16282,17 @@
         <v>1</v>
       </c>
       <c r="F385" s="22"/>
-      <c r="G385" s="23"/>
-      <c r="H385" s="23"/>
-      <c r="I385" s="23"/>
-      <c r="J385" s="23"/>
-      <c r="K385" s="23"/>
+      <c r="G385" s="11"/>
+      <c r="H385" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I385" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J385" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K385" s="11"/>
       <c r="L385" s="22"/>
     </row>
     <row r="386" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15928,11 +16306,17 @@
         <v>1</v>
       </c>
       <c r="F386" s="22"/>
-      <c r="G386" s="23"/>
-      <c r="H386" s="23"/>
-      <c r="I386" s="23"/>
-      <c r="J386" s="23"/>
-      <c r="K386" s="23"/>
+      <c r="G386" s="11"/>
+      <c r="H386" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I386" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J386" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K386" s="11"/>
       <c r="L386" s="22"/>
     </row>
     <row r="387" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15948,11 +16332,17 @@
       <c r="F387" s="64">
         <v>1</v>
       </c>
-      <c r="G387" s="23"/>
-      <c r="H387" s="23"/>
-      <c r="I387" s="23"/>
-      <c r="J387" s="23"/>
-      <c r="K387" s="23"/>
+      <c r="G387" s="11"/>
+      <c r="H387" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I387" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J387" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K387" s="11"/>
       <c r="L387" s="64"/>
     </row>
     <row r="388" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15966,11 +16356,17 @@
       <c r="D388" s="20"/>
       <c r="E388" s="21"/>
       <c r="F388" s="64"/>
-      <c r="G388" s="23"/>
-      <c r="H388" s="23"/>
-      <c r="I388" s="23"/>
-      <c r="J388" s="23"/>
-      <c r="K388" s="23"/>
+      <c r="G388" s="11"/>
+      <c r="H388" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I388" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J388" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K388" s="11"/>
       <c r="L388" s="64"/>
     </row>
     <row r="389" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15984,11 +16380,17 @@
       <c r="D389" s="20"/>
       <c r="E389" s="21"/>
       <c r="F389" s="64"/>
-      <c r="G389" s="23"/>
-      <c r="H389" s="23"/>
-      <c r="I389" s="23"/>
-      <c r="J389" s="23"/>
-      <c r="K389" s="23"/>
+      <c r="G389" s="11"/>
+      <c r="H389" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I389" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J389" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K389" s="11"/>
       <c r="L389" s="64"/>
     </row>
     <row r="390" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16002,11 +16404,17 @@
       <c r="D390" s="20"/>
       <c r="E390" s="21"/>
       <c r="F390" s="64"/>
-      <c r="G390" s="23"/>
-      <c r="H390" s="23"/>
-      <c r="I390" s="23"/>
-      <c r="J390" s="23"/>
-      <c r="K390" s="23"/>
+      <c r="G390" s="11"/>
+      <c r="H390" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I390" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J390" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K390" s="11"/>
       <c r="L390" s="64"/>
     </row>
     <row r="391" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16022,11 +16430,17 @@
       <c r="F391" s="64">
         <v>1</v>
       </c>
-      <c r="G391" s="23"/>
-      <c r="H391" s="23"/>
-      <c r="I391" s="23"/>
-      <c r="J391" s="23"/>
-      <c r="K391" s="23"/>
+      <c r="G391" s="11"/>
+      <c r="H391" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I391" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J391" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K391" s="11"/>
       <c r="L391" s="64"/>
     </row>
     <row r="392" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16040,11 +16454,17 @@
       <c r="D392" s="20"/>
       <c r="E392" s="21"/>
       <c r="F392" s="22"/>
-      <c r="G392" s="23"/>
-      <c r="H392" s="23"/>
-      <c r="I392" s="23"/>
-      <c r="J392" s="23"/>
-      <c r="K392" s="23"/>
+      <c r="G392" s="11"/>
+      <c r="H392" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I392" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J392" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K392" s="11"/>
       <c r="L392" s="22"/>
     </row>
     <row r="393" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16058,11 +16478,17 @@
       <c r="D393" s="20"/>
       <c r="E393" s="21"/>
       <c r="F393" s="22"/>
-      <c r="G393" s="23"/>
-      <c r="H393" s="23"/>
-      <c r="I393" s="23"/>
-      <c r="J393" s="23"/>
-      <c r="K393" s="23"/>
+      <c r="G393" s="11"/>
+      <c r="H393" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I393" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J393" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K393" s="11"/>
       <c r="L393" s="22"/>
     </row>
     <row r="394" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16076,11 +16502,17 @@
       <c r="D394" s="20"/>
       <c r="E394" s="21"/>
       <c r="F394" s="22"/>
-      <c r="G394" s="23"/>
-      <c r="H394" s="23"/>
-      <c r="I394" s="23"/>
-      <c r="J394" s="23"/>
-      <c r="K394" s="23"/>
+      <c r="G394" s="11"/>
+      <c r="H394" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I394" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J394" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K394" s="11"/>
       <c r="L394" s="22"/>
     </row>
     <row r="395" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16090,7 +16522,7 @@
       <c r="D395" s="29"/>
       <c r="E395" s="30"/>
       <c r="F395" s="31"/>
-      <c r="G395" s="32"/>
+      <c r="G395" s="11"/>
       <c r="H395" s="32"/>
       <c r="I395" s="32"/>
       <c r="J395" s="32"/>
@@ -16142,11 +16574,17 @@
         <v>2</v>
       </c>
       <c r="F398" s="22"/>
-      <c r="G398" s="23"/>
-      <c r="H398" s="23"/>
-      <c r="I398" s="23"/>
-      <c r="J398" s="23"/>
-      <c r="K398" s="23"/>
+      <c r="G398" s="11"/>
+      <c r="H398" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I398" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J398" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K398" s="11"/>
       <c r="L398" s="22"/>
     </row>
     <row r="399" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -16159,11 +16597,17 @@
         <v>2</v>
       </c>
       <c r="F399" s="22"/>
-      <c r="G399" s="23"/>
-      <c r="H399" s="23"/>
-      <c r="I399" s="23"/>
-      <c r="J399" s="23"/>
-      <c r="K399" s="23"/>
+      <c r="G399" s="11"/>
+      <c r="H399" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I399" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J399" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K399" s="11"/>
       <c r="L399" s="22"/>
     </row>
     <row r="400" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -16176,11 +16620,17 @@
         <v>2</v>
       </c>
       <c r="F400" s="22"/>
-      <c r="G400" s="23"/>
-      <c r="H400" s="23"/>
-      <c r="I400" s="23"/>
-      <c r="J400" s="23"/>
-      <c r="K400" s="23"/>
+      <c r="G400" s="11"/>
+      <c r="H400" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I400" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J400" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K400" s="11"/>
       <c r="L400" s="22"/>
     </row>
     <row r="401" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16194,11 +16644,17 @@
         <v>2</v>
       </c>
       <c r="F401" s="22"/>
-      <c r="G401" s="23"/>
-      <c r="H401" s="23"/>
-      <c r="I401" s="23"/>
-      <c r="J401" s="23"/>
-      <c r="K401" s="23"/>
+      <c r="G401" s="11"/>
+      <c r="H401" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I401" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J401" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K401" s="11"/>
       <c r="L401" s="22"/>
     </row>
     <row r="402" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16212,11 +16668,17 @@
         <v>2</v>
       </c>
       <c r="F402" s="22"/>
-      <c r="G402" s="23"/>
-      <c r="H402" s="23"/>
-      <c r="I402" s="23"/>
-      <c r="J402" s="23"/>
-      <c r="K402" s="23"/>
+      <c r="G402" s="11"/>
+      <c r="H402" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I402" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J402" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K402" s="11"/>
       <c r="L402" s="22"/>
     </row>
     <row r="403" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16230,11 +16692,17 @@
         <v>1</v>
       </c>
       <c r="F403" s="22"/>
-      <c r="G403" s="23"/>
-      <c r="H403" s="23"/>
-      <c r="I403" s="23"/>
-      <c r="J403" s="23"/>
-      <c r="K403" s="23"/>
+      <c r="G403" s="11"/>
+      <c r="H403" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I403" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J403" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K403" s="11"/>
       <c r="L403" s="22"/>
     </row>
     <row r="404" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16248,11 +16716,17 @@
       </c>
       <c r="E404" s="21"/>
       <c r="F404" s="22"/>
-      <c r="G404" s="23"/>
-      <c r="H404" s="23"/>
-      <c r="I404" s="23"/>
-      <c r="J404" s="23"/>
-      <c r="K404" s="23"/>
+      <c r="G404" s="11"/>
+      <c r="H404" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I404" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J404" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K404" s="11"/>
       <c r="L404" s="22"/>
     </row>
     <row r="405" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16266,11 +16740,17 @@
       <c r="D405" s="20"/>
       <c r="E405" s="21"/>
       <c r="F405" s="22"/>
-      <c r="G405" s="23"/>
-      <c r="H405" s="23"/>
-      <c r="I405" s="23"/>
-      <c r="J405" s="23"/>
-      <c r="K405" s="23"/>
+      <c r="G405" s="11"/>
+      <c r="H405" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I405" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J405" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K405" s="11"/>
       <c r="L405" s="22"/>
     </row>
     <row r="406" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16284,11 +16764,17 @@
       <c r="D406" s="20"/>
       <c r="E406" s="21"/>
       <c r="F406" s="22"/>
-      <c r="G406" s="23"/>
-      <c r="H406" s="23"/>
-      <c r="I406" s="23"/>
-      <c r="J406" s="23"/>
-      <c r="K406" s="23"/>
+      <c r="G406" s="11"/>
+      <c r="H406" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I406" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J406" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K406" s="11"/>
       <c r="L406" s="22"/>
     </row>
     <row r="407" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16302,11 +16788,17 @@
       <c r="D407" s="20"/>
       <c r="E407" s="21"/>
       <c r="F407" s="22"/>
-      <c r="G407" s="23"/>
-      <c r="H407" s="23"/>
-      <c r="I407" s="23"/>
-      <c r="J407" s="23"/>
-      <c r="K407" s="23"/>
+      <c r="G407" s="11"/>
+      <c r="H407" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I407" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J407" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K407" s="11"/>
       <c r="L407" s="22"/>
     </row>
     <row r="408" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16320,11 +16812,17 @@
       <c r="D408" s="20"/>
       <c r="E408" s="21"/>
       <c r="F408" s="22"/>
-      <c r="G408" s="23"/>
-      <c r="H408" s="23"/>
-      <c r="I408" s="23"/>
-      <c r="J408" s="23"/>
-      <c r="K408" s="23"/>
+      <c r="G408" s="11"/>
+      <c r="H408" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I408" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J408" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K408" s="11"/>
       <c r="L408" s="22"/>
     </row>
     <row r="409" spans="1:12" s="33" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16338,11 +16836,17 @@
       <c r="D409" s="20"/>
       <c r="E409" s="21"/>
       <c r="F409" s="22"/>
-      <c r="G409" s="23"/>
-      <c r="H409" s="23"/>
-      <c r="I409" s="23"/>
-      <c r="J409" s="23"/>
-      <c r="K409" s="23"/>
+      <c r="G409" s="11"/>
+      <c r="H409" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I409" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J409" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K409" s="11"/>
       <c r="L409" s="22"/>
     </row>
     <row r="410" spans="1:12" s="24" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16358,11 +16862,17 @@
       <c r="F410" s="22">
         <v>1</v>
       </c>
-      <c r="G410" s="23"/>
-      <c r="H410" s="23"/>
-      <c r="I410" s="23"/>
-      <c r="J410" s="23"/>
-      <c r="K410" s="23"/>
+      <c r="G410" s="11"/>
+      <c r="H410" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I410" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J410" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K410" s="11"/>
       <c r="L410" s="22"/>
     </row>
     <row r="411" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16376,11 +16886,17 @@
         <v>1</v>
       </c>
       <c r="F411" s="22"/>
-      <c r="G411" s="23"/>
-      <c r="H411" s="23"/>
-      <c r="I411" s="23"/>
-      <c r="J411" s="23"/>
-      <c r="K411" s="23"/>
+      <c r="G411" s="11"/>
+      <c r="H411" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I411" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J411" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K411" s="11"/>
       <c r="L411" s="22"/>
     </row>
     <row r="412" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16394,11 +16910,17 @@
         <v>1</v>
       </c>
       <c r="F412" s="22"/>
-      <c r="G412" s="23"/>
-      <c r="H412" s="23"/>
-      <c r="I412" s="23"/>
-      <c r="J412" s="23"/>
-      <c r="K412" s="23"/>
+      <c r="G412" s="11"/>
+      <c r="H412" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I412" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J412" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K412" s="11"/>
       <c r="L412" s="22"/>
     </row>
     <row r="413" spans="1:12" s="12" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -16412,11 +16934,17 @@
         <v>1</v>
       </c>
       <c r="F413" s="22"/>
-      <c r="G413" s="23"/>
-      <c r="H413" s="23"/>
-      <c r="I413" s="23"/>
-      <c r="J413" s="23"/>
-      <c r="K413" s="23"/>
+      <c r="G413" s="11"/>
+      <c r="H413" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I413" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J413" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K413" s="11"/>
       <c r="L413" s="22"/>
     </row>
     <row r="414" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -16431,11 +16959,17 @@
       <c r="F414" s="64">
         <v>1</v>
       </c>
-      <c r="G414" s="23"/>
-      <c r="H414" s="23"/>
-      <c r="I414" s="23"/>
-      <c r="J414" s="23"/>
-      <c r="K414" s="23"/>
+      <c r="G414" s="11"/>
+      <c r="H414" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I414" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J414" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K414" s="11"/>
       <c r="L414" s="64"/>
     </row>
     <row r="415" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -16448,11 +16982,17 @@
       <c r="D415" s="20"/>
       <c r="E415" s="21"/>
       <c r="F415" s="64"/>
-      <c r="G415" s="23"/>
-      <c r="H415" s="23"/>
-      <c r="I415" s="23"/>
-      <c r="J415" s="23"/>
-      <c r="K415" s="23"/>
+      <c r="G415" s="11"/>
+      <c r="H415" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I415" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J415" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K415" s="11"/>
       <c r="L415" s="64"/>
     </row>
     <row r="416" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16466,11 +17006,17 @@
       <c r="D416" s="20"/>
       <c r="E416" s="21"/>
       <c r="F416" s="64"/>
-      <c r="G416" s="23"/>
-      <c r="H416" s="23"/>
-      <c r="I416" s="23"/>
-      <c r="J416" s="23"/>
-      <c r="K416" s="23"/>
+      <c r="G416" s="11"/>
+      <c r="H416" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I416" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J416" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K416" s="11"/>
       <c r="L416" s="64"/>
     </row>
     <row r="417" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16484,11 +17030,17 @@
       <c r="D417" s="20"/>
       <c r="E417" s="21"/>
       <c r="F417" s="64"/>
-      <c r="G417" s="23"/>
-      <c r="H417" s="23"/>
-      <c r="I417" s="23"/>
-      <c r="J417" s="23"/>
-      <c r="K417" s="23"/>
+      <c r="G417" s="11"/>
+      <c r="H417" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I417" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J417" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K417" s="11"/>
       <c r="L417" s="64"/>
     </row>
     <row r="418" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16504,11 +17056,17 @@
       <c r="F418" s="64">
         <v>1</v>
       </c>
-      <c r="G418" s="23"/>
-      <c r="H418" s="23"/>
-      <c r="I418" s="23"/>
-      <c r="J418" s="23"/>
-      <c r="K418" s="23"/>
+      <c r="G418" s="11"/>
+      <c r="H418" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I418" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J418" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K418" s="11"/>
       <c r="L418" s="64"/>
     </row>
     <row r="419" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16522,11 +17080,17 @@
       <c r="D419" s="20"/>
       <c r="E419" s="21"/>
       <c r="F419" s="22"/>
-      <c r="G419" s="23"/>
-      <c r="H419" s="23"/>
-      <c r="I419" s="23"/>
-      <c r="J419" s="23"/>
-      <c r="K419" s="23"/>
+      <c r="G419" s="11"/>
+      <c r="H419" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I419" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J419" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K419" s="11"/>
       <c r="L419" s="22"/>
     </row>
     <row r="420" spans="1:12" s="24" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -16540,11 +17104,17 @@
       <c r="D420" s="20"/>
       <c r="E420" s="21"/>
       <c r="F420" s="22"/>
-      <c r="G420" s="23"/>
-      <c r="H420" s="23"/>
-      <c r="I420" s="23"/>
-      <c r="J420" s="23"/>
-      <c r="K420" s="23"/>
+      <c r="G420" s="11"/>
+      <c r="H420" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I420" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J420" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K420" s="11"/>
       <c r="L420" s="22"/>
     </row>
     <row r="421" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16558,11 +17128,17 @@
       <c r="D421" s="20"/>
       <c r="E421" s="21"/>
       <c r="F421" s="22"/>
-      <c r="G421" s="23"/>
-      <c r="H421" s="23"/>
-      <c r="I421" s="23"/>
-      <c r="J421" s="23"/>
-      <c r="K421" s="23"/>
+      <c r="G421" s="11"/>
+      <c r="H421" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I421" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J421" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K421" s="11"/>
       <c r="L421" s="22"/>
     </row>
     <row r="422" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16572,11 +17148,17 @@
       <c r="D422" s="20"/>
       <c r="E422" s="21"/>
       <c r="F422" s="22"/>
-      <c r="G422" s="23"/>
-      <c r="H422" s="23"/>
-      <c r="I422" s="23"/>
-      <c r="J422" s="23"/>
-      <c r="K422" s="23"/>
+      <c r="G422" s="11"/>
+      <c r="H422" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I422" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J422" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K422" s="11"/>
       <c r="L422" s="22"/>
     </row>
     <row r="423" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16623,11 +17205,17 @@
       </c>
       <c r="E425" s="21"/>
       <c r="F425" s="22"/>
-      <c r="G425" s="23"/>
-      <c r="H425" s="23"/>
-      <c r="I425" s="23"/>
-      <c r="J425" s="23"/>
-      <c r="K425" s="23"/>
+      <c r="G425" s="11"/>
+      <c r="H425" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I425" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J425" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K425" s="11"/>
       <c r="L425" s="22"/>
     </row>
     <row r="426" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -16640,11 +17228,17 @@
       <c r="D426" s="20"/>
       <c r="E426" s="21"/>
       <c r="F426" s="22"/>
-      <c r="G426" s="23"/>
-      <c r="H426" s="23"/>
-      <c r="I426" s="23"/>
-      <c r="J426" s="23"/>
-      <c r="K426" s="23"/>
+      <c r="G426" s="11"/>
+      <c r="H426" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I426" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J426" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K426" s="11"/>
       <c r="L426" s="22"/>
     </row>
     <row r="427" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16658,11 +17252,17 @@
       <c r="D427" s="20"/>
       <c r="E427" s="21"/>
       <c r="F427" s="22"/>
-      <c r="G427" s="23"/>
-      <c r="H427" s="23"/>
-      <c r="I427" s="23"/>
-      <c r="J427" s="23"/>
-      <c r="K427" s="23"/>
+      <c r="G427" s="11"/>
+      <c r="H427" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I427" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J427" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K427" s="11"/>
       <c r="L427" s="22"/>
     </row>
     <row r="428" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16676,11 +17276,17 @@
       <c r="D428" s="20"/>
       <c r="E428" s="21"/>
       <c r="F428" s="22"/>
-      <c r="G428" s="23"/>
-      <c r="H428" s="23"/>
-      <c r="I428" s="23"/>
-      <c r="J428" s="23"/>
-      <c r="K428" s="23"/>
+      <c r="G428" s="11"/>
+      <c r="H428" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I428" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J428" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K428" s="11"/>
       <c r="L428" s="22"/>
     </row>
     <row r="429" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16696,11 +17302,17 @@
       <c r="F429" s="64">
         <v>1</v>
       </c>
-      <c r="G429" s="23"/>
-      <c r="H429" s="23"/>
-      <c r="I429" s="23"/>
-      <c r="J429" s="23"/>
-      <c r="K429" s="23"/>
+      <c r="G429" s="11"/>
+      <c r="H429" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I429" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J429" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K429" s="11"/>
       <c r="L429" s="64"/>
     </row>
     <row r="430" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16714,11 +17326,17 @@
       <c r="D430" s="20"/>
       <c r="E430" s="21"/>
       <c r="F430" s="64"/>
-      <c r="G430" s="23"/>
-      <c r="H430" s="23"/>
-      <c r="I430" s="23"/>
-      <c r="J430" s="23"/>
-      <c r="K430" s="23"/>
+      <c r="G430" s="11"/>
+      <c r="H430" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I430" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J430" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K430" s="11"/>
       <c r="L430" s="64"/>
     </row>
     <row r="431" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16732,11 +17350,17 @@
       <c r="D431" s="20"/>
       <c r="E431" s="21"/>
       <c r="F431" s="64"/>
-      <c r="G431" s="23"/>
-      <c r="H431" s="23"/>
-      <c r="I431" s="23"/>
-      <c r="J431" s="23"/>
-      <c r="K431" s="23"/>
+      <c r="G431" s="11"/>
+      <c r="H431" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I431" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J431" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K431" s="11"/>
       <c r="L431" s="64"/>
     </row>
     <row r="432" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16750,11 +17374,17 @@
       <c r="D432" s="20"/>
       <c r="E432" s="21"/>
       <c r="F432" s="64"/>
-      <c r="G432" s="23"/>
-      <c r="H432" s="23"/>
-      <c r="I432" s="23"/>
-      <c r="J432" s="23"/>
-      <c r="K432" s="23"/>
+      <c r="G432" s="11"/>
+      <c r="H432" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I432" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J432" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K432" s="11"/>
       <c r="L432" s="64"/>
     </row>
     <row r="433" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16770,11 +17400,17 @@
       <c r="F433" s="64">
         <v>1</v>
       </c>
-      <c r="G433" s="23"/>
-      <c r="H433" s="23"/>
-      <c r="I433" s="23"/>
-      <c r="J433" s="23"/>
-      <c r="K433" s="23"/>
+      <c r="G433" s="11"/>
+      <c r="H433" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I433" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J433" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K433" s="11"/>
       <c r="L433" s="64"/>
     </row>
     <row r="434" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -16787,11 +17423,17 @@
       <c r="D434" s="20"/>
       <c r="E434" s="21"/>
       <c r="F434" s="22"/>
-      <c r="G434" s="23"/>
-      <c r="H434" s="23"/>
-      <c r="I434" s="23"/>
-      <c r="J434" s="23"/>
-      <c r="K434" s="23"/>
+      <c r="G434" s="11"/>
+      <c r="H434" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I434" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J434" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K434" s="11"/>
       <c r="L434" s="22"/>
     </row>
     <row r="435" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -16804,11 +17446,17 @@
       <c r="D435" s="20"/>
       <c r="E435" s="21"/>
       <c r="F435" s="22"/>
-      <c r="G435" s="23"/>
-      <c r="H435" s="23"/>
-      <c r="I435" s="23"/>
-      <c r="J435" s="23"/>
-      <c r="K435" s="23"/>
+      <c r="G435" s="11"/>
+      <c r="H435" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I435" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J435" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K435" s="11"/>
       <c r="L435" s="22"/>
     </row>
     <row r="436" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16822,11 +17470,17 @@
       <c r="D436" s="20"/>
       <c r="E436" s="21"/>
       <c r="F436" s="22"/>
-      <c r="G436" s="23"/>
-      <c r="H436" s="23"/>
-      <c r="I436" s="23"/>
-      <c r="J436" s="23"/>
-      <c r="K436" s="23"/>
+      <c r="G436" s="11"/>
+      <c r="H436" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I436" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J436" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K436" s="11"/>
       <c r="L436" s="22"/>
     </row>
     <row r="437" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16836,11 +17490,11 @@
       <c r="D437" s="20"/>
       <c r="E437" s="21"/>
       <c r="F437" s="22"/>
-      <c r="G437" s="23"/>
-      <c r="H437" s="23"/>
-      <c r="I437" s="23"/>
-      <c r="J437" s="23"/>
-      <c r="K437" s="23"/>
+      <c r="G437" s="11"/>
+      <c r="H437" s="11"/>
+      <c r="I437" s="11"/>
+      <c r="J437" s="11"/>
+      <c r="K437" s="11"/>
       <c r="L437" s="22"/>
     </row>
     <row r="438" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16861,7 +17515,7 @@
       <c r="K438" s="11"/>
       <c r="L438" s="10"/>
     </row>
-    <row r="439" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="16"/>
       <c r="B439" s="14" t="s">
         <v>249</v>
@@ -16889,11 +17543,16 @@
       </c>
       <c r="E440" s="42"/>
       <c r="F440" s="43"/>
-      <c r="G440" s="23"/>
-      <c r="H440" s="23"/>
-      <c r="I440" s="23"/>
-      <c r="J440" s="23"/>
-      <c r="K440" s="23"/>
+      <c r="H440" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I440" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J440" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K440" s="11"/>
       <c r="L440" s="43"/>
     </row>
     <row r="441" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16908,13 +17567,19 @@
       <c r="D441" s="41"/>
       <c r="E441" s="42"/>
       <c r="F441" s="43"/>
-      <c r="G441" s="23">
+      <c r="G441" s="64">
         <v>2</v>
       </c>
-      <c r="H441" s="23"/>
-      <c r="I441" s="23"/>
-      <c r="J441" s="23"/>
-      <c r="K441" s="23"/>
+      <c r="H441" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I441" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J441" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K441" s="11"/>
       <c r="L441" s="43"/>
     </row>
     <row r="442" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16929,11 +17594,17 @@
       <c r="D442" s="41"/>
       <c r="E442" s="42"/>
       <c r="F442" s="43"/>
-      <c r="G442" s="23"/>
-      <c r="H442" s="23"/>
-      <c r="I442" s="23"/>
-      <c r="J442" s="23"/>
-      <c r="K442" s="23"/>
+      <c r="G442" s="11"/>
+      <c r="H442" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I442" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J442" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K442" s="11"/>
       <c r="L442" s="43"/>
     </row>
     <row r="443" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16948,11 +17619,17 @@
       <c r="D443" s="41"/>
       <c r="E443" s="42"/>
       <c r="F443" s="43"/>
-      <c r="G443" s="23"/>
-      <c r="H443" s="23"/>
-      <c r="I443" s="23"/>
-      <c r="J443" s="23"/>
-      <c r="K443" s="23"/>
+      <c r="G443" s="11"/>
+      <c r="H443" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I443" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J443" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K443" s="11"/>
       <c r="L443" s="43"/>
     </row>
     <row r="444" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16962,11 +17639,17 @@
       <c r="D444" s="41"/>
       <c r="E444" s="42"/>
       <c r="F444" s="43"/>
-      <c r="G444" s="23"/>
-      <c r="H444" s="23"/>
-      <c r="I444" s="23"/>
-      <c r="J444" s="23"/>
-      <c r="K444" s="23"/>
+      <c r="G444" s="11"/>
+      <c r="H444" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I444" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J444" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K444" s="11"/>
       <c r="L444" s="43"/>
     </row>
     <row r="445" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -17014,11 +17697,17 @@
       <c r="D447" s="41"/>
       <c r="E447" s="42"/>
       <c r="F447" s="43"/>
-      <c r="G447" s="23"/>
-      <c r="H447" s="23"/>
-      <c r="I447" s="23"/>
-      <c r="J447" s="23"/>
-      <c r="K447" s="23"/>
+      <c r="G447" s="11"/>
+      <c r="H447" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I447" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J447" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K447" s="11"/>
       <c r="L447" s="43"/>
     </row>
     <row r="448" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -17032,11 +17721,17 @@
       <c r="D448" s="41"/>
       <c r="E448" s="42"/>
       <c r="F448" s="43"/>
-      <c r="G448" s="23"/>
-      <c r="H448" s="23"/>
-      <c r="I448" s="23"/>
-      <c r="J448" s="23"/>
-      <c r="K448" s="23"/>
+      <c r="G448" s="11"/>
+      <c r="H448" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I448" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J448" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K448" s="11"/>
       <c r="L448" s="43"/>
     </row>
     <row r="449" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -17046,11 +17741,11 @@
       <c r="D449" s="41"/>
       <c r="E449" s="42"/>
       <c r="F449" s="43"/>
-      <c r="G449" s="23"/>
-      <c r="H449" s="23"/>
-      <c r="I449" s="23"/>
-      <c r="J449" s="23"/>
-      <c r="K449" s="23"/>
+      <c r="G449" s="11"/>
+      <c r="H449" s="11"/>
+      <c r="I449" s="11"/>
+      <c r="J449" s="11"/>
+      <c r="K449" s="11"/>
       <c r="L449" s="43"/>
     </row>
     <row r="450" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -17098,11 +17793,17 @@
       <c r="D452" s="41"/>
       <c r="E452" s="42"/>
       <c r="F452" s="43"/>
-      <c r="G452" s="23"/>
-      <c r="H452" s="23"/>
-      <c r="I452" s="23"/>
-      <c r="J452" s="23"/>
-      <c r="K452" s="23"/>
+      <c r="G452" s="11"/>
+      <c r="H452" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I452" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J452" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K452" s="11"/>
       <c r="L452" s="43"/>
     </row>
     <row r="453" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -17116,11 +17817,17 @@
       <c r="D453" s="41"/>
       <c r="E453" s="42"/>
       <c r="F453" s="43"/>
-      <c r="G453" s="23"/>
-      <c r="H453" s="23"/>
-      <c r="I453" s="23"/>
-      <c r="J453" s="23"/>
-      <c r="K453" s="23"/>
+      <c r="G453" s="11"/>
+      <c r="H453" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I453" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J453" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K453" s="11"/>
       <c r="L453" s="43"/>
     </row>
     <row r="454" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -17175,17 +17882,18 @@
       <c r="B456" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C456" s="90" t="s">
+      <c r="C456" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D456" s="90"/>
-      <c r="E456" s="90"/>
-      <c r="F456" s="90"/>
-      <c r="G456" s="90"/>
-      <c r="H456" s="95"/>
-      <c r="I456" s="95"/>
-      <c r="J456" s="95"/>
-      <c r="K456" s="95"/>
+      <c r="D456" s="98"/>
+      <c r="E456" s="98"/>
+      <c r="F456" s="98"/>
+      <c r="G456" s="98"/>
+      <c r="H456" s="89"/>
+      <c r="I456" s="89"/>
+      <c r="J456" s="89"/>
+      <c r="K456" s="89"/>
+      <c r="L456" s="89"/>
     </row>
     <row r="457" spans="1:12" s="24" customFormat="1" ht="99.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
@@ -18125,42 +18833,51 @@
       <c r="B511" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C511" s="90" t="s">
+      <c r="C511" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D511" s="90"/>
-      <c r="E511" s="90"/>
-      <c r="F511" s="90"/>
-      <c r="G511" s="90"/>
-      <c r="H511" s="95"/>
-      <c r="I511" s="95"/>
-      <c r="J511" s="95"/>
-      <c r="K511" s="95"/>
+      <c r="D511" s="98"/>
+      <c r="E511" s="98"/>
+      <c r="F511" s="98"/>
+      <c r="G511" s="98"/>
+      <c r="H511" s="89"/>
+      <c r="I511" s="89"/>
+      <c r="J511" s="89"/>
+      <c r="K511" s="89"/>
+      <c r="L511" s="89"/>
     </row>
     <row r="512" spans="1:12" ht="82.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="1"/>
       <c r="B512" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C512" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D512" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E512" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F512" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G512" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="H512" s="11"/>
-      <c r="I512" s="11"/>
-      <c r="J512" s="11"/>
-      <c r="K512" s="11"/>
+      <c r="C512" s="92" t="s">
+        <v>469</v>
+      </c>
+      <c r="D512" s="41" t="s">
+        <v>470</v>
+      </c>
+      <c r="E512" s="42" t="s">
+        <v>471</v>
+      </c>
+      <c r="F512" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="G512" s="93" t="s">
+        <v>473</v>
+      </c>
+      <c r="H512" s="90" t="s">
+        <v>464</v>
+      </c>
+      <c r="I512" s="90" t="s">
+        <v>465</v>
+      </c>
+      <c r="J512" s="90" t="s">
+        <v>466</v>
+      </c>
+      <c r="K512" s="90" t="s">
+        <v>468</v>
+      </c>
       <c r="L512" s="10"/>
     </row>
     <row r="513" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18174,7 +18891,7 @@
       <c r="D513" s="8"/>
       <c r="E513" s="9"/>
       <c r="F513" s="10"/>
-      <c r="G513" s="11"/>
+      <c r="G513" s="42"/>
       <c r="H513" s="11"/>
       <c r="I513" s="11"/>
       <c r="J513" s="11"/>
@@ -18190,7 +18907,7 @@
       <c r="D514" s="8"/>
       <c r="E514" s="9"/>
       <c r="F514" s="10"/>
-      <c r="G514" s="11"/>
+      <c r="G514" s="42"/>
       <c r="H514" s="11"/>
       <c r="I514" s="11"/>
       <c r="J514" s="11"/>
@@ -18209,13 +18926,19 @@
       <c r="D515" s="41"/>
       <c r="E515" s="42"/>
       <c r="F515" s="43"/>
-      <c r="G515" s="23">
+      <c r="G515" s="42">
         <v>2</v>
       </c>
-      <c r="H515" s="23"/>
-      <c r="I515" s="23"/>
-      <c r="J515" s="23"/>
-      <c r="K515" s="23"/>
+      <c r="H515" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I515" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J515" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K515" s="11"/>
       <c r="L515" s="43"/>
     </row>
     <row r="516" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18230,11 +18953,17 @@
       <c r="D516" s="41"/>
       <c r="E516" s="42"/>
       <c r="F516" s="43"/>
-      <c r="G516" s="23"/>
-      <c r="H516" s="23"/>
-      <c r="I516" s="23"/>
-      <c r="J516" s="23"/>
-      <c r="K516" s="23"/>
+      <c r="G516" s="42"/>
+      <c r="H516" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I516" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J516" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K516" s="11"/>
       <c r="L516" s="43"/>
     </row>
     <row r="517" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18246,13 +18975,19 @@
       <c r="D517" s="41"/>
       <c r="E517" s="42"/>
       <c r="F517" s="43"/>
-      <c r="G517" s="23">
-        <v>1</v>
-      </c>
-      <c r="H517" s="23"/>
-      <c r="I517" s="23"/>
-      <c r="J517" s="23"/>
-      <c r="K517" s="23"/>
+      <c r="G517" s="42">
+        <v>1</v>
+      </c>
+      <c r="H517" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="I517" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="J517" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="K517" s="11"/>
       <c r="L517" s="43"/>
     </row>
     <row r="518" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18267,11 +19002,17 @@
       <c r="D518" s="41"/>
       <c r="E518" s="42"/>
       <c r="F518" s="43"/>
-      <c r="G518" s="23"/>
-      <c r="H518" s="23"/>
-      <c r="I518" s="23"/>
-      <c r="J518" s="23"/>
-      <c r="K518" s="23"/>
+      <c r="G518" s="42"/>
+      <c r="H518" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I518" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J518" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K518" s="11"/>
       <c r="L518" s="43"/>
     </row>
     <row r="519" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18281,11 +19022,11 @@
       <c r="D519" s="29"/>
       <c r="E519" s="30"/>
       <c r="F519" s="31"/>
-      <c r="G519" s="32"/>
-      <c r="H519" s="32"/>
-      <c r="I519" s="32"/>
-      <c r="J519" s="32"/>
-      <c r="K519" s="32"/>
+      <c r="G519" s="42"/>
+      <c r="H519" s="11"/>
+      <c r="I519" s="11"/>
+      <c r="J519" s="11"/>
+      <c r="K519" s="11"/>
       <c r="L519" s="31"/>
     </row>
     <row r="520" spans="1:12" ht="25.8" customHeight="1" x14ac:dyDescent="0.35">
@@ -18299,7 +19040,7 @@
       <c r="D520" s="8"/>
       <c r="E520" s="9"/>
       <c r="F520" s="10"/>
-      <c r="G520" s="11"/>
+      <c r="G520" s="42"/>
       <c r="H520" s="11"/>
       <c r="I520" s="11"/>
       <c r="J520" s="11"/>
@@ -18315,7 +19056,7 @@
       <c r="D521" s="8"/>
       <c r="E521" s="9"/>
       <c r="F521" s="10"/>
-      <c r="G521" s="11"/>
+      <c r="G521" s="42"/>
       <c r="H521" s="11"/>
       <c r="I521" s="11"/>
       <c r="J521" s="11"/>
@@ -18334,11 +19075,17 @@
       </c>
       <c r="E522" s="42"/>
       <c r="F522" s="43"/>
-      <c r="G522" s="23"/>
-      <c r="H522" s="23"/>
-      <c r="I522" s="23"/>
-      <c r="J522" s="23"/>
-      <c r="K522" s="23"/>
+      <c r="G522" s="42"/>
+      <c r="H522" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I522" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J522" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K522" s="11"/>
       <c r="L522" s="43"/>
     </row>
     <row r="523" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18353,13 +19100,19 @@
       <c r="D523" s="41"/>
       <c r="E523" s="42"/>
       <c r="F523" s="43"/>
-      <c r="G523" s="23">
+      <c r="G523" s="42">
         <v>2</v>
       </c>
-      <c r="H523" s="23"/>
-      <c r="I523" s="23"/>
-      <c r="J523" s="23"/>
-      <c r="K523" s="23"/>
+      <c r="H523" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I523" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J523" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K523" s="11"/>
       <c r="L523" s="43"/>
     </row>
     <row r="524" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18374,11 +19127,17 @@
       <c r="D524" s="41"/>
       <c r="E524" s="42"/>
       <c r="F524" s="43"/>
-      <c r="G524" s="23"/>
-      <c r="H524" s="23"/>
-      <c r="I524" s="23"/>
-      <c r="J524" s="23"/>
-      <c r="K524" s="23"/>
+      <c r="G524" s="42"/>
+      <c r="H524" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I524" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J524" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K524" s="11"/>
       <c r="L524" s="43"/>
     </row>
     <row r="525" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18393,11 +19152,17 @@
       <c r="D525" s="41"/>
       <c r="E525" s="42"/>
       <c r="F525" s="43"/>
-      <c r="G525" s="23"/>
-      <c r="H525" s="23"/>
-      <c r="I525" s="23"/>
-      <c r="J525" s="23"/>
-      <c r="K525" s="23"/>
+      <c r="G525" s="42"/>
+      <c r="H525" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I525" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J525" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K525" s="11"/>
       <c r="L525" s="43"/>
     </row>
     <row r="526" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18407,11 +19172,11 @@
       <c r="D526" s="41"/>
       <c r="E526" s="42"/>
       <c r="F526" s="43"/>
-      <c r="G526" s="23"/>
-      <c r="H526" s="23"/>
-      <c r="I526" s="23"/>
-      <c r="J526" s="23"/>
-      <c r="K526" s="23"/>
+      <c r="G526" s="42"/>
+      <c r="H526" s="11"/>
+      <c r="I526" s="11"/>
+      <c r="J526" s="11"/>
+      <c r="K526" s="11"/>
       <c r="L526" s="43"/>
     </row>
     <row r="527" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18425,7 +19190,7 @@
       <c r="D527" s="8"/>
       <c r="E527" s="9"/>
       <c r="F527" s="10"/>
-      <c r="G527" s="11"/>
+      <c r="G527" s="42"/>
       <c r="H527" s="11"/>
       <c r="I527" s="11"/>
       <c r="J527" s="11"/>
@@ -18441,7 +19206,7 @@
       <c r="D528" s="8"/>
       <c r="E528" s="9"/>
       <c r="F528" s="10"/>
-      <c r="G528" s="11"/>
+      <c r="G528" s="42"/>
       <c r="H528" s="11"/>
       <c r="I528" s="11"/>
       <c r="J528" s="11"/>
@@ -18455,15 +19220,21 @@
       </c>
       <c r="C529" s="40"/>
       <c r="D529" s="41"/>
-      <c r="E529" s="42">
-        <v>1</v>
-      </c>
+      <c r="E529" s="42"/>
       <c r="F529" s="43"/>
-      <c r="G529" s="23"/>
-      <c r="H529" s="23"/>
-      <c r="I529" s="23"/>
-      <c r="J529" s="23"/>
-      <c r="K529" s="23"/>
+      <c r="G529" s="42">
+        <v>1</v>
+      </c>
+      <c r="H529" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="I529" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="J529" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="K529" s="11"/>
       <c r="L529" s="43"/>
     </row>
     <row r="530" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -18472,15 +19243,21 @@
       </c>
       <c r="C530" s="40"/>
       <c r="D530" s="41"/>
-      <c r="E530" s="42">
-        <v>1</v>
-      </c>
+      <c r="E530" s="42"/>
       <c r="F530" s="43"/>
-      <c r="G530" s="23"/>
-      <c r="H530" s="23"/>
-      <c r="I530" s="23"/>
-      <c r="J530" s="23"/>
-      <c r="K530" s="23"/>
+      <c r="G530" s="42">
+        <v>1</v>
+      </c>
+      <c r="H530" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="I530" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="J530" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="K530" s="11"/>
       <c r="L530" s="43"/>
     </row>
     <row r="531" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -18493,13 +19270,19 @@
       <c r="D531" s="41"/>
       <c r="E531" s="42"/>
       <c r="F531" s="43"/>
-      <c r="G531" s="23">
-        <v>1</v>
-      </c>
-      <c r="H531" s="23"/>
-      <c r="I531" s="23"/>
-      <c r="J531" s="23"/>
-      <c r="K531" s="23"/>
+      <c r="G531" s="42">
+        <v>1</v>
+      </c>
+      <c r="H531" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I531" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J531" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K531" s="11"/>
       <c r="L531" s="43"/>
     </row>
     <row r="532" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18513,11 +19296,17 @@
       <c r="D532" s="41"/>
       <c r="E532" s="42"/>
       <c r="F532" s="43"/>
-      <c r="G532" s="23"/>
-      <c r="H532" s="23"/>
-      <c r="I532" s="23"/>
-      <c r="J532" s="23"/>
-      <c r="K532" s="23"/>
+      <c r="G532" s="42"/>
+      <c r="H532" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I532" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J532" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K532" s="11"/>
       <c r="L532" s="43"/>
     </row>
     <row r="533" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18531,11 +19320,17 @@
       <c r="D533" s="41"/>
       <c r="E533" s="42"/>
       <c r="F533" s="43"/>
-      <c r="G533" s="23"/>
-      <c r="H533" s="23"/>
-      <c r="I533" s="23"/>
-      <c r="J533" s="23"/>
-      <c r="K533" s="23"/>
+      <c r="G533" s="42"/>
+      <c r="H533" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I533" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J533" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K533" s="11"/>
       <c r="L533" s="43"/>
     </row>
     <row r="534" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18545,11 +19340,11 @@
       <c r="D534" s="29"/>
       <c r="E534" s="30"/>
       <c r="F534" s="31"/>
-      <c r="G534" s="32"/>
-      <c r="H534" s="32"/>
-      <c r="I534" s="32"/>
-      <c r="J534" s="32"/>
-      <c r="K534" s="32"/>
+      <c r="G534" s="42"/>
+      <c r="H534" s="11"/>
+      <c r="I534" s="11"/>
+      <c r="J534" s="11"/>
+      <c r="K534" s="11"/>
       <c r="L534" s="31"/>
     </row>
     <row r="535" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -18563,7 +19358,7 @@
       <c r="D535" s="8"/>
       <c r="E535" s="9"/>
       <c r="F535" s="10"/>
-      <c r="G535" s="11"/>
+      <c r="G535" s="42"/>
       <c r="H535" s="11"/>
       <c r="I535" s="11"/>
       <c r="J535" s="11"/>
@@ -18579,7 +19374,7 @@
       <c r="D536" s="8"/>
       <c r="E536" s="9"/>
       <c r="F536" s="10"/>
-      <c r="G536" s="11"/>
+      <c r="G536" s="42"/>
       <c r="H536" s="11"/>
       <c r="I536" s="11"/>
       <c r="J536" s="11"/>
@@ -18598,13 +19393,19 @@
       <c r="D537" s="41"/>
       <c r="E537" s="42"/>
       <c r="F537" s="43"/>
-      <c r="G537" s="23">
+      <c r="G537" s="42">
         <v>2</v>
       </c>
-      <c r="H537" s="23"/>
-      <c r="I537" s="23"/>
-      <c r="J537" s="23"/>
-      <c r="K537" s="23"/>
+      <c r="H537" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I537" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J537" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K537" s="11"/>
       <c r="L537" s="43"/>
     </row>
     <row r="538" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18619,11 +19420,17 @@
       <c r="D538" s="41"/>
       <c r="E538" s="42"/>
       <c r="F538" s="43"/>
-      <c r="G538" s="23"/>
-      <c r="H538" s="23"/>
-      <c r="I538" s="23"/>
-      <c r="J538" s="23"/>
-      <c r="K538" s="23"/>
+      <c r="G538" s="42"/>
+      <c r="H538" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I538" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J538" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K538" s="11"/>
       <c r="L538" s="43"/>
     </row>
     <row r="539" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18635,13 +19442,19 @@
       <c r="D539" s="41"/>
       <c r="E539" s="42"/>
       <c r="F539" s="43"/>
-      <c r="G539" s="23">
+      <c r="G539" s="42">
         <v>2</v>
       </c>
-      <c r="H539" s="23"/>
-      <c r="I539" s="23"/>
-      <c r="J539" s="23"/>
-      <c r="K539" s="23"/>
+      <c r="H539" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="I539" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="J539" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="K539" s="11"/>
       <c r="L539" s="43"/>
     </row>
     <row r="540" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -18655,11 +19468,17 @@
       <c r="D540" s="41"/>
       <c r="E540" s="42"/>
       <c r="F540" s="43"/>
-      <c r="G540" s="23"/>
-      <c r="H540" s="23"/>
-      <c r="I540" s="23"/>
-      <c r="J540" s="23"/>
-      <c r="K540" s="23"/>
+      <c r="G540" s="42"/>
+      <c r="H540" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I540" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J540" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K540" s="11"/>
       <c r="L540" s="43"/>
     </row>
     <row r="541" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -18669,11 +19488,11 @@
       <c r="D541" s="29"/>
       <c r="E541" s="30"/>
       <c r="F541" s="31"/>
-      <c r="G541" s="32"/>
-      <c r="H541" s="32"/>
-      <c r="I541" s="32"/>
-      <c r="J541" s="32"/>
-      <c r="K541" s="32"/>
+      <c r="G541" s="42"/>
+      <c r="H541" s="11"/>
+      <c r="I541" s="11"/>
+      <c r="J541" s="11"/>
+      <c r="K541" s="11"/>
       <c r="L541" s="31"/>
     </row>
     <row r="542" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -18687,7 +19506,7 @@
       <c r="D542" s="8"/>
       <c r="E542" s="9"/>
       <c r="F542" s="10"/>
-      <c r="G542" s="11"/>
+      <c r="G542" s="42"/>
       <c r="H542" s="11"/>
       <c r="I542" s="11"/>
       <c r="J542" s="11"/>
@@ -18703,7 +19522,7 @@
       <c r="D543" s="8"/>
       <c r="E543" s="9"/>
       <c r="F543" s="10"/>
-      <c r="G543" s="11"/>
+      <c r="G543" s="42"/>
       <c r="H543" s="11"/>
       <c r="I543" s="11"/>
       <c r="J543" s="11"/>
@@ -18721,11 +19540,17 @@
       <c r="D544" s="41"/>
       <c r="E544" s="42"/>
       <c r="F544" s="43"/>
-      <c r="G544" s="23"/>
-      <c r="H544" s="23"/>
-      <c r="I544" s="23"/>
-      <c r="J544" s="23"/>
-      <c r="K544" s="23"/>
+      <c r="G544" s="42"/>
+      <c r="H544" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I544" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J544" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K544" s="11"/>
       <c r="L544" s="43"/>
     </row>
     <row r="545" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -18738,11 +19563,17 @@
       <c r="D545" s="41"/>
       <c r="E545" s="42"/>
       <c r="F545" s="43"/>
-      <c r="G545" s="23"/>
-      <c r="H545" s="23"/>
-      <c r="I545" s="23"/>
-      <c r="J545" s="23"/>
-      <c r="K545" s="23"/>
+      <c r="G545" s="42"/>
+      <c r="H545" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I545" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J545" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K545" s="11"/>
       <c r="L545" s="43"/>
     </row>
     <row r="546" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -18755,11 +19586,17 @@
       <c r="D546" s="41"/>
       <c r="E546" s="42"/>
       <c r="F546" s="43"/>
-      <c r="G546" s="23"/>
-      <c r="H546" s="23"/>
-      <c r="I546" s="23"/>
-      <c r="J546" s="23"/>
-      <c r="K546" s="23"/>
+      <c r="G546" s="42"/>
+      <c r="H546" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I546" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J546" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K546" s="11"/>
       <c r="L546" s="43"/>
     </row>
     <row r="547" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18773,13 +19610,19 @@
       <c r="D547" s="41"/>
       <c r="E547" s="42"/>
       <c r="F547" s="43"/>
-      <c r="G547" s="23">
-        <v>1</v>
-      </c>
-      <c r="H547" s="23"/>
-      <c r="I547" s="23"/>
-      <c r="J547" s="23"/>
-      <c r="K547" s="23"/>
+      <c r="G547" s="42">
+        <v>1</v>
+      </c>
+      <c r="H547" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I547" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J547" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K547" s="11"/>
       <c r="L547" s="43"/>
     </row>
     <row r="548" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18793,11 +19636,17 @@
       <c r="D548" s="41"/>
       <c r="E548" s="42"/>
       <c r="F548" s="43"/>
-      <c r="G548" s="23"/>
-      <c r="H548" s="23"/>
-      <c r="I548" s="23"/>
-      <c r="J548" s="23"/>
-      <c r="K548" s="23"/>
+      <c r="G548" s="42"/>
+      <c r="H548" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I548" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J548" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K548" s="11"/>
       <c r="L548" s="43"/>
     </row>
     <row r="549" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -18810,11 +19659,17 @@
       <c r="D549" s="41"/>
       <c r="E549" s="42"/>
       <c r="F549" s="43"/>
-      <c r="G549" s="23"/>
-      <c r="H549" s="23"/>
-      <c r="I549" s="23"/>
-      <c r="J549" s="23"/>
-      <c r="K549" s="23"/>
+      <c r="G549" s="42"/>
+      <c r="H549" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I549" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J549" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K549" s="11"/>
       <c r="L549" s="43"/>
     </row>
     <row r="550" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -18827,11 +19682,17 @@
       </c>
       <c r="E550" s="42"/>
       <c r="F550" s="43"/>
-      <c r="G550" s="23"/>
-      <c r="H550" s="23"/>
-      <c r="I550" s="23"/>
-      <c r="J550" s="23"/>
-      <c r="K550" s="23"/>
+      <c r="G550" s="42"/>
+      <c r="H550" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I550" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J550" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K550" s="11"/>
       <c r="L550" s="43"/>
     </row>
     <row r="551" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18845,11 +19706,17 @@
         <v>2</v>
       </c>
       <c r="F551" s="43"/>
-      <c r="G551" s="23"/>
-      <c r="H551" s="23"/>
-      <c r="I551" s="23"/>
-      <c r="J551" s="23"/>
-      <c r="K551" s="23"/>
+      <c r="G551" s="42"/>
+      <c r="H551" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I551" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J551" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K551" s="11"/>
       <c r="L551" s="43"/>
     </row>
     <row r="552" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18863,11 +19730,17 @@
         <v>1</v>
       </c>
       <c r="F552" s="43"/>
-      <c r="G552" s="23"/>
-      <c r="H552" s="23"/>
-      <c r="I552" s="23"/>
-      <c r="J552" s="23"/>
-      <c r="K552" s="23"/>
+      <c r="G552" s="42"/>
+      <c r="H552" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I552" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J552" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K552" s="11"/>
       <c r="L552" s="43"/>
     </row>
     <row r="553" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -18882,11 +19755,17 @@
       <c r="F553" s="43">
         <v>1</v>
       </c>
-      <c r="G553" s="23"/>
-      <c r="H553" s="23"/>
-      <c r="I553" s="23"/>
-      <c r="J553" s="23"/>
-      <c r="K553" s="23"/>
+      <c r="G553" s="42"/>
+      <c r="H553" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I553" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J553" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K553" s="11"/>
       <c r="L553" s="43"/>
     </row>
     <row r="554" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18900,11 +19779,17 @@
         <v>2</v>
       </c>
       <c r="F554" s="43"/>
-      <c r="G554" s="23"/>
-      <c r="H554" s="23"/>
-      <c r="I554" s="23"/>
-      <c r="J554" s="23"/>
-      <c r="K554" s="23"/>
+      <c r="G554" s="42"/>
+      <c r="H554" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I554" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J554" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K554" s="11"/>
       <c r="L554" s="43"/>
     </row>
     <row r="555" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18918,11 +19803,17 @@
         <v>2</v>
       </c>
       <c r="F555" s="43"/>
-      <c r="G555" s="23"/>
-      <c r="H555" s="23"/>
-      <c r="I555" s="23"/>
-      <c r="J555" s="23"/>
-      <c r="K555" s="23"/>
+      <c r="G555" s="42"/>
+      <c r="H555" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I555" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J555" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K555" s="11"/>
       <c r="L555" s="43"/>
     </row>
     <row r="556" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18934,13 +19825,19 @@
       <c r="D556" s="29"/>
       <c r="E556" s="30"/>
       <c r="F556" s="31"/>
-      <c r="G556" s="23">
-        <v>1</v>
-      </c>
-      <c r="H556" s="23"/>
-      <c r="I556" s="23"/>
-      <c r="J556" s="23"/>
-      <c r="K556" s="23"/>
+      <c r="G556" s="42">
+        <v>1</v>
+      </c>
+      <c r="H556" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I556" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J556" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K556" s="11"/>
       <c r="L556" s="31"/>
     </row>
     <row r="557" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18950,11 +19847,11 @@
       <c r="D557" s="29"/>
       <c r="E557" s="30"/>
       <c r="F557" s="31"/>
-      <c r="G557" s="23"/>
-      <c r="H557" s="23"/>
-      <c r="I557" s="23"/>
-      <c r="J557" s="23"/>
-      <c r="K557" s="23"/>
+      <c r="G557" s="42"/>
+      <c r="H557" s="11"/>
+      <c r="I557" s="11"/>
+      <c r="J557" s="11"/>
+      <c r="K557" s="11"/>
       <c r="L557" s="31"/>
     </row>
     <row r="558" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18968,11 +19865,11 @@
       <c r="D558" s="29"/>
       <c r="E558" s="30"/>
       <c r="F558" s="31"/>
-      <c r="G558" s="23"/>
-      <c r="H558" s="23"/>
-      <c r="I558" s="23"/>
-      <c r="J558" s="23"/>
-      <c r="K558" s="23"/>
+      <c r="G558" s="42"/>
+      <c r="H558" s="11"/>
+      <c r="I558" s="11"/>
+      <c r="J558" s="11"/>
+      <c r="K558" s="11"/>
       <c r="L558" s="31"/>
     </row>
     <row r="559" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18984,7 +19881,7 @@
       <c r="D559" s="8"/>
       <c r="E559" s="9"/>
       <c r="F559" s="10"/>
-      <c r="G559" s="11"/>
+      <c r="G559" s="42"/>
       <c r="H559" s="11"/>
       <c r="I559" s="11"/>
       <c r="J559" s="11"/>
@@ -19002,11 +19899,17 @@
         <v>2</v>
       </c>
       <c r="F560" s="22"/>
-      <c r="G560" s="23"/>
-      <c r="H560" s="23"/>
-      <c r="I560" s="23"/>
-      <c r="J560" s="23"/>
-      <c r="K560" s="23"/>
+      <c r="G560" s="42"/>
+      <c r="H560" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I560" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J560" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K560" s="11"/>
       <c r="L560" s="22"/>
     </row>
     <row r="561" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19020,11 +19923,17 @@
         <v>2</v>
       </c>
       <c r="F561" s="22"/>
-      <c r="G561" s="23"/>
-      <c r="H561" s="23"/>
-      <c r="I561" s="23"/>
-      <c r="J561" s="23"/>
-      <c r="K561" s="23"/>
+      <c r="G561" s="42"/>
+      <c r="H561" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I561" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J561" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K561" s="11"/>
       <c r="L561" s="22"/>
     </row>
     <row r="562" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -19037,11 +19946,17 @@
         <v>2</v>
       </c>
       <c r="F562" s="22"/>
-      <c r="G562" s="23"/>
-      <c r="H562" s="23"/>
-      <c r="I562" s="23"/>
-      <c r="J562" s="23"/>
-      <c r="K562" s="23"/>
+      <c r="G562" s="42"/>
+      <c r="H562" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I562" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J562" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K562" s="11"/>
       <c r="L562" s="22"/>
     </row>
     <row r="563" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -19054,11 +19969,17 @@
         <v>2</v>
       </c>
       <c r="F563" s="22"/>
-      <c r="G563" s="23"/>
-      <c r="H563" s="23"/>
-      <c r="I563" s="23"/>
-      <c r="J563" s="23"/>
-      <c r="K563" s="23"/>
+      <c r="G563" s="42"/>
+      <c r="H563" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I563" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J563" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K563" s="11"/>
       <c r="L563" s="22"/>
     </row>
     <row r="564" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19072,11 +19993,17 @@
         <v>2</v>
       </c>
       <c r="F564" s="22"/>
-      <c r="G564" s="23"/>
-      <c r="H564" s="23"/>
-      <c r="I564" s="23"/>
-      <c r="J564" s="23"/>
-      <c r="K564" s="23"/>
+      <c r="G564" s="42"/>
+      <c r="H564" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I564" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J564" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K564" s="11"/>
       <c r="L564" s="22"/>
     </row>
     <row r="565" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19090,11 +20017,17 @@
         <v>1</v>
       </c>
       <c r="F565" s="22"/>
-      <c r="G565" s="23"/>
-      <c r="H565" s="23"/>
-      <c r="I565" s="23"/>
-      <c r="J565" s="23"/>
-      <c r="K565" s="23"/>
+      <c r="G565" s="42"/>
+      <c r="H565" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I565" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J565" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K565" s="11"/>
       <c r="L565" s="22"/>
     </row>
     <row r="566" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -19107,11 +20040,17 @@
       <c r="D566" s="20"/>
       <c r="E566" s="21"/>
       <c r="F566" s="22"/>
-      <c r="G566" s="23"/>
-      <c r="H566" s="23"/>
-      <c r="I566" s="23"/>
-      <c r="J566" s="23"/>
-      <c r="K566" s="23"/>
+      <c r="G566" s="42"/>
+      <c r="H566" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I566" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J566" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K566" s="11"/>
       <c r="L566" s="22"/>
     </row>
     <row r="567" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -19124,11 +20063,17 @@
       <c r="D567" s="20"/>
       <c r="E567" s="21"/>
       <c r="F567" s="22"/>
-      <c r="G567" s="23"/>
-      <c r="H567" s="23"/>
-      <c r="I567" s="23"/>
-      <c r="J567" s="23"/>
-      <c r="K567" s="23"/>
+      <c r="G567" s="42"/>
+      <c r="H567" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I567" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J567" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K567" s="11"/>
       <c r="L567" s="22"/>
     </row>
     <row r="568" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19144,11 +20089,17 @@
       <c r="F568" s="22">
         <v>1</v>
       </c>
-      <c r="G568" s="23"/>
-      <c r="H568" s="23"/>
-      <c r="I568" s="23"/>
-      <c r="J568" s="23"/>
-      <c r="K568" s="23"/>
+      <c r="G568" s="42"/>
+      <c r="H568" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I568" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J568" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K568" s="11"/>
       <c r="L568" s="22"/>
     </row>
     <row r="569" spans="1:12" s="33" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -19162,11 +20113,17 @@
         <v>1</v>
       </c>
       <c r="F569" s="22"/>
-      <c r="G569" s="23"/>
-      <c r="H569" s="23"/>
-      <c r="I569" s="23"/>
-      <c r="J569" s="23"/>
-      <c r="K569" s="23"/>
+      <c r="G569" s="42"/>
+      <c r="H569" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I569" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J569" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K569" s="11"/>
       <c r="L569" s="22"/>
     </row>
     <row r="570" spans="1:12" s="24" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -19180,11 +20137,17 @@
         <v>1</v>
       </c>
       <c r="F570" s="22"/>
-      <c r="G570" s="23"/>
-      <c r="H570" s="23"/>
-      <c r="I570" s="23"/>
-      <c r="J570" s="23"/>
-      <c r="K570" s="23"/>
+      <c r="G570" s="42"/>
+      <c r="H570" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I570" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J570" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K570" s="11"/>
       <c r="L570" s="22"/>
     </row>
     <row r="571" spans="1:12" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19198,11 +20161,17 @@
         <v>1</v>
       </c>
       <c r="F571" s="22"/>
-      <c r="G571" s="23"/>
-      <c r="H571" s="23"/>
-      <c r="I571" s="23"/>
-      <c r="J571" s="23"/>
-      <c r="K571" s="23"/>
+      <c r="G571" s="42"/>
+      <c r="H571" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I571" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J571" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K571" s="11"/>
       <c r="L571" s="22"/>
     </row>
     <row r="572" spans="1:12" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19212,11 +20181,11 @@
       <c r="D572" s="20"/>
       <c r="E572" s="21"/>
       <c r="F572" s="22"/>
-      <c r="G572" s="23"/>
-      <c r="H572" s="23"/>
-      <c r="I572" s="23"/>
-      <c r="J572" s="23"/>
-      <c r="K572" s="23"/>
+      <c r="G572" s="42"/>
+      <c r="H572" s="11"/>
+      <c r="I572" s="11"/>
+      <c r="J572" s="11"/>
+      <c r="K572" s="11"/>
       <c r="L572" s="22"/>
     </row>
     <row r="573" spans="1:12" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19230,7 +20199,7 @@
       <c r="D573" s="8"/>
       <c r="E573" s="9"/>
       <c r="F573" s="10"/>
-      <c r="G573" s="11"/>
+      <c r="G573" s="42"/>
       <c r="H573" s="11"/>
       <c r="I573" s="11"/>
       <c r="J573" s="11"/>
@@ -19246,7 +20215,7 @@
       <c r="D574" s="8"/>
       <c r="E574" s="9"/>
       <c r="F574" s="10"/>
-      <c r="G574" s="11"/>
+      <c r="G574" s="42"/>
       <c r="H574" s="11"/>
       <c r="I574" s="11"/>
       <c r="J574" s="11"/>
@@ -19264,11 +20233,17 @@
       <c r="D575" s="41"/>
       <c r="E575" s="42"/>
       <c r="F575" s="43"/>
-      <c r="G575" s="23"/>
-      <c r="H575" s="23"/>
-      <c r="I575" s="23"/>
-      <c r="J575" s="23"/>
-      <c r="K575" s="23"/>
+      <c r="G575" s="42"/>
+      <c r="H575" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I575" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J575" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K575" s="11"/>
       <c r="L575" s="43"/>
     </row>
     <row r="576" spans="1:12" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19282,11 +20257,17 @@
       <c r="D576" s="41"/>
       <c r="E576" s="42"/>
       <c r="F576" s="43"/>
-      <c r="G576" s="23"/>
-      <c r="H576" s="23"/>
-      <c r="I576" s="23"/>
-      <c r="J576" s="23"/>
-      <c r="K576" s="23"/>
+      <c r="G576" s="42"/>
+      <c r="H576" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I576" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J576" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K576" s="11"/>
       <c r="L576" s="43"/>
     </row>
     <row r="577" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19296,11 +20277,11 @@
       <c r="D577" s="29"/>
       <c r="E577" s="30"/>
       <c r="F577" s="31"/>
-      <c r="G577" s="32"/>
-      <c r="H577" s="32"/>
-      <c r="I577" s="32"/>
-      <c r="J577" s="32"/>
-      <c r="K577" s="32"/>
+      <c r="G577" s="42"/>
+      <c r="H577" s="11"/>
+      <c r="I577" s="11"/>
+      <c r="J577" s="11"/>
+      <c r="K577" s="11"/>
       <c r="L577" s="31"/>
     </row>
     <row r="578" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -19318,7 +20299,7 @@
       </c>
       <c r="E578" s="46">
         <f>SUM(E513:E577)</f>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F578" s="46">
         <f>SUM(F513:F577)</f>
@@ -19326,7 +20307,7 @@
       </c>
       <c r="G578" s="46">
         <f>SUM(G513:G577)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H578" s="46"/>
       <c r="I578" s="46"/>
@@ -19355,42 +20336,50 @@
       <c r="B580" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C580" s="90" t="s">
+      <c r="C580" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D580" s="90"/>
-      <c r="E580" s="90"/>
-      <c r="F580" s="90"/>
-      <c r="G580" s="90"/>
-      <c r="H580" s="95"/>
-      <c r="I580" s="95"/>
-      <c r="J580" s="95"/>
-      <c r="K580" s="95"/>
+      <c r="D580" s="98"/>
+      <c r="E580" s="98"/>
+      <c r="F580" s="98"/>
+      <c r="G580" s="98"/>
+      <c r="H580" s="89"/>
+      <c r="I580" s="89"/>
+      <c r="J580" s="89"/>
+      <c r="K580" s="89"/>
     </row>
     <row r="581" spans="1:12" s="24" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1"/>
       <c r="B581" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C581" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D581" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E581" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F581" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G581" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="H581" s="11"/>
-      <c r="I581" s="11"/>
-      <c r="J581" s="11"/>
-      <c r="K581" s="11"/>
+      <c r="C581" s="92" t="s">
+        <v>469</v>
+      </c>
+      <c r="D581" s="41" t="s">
+        <v>470</v>
+      </c>
+      <c r="E581" s="42" t="s">
+        <v>471</v>
+      </c>
+      <c r="F581" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="G581" s="93" t="s">
+        <v>473</v>
+      </c>
+      <c r="H581" s="90" t="s">
+        <v>464</v>
+      </c>
+      <c r="I581" s="90" t="s">
+        <v>465</v>
+      </c>
+      <c r="J581" s="90" t="s">
+        <v>466</v>
+      </c>
+      <c r="K581" s="90" t="s">
+        <v>468</v>
+      </c>
       <c r="L581" s="10"/>
     </row>
     <row r="582" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19439,13 +20428,19 @@
       <c r="D584" s="41"/>
       <c r="E584" s="42"/>
       <c r="F584" s="43"/>
-      <c r="G584" s="23">
-        <v>1</v>
-      </c>
-      <c r="H584" s="23"/>
-      <c r="I584" s="23"/>
-      <c r="J584" s="23"/>
-      <c r="K584" s="23"/>
+      <c r="G584" s="42">
+        <v>1</v>
+      </c>
+      <c r="H584" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I584" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J584" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K584" s="11"/>
       <c r="L584" s="43"/>
     </row>
     <row r="585" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -19459,11 +20454,17 @@
       <c r="D585" s="41"/>
       <c r="E585" s="42"/>
       <c r="F585" s="43"/>
-      <c r="G585" s="23"/>
-      <c r="H585" s="23"/>
-      <c r="I585" s="23"/>
-      <c r="J585" s="23"/>
-      <c r="K585" s="23"/>
+      <c r="G585" s="42"/>
+      <c r="H585" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I585" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J585" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K585" s="11"/>
       <c r="L585" s="43"/>
     </row>
     <row r="586" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19475,13 +20476,19 @@
       <c r="D586" s="41"/>
       <c r="E586" s="42"/>
       <c r="F586" s="43"/>
-      <c r="G586" s="23">
-        <v>1</v>
-      </c>
-      <c r="H586" s="23"/>
-      <c r="I586" s="23"/>
-      <c r="J586" s="23"/>
-      <c r="K586" s="23"/>
+      <c r="G586" s="42">
+        <v>1</v>
+      </c>
+      <c r="H586" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="I586" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="J586" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="K586" s="11"/>
       <c r="L586" s="43"/>
     </row>
     <row r="587" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19496,11 +20503,17 @@
       <c r="D587" s="41"/>
       <c r="E587" s="42"/>
       <c r="F587" s="43"/>
-      <c r="G587" s="23"/>
-      <c r="H587" s="23"/>
-      <c r="I587" s="23"/>
-      <c r="J587" s="23"/>
-      <c r="K587" s="23"/>
+      <c r="G587" s="42"/>
+      <c r="H587" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I587" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J587" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K587" s="11"/>
       <c r="L587" s="43"/>
     </row>
     <row r="588" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19510,11 +20523,11 @@
       <c r="D588" s="41"/>
       <c r="E588" s="42"/>
       <c r="F588" s="43"/>
-      <c r="G588" s="23"/>
-      <c r="H588" s="23"/>
-      <c r="I588" s="23"/>
-      <c r="J588" s="23"/>
-      <c r="K588" s="23"/>
+      <c r="G588" s="42"/>
+      <c r="H588" s="42"/>
+      <c r="I588" s="42"/>
+      <c r="J588" s="42"/>
+      <c r="K588" s="11"/>
       <c r="L588" s="43"/>
     </row>
     <row r="589" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19528,10 +20541,10 @@
       <c r="D589" s="8"/>
       <c r="E589" s="9"/>
       <c r="F589" s="10"/>
-      <c r="G589" s="11"/>
-      <c r="H589" s="11"/>
-      <c r="I589" s="11"/>
-      <c r="J589" s="11"/>
+      <c r="G589" s="42"/>
+      <c r="H589" s="42"/>
+      <c r="I589" s="42"/>
+      <c r="J589" s="42"/>
       <c r="K589" s="11"/>
       <c r="L589" s="10"/>
     </row>
@@ -19544,10 +20557,10 @@
       <c r="D590" s="8"/>
       <c r="E590" s="9"/>
       <c r="F590" s="10"/>
-      <c r="G590" s="11"/>
-      <c r="H590" s="11"/>
-      <c r="I590" s="11"/>
-      <c r="J590" s="11"/>
+      <c r="G590" s="42"/>
+      <c r="H590" s="42"/>
+      <c r="I590" s="42"/>
+      <c r="J590" s="42"/>
       <c r="K590" s="11"/>
       <c r="L590" s="10"/>
     </row>
@@ -19563,13 +20576,19 @@
       <c r="D591" s="41"/>
       <c r="E591" s="42"/>
       <c r="F591" s="43"/>
-      <c r="G591" s="23">
-        <v>1</v>
-      </c>
-      <c r="H591" s="23"/>
-      <c r="I591" s="23"/>
-      <c r="J591" s="23"/>
-      <c r="K591" s="23"/>
+      <c r="G591" s="42">
+        <v>1</v>
+      </c>
+      <c r="H591" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I591" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J591" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K591" s="11"/>
       <c r="L591" s="43"/>
     </row>
     <row r="592" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19584,11 +20603,17 @@
       <c r="D592" s="41"/>
       <c r="E592" s="42"/>
       <c r="F592" s="43"/>
-      <c r="G592" s="23"/>
-      <c r="H592" s="23"/>
-      <c r="I592" s="23"/>
-      <c r="J592" s="23"/>
-      <c r="K592" s="23"/>
+      <c r="G592" s="42"/>
+      <c r="H592" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I592" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J592" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K592" s="11"/>
       <c r="L592" s="43"/>
     </row>
     <row r="593" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -19599,13 +20624,19 @@
       <c r="D593" s="41"/>
       <c r="E593" s="42"/>
       <c r="F593" s="43"/>
-      <c r="G593" s="23">
-        <v>2</v>
-      </c>
-      <c r="H593" s="23"/>
-      <c r="I593" s="23"/>
-      <c r="J593" s="23"/>
-      <c r="K593" s="23"/>
+      <c r="G593" s="42">
+        <v>1</v>
+      </c>
+      <c r="H593" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="I593" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="J593" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="K593" s="11"/>
       <c r="L593" s="43"/>
     </row>
     <row r="594" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -19619,11 +20650,17 @@
       <c r="D594" s="41"/>
       <c r="E594" s="42"/>
       <c r="F594" s="43"/>
-      <c r="G594" s="23"/>
-      <c r="H594" s="23"/>
-      <c r="I594" s="23"/>
-      <c r="J594" s="23"/>
-      <c r="K594" s="23"/>
+      <c r="G594" s="42"/>
+      <c r="H594" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I594" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J594" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K594" s="11"/>
       <c r="L594" s="43"/>
     </row>
     <row r="595" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19633,11 +20670,11 @@
       <c r="D595" s="29"/>
       <c r="E595" s="30"/>
       <c r="F595" s="31"/>
-      <c r="G595" s="32"/>
-      <c r="H595" s="32"/>
-      <c r="I595" s="32"/>
-      <c r="J595" s="32"/>
-      <c r="K595" s="32"/>
+      <c r="G595" s="42"/>
+      <c r="H595" s="42"/>
+      <c r="I595" s="42"/>
+      <c r="J595" s="42"/>
+      <c r="K595" s="11"/>
       <c r="L595" s="31"/>
     </row>
     <row r="596" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19651,10 +20688,10 @@
       <c r="D596" s="8"/>
       <c r="E596" s="9"/>
       <c r="F596" s="10"/>
-      <c r="G596" s="11"/>
-      <c r="H596" s="11"/>
-      <c r="I596" s="11"/>
-      <c r="J596" s="11"/>
+      <c r="G596" s="42"/>
+      <c r="H596" s="42"/>
+      <c r="I596" s="42"/>
+      <c r="J596" s="42"/>
       <c r="K596" s="11"/>
       <c r="L596" s="10"/>
     </row>
@@ -19667,10 +20704,10 @@
       <c r="D597" s="8"/>
       <c r="E597" s="9"/>
       <c r="F597" s="10"/>
-      <c r="G597" s="11"/>
-      <c r="H597" s="11"/>
-      <c r="I597" s="11"/>
-      <c r="J597" s="11"/>
+      <c r="G597" s="42"/>
+      <c r="H597" s="42"/>
+      <c r="I597" s="42"/>
+      <c r="J597" s="42"/>
       <c r="K597" s="11"/>
       <c r="L597" s="10"/>
     </row>
@@ -19685,11 +20722,17 @@
       </c>
       <c r="E598" s="21"/>
       <c r="F598" s="22"/>
-      <c r="G598" s="23"/>
-      <c r="H598" s="23"/>
-      <c r="I598" s="23"/>
-      <c r="J598" s="23"/>
-      <c r="K598" s="23"/>
+      <c r="G598" s="42"/>
+      <c r="H598" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I598" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J598" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K598" s="11"/>
       <c r="L598" s="22"/>
     </row>
     <row r="599" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19703,11 +20746,17 @@
       <c r="D599" s="20"/>
       <c r="E599" s="21"/>
       <c r="F599" s="22"/>
-      <c r="G599" s="23"/>
-      <c r="H599" s="23"/>
-      <c r="I599" s="23"/>
-      <c r="J599" s="23"/>
-      <c r="K599" s="23"/>
+      <c r="G599" s="42"/>
+      <c r="H599" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I599" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J599" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K599" s="11"/>
       <c r="L599" s="22"/>
     </row>
     <row r="600" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -19720,11 +20769,17 @@
       <c r="D600" s="20"/>
       <c r="E600" s="21"/>
       <c r="F600" s="22"/>
-      <c r="G600" s="23"/>
-      <c r="H600" s="23"/>
-      <c r="I600" s="23"/>
-      <c r="J600" s="23"/>
-      <c r="K600" s="23"/>
+      <c r="G600" s="42"/>
+      <c r="H600" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I600" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J600" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K600" s="11"/>
       <c r="L600" s="22"/>
     </row>
     <row r="601" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -19737,11 +20792,17 @@
       <c r="D601" s="20"/>
       <c r="E601" s="21"/>
       <c r="F601" s="22"/>
-      <c r="G601" s="23"/>
-      <c r="H601" s="23"/>
-      <c r="I601" s="23"/>
-      <c r="J601" s="23"/>
-      <c r="K601" s="23"/>
+      <c r="G601" s="42"/>
+      <c r="H601" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I601" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J601" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K601" s="11"/>
       <c r="L601" s="22"/>
     </row>
     <row r="602" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19757,11 +20818,17 @@
       <c r="F602" s="64">
         <v>1</v>
       </c>
-      <c r="G602" s="23"/>
-      <c r="H602" s="23"/>
-      <c r="I602" s="23"/>
-      <c r="J602" s="23"/>
-      <c r="K602" s="23"/>
+      <c r="G602" s="42"/>
+      <c r="H602" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I602" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J602" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K602" s="11"/>
       <c r="L602" s="64"/>
     </row>
     <row r="603" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19775,11 +20842,17 @@
       <c r="D603" s="20"/>
       <c r="E603" s="21"/>
       <c r="F603" s="64"/>
-      <c r="G603" s="23"/>
-      <c r="H603" s="23"/>
-      <c r="I603" s="23"/>
-      <c r="J603" s="23"/>
-      <c r="K603" s="23"/>
+      <c r="G603" s="42"/>
+      <c r="H603" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I603" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J603" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K603" s="11"/>
       <c r="L603" s="64"/>
     </row>
     <row r="604" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19793,11 +20866,17 @@
       <c r="D604" s="20"/>
       <c r="E604" s="21"/>
       <c r="F604" s="64"/>
-      <c r="G604" s="23"/>
-      <c r="H604" s="23"/>
-      <c r="I604" s="23"/>
-      <c r="J604" s="23"/>
-      <c r="K604" s="23"/>
+      <c r="G604" s="42"/>
+      <c r="H604" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I604" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J604" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K604" s="11"/>
       <c r="L604" s="64"/>
     </row>
     <row r="605" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19811,11 +20890,17 @@
       <c r="D605" s="20"/>
       <c r="E605" s="21"/>
       <c r="F605" s="64"/>
-      <c r="G605" s="23"/>
-      <c r="H605" s="23"/>
-      <c r="I605" s="23"/>
-      <c r="J605" s="23"/>
-      <c r="K605" s="23"/>
+      <c r="G605" s="42"/>
+      <c r="H605" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I605" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J605" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K605" s="11"/>
       <c r="L605" s="64"/>
     </row>
     <row r="606" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19831,11 +20916,17 @@
       <c r="F606" s="64">
         <v>1</v>
       </c>
-      <c r="G606" s="23"/>
-      <c r="H606" s="23"/>
-      <c r="I606" s="23"/>
-      <c r="J606" s="23"/>
-      <c r="K606" s="23"/>
+      <c r="G606" s="42"/>
+      <c r="H606" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I606" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J606" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K606" s="11"/>
       <c r="L606" s="64"/>
     </row>
     <row r="607" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19849,11 +20940,17 @@
       <c r="D607" s="20"/>
       <c r="E607" s="21"/>
       <c r="F607" s="22"/>
-      <c r="G607" s="23"/>
-      <c r="H607" s="23"/>
-      <c r="I607" s="23"/>
-      <c r="J607" s="23"/>
-      <c r="K607" s="23"/>
+      <c r="G607" s="42"/>
+      <c r="H607" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I607" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J607" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K607" s="11"/>
       <c r="L607" s="22"/>
     </row>
     <row r="608" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19867,11 +20964,17 @@
       <c r="D608" s="20"/>
       <c r="E608" s="21"/>
       <c r="F608" s="22"/>
-      <c r="G608" s="23"/>
-      <c r="H608" s="23"/>
-      <c r="I608" s="23"/>
-      <c r="J608" s="23"/>
-      <c r="K608" s="23"/>
+      <c r="G608" s="42"/>
+      <c r="H608" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I608" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J608" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K608" s="11"/>
       <c r="L608" s="22"/>
     </row>
     <row r="609" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19885,11 +20988,17 @@
       <c r="D609" s="20"/>
       <c r="E609" s="21"/>
       <c r="F609" s="22"/>
-      <c r="G609" s="23"/>
-      <c r="H609" s="23"/>
-      <c r="I609" s="23"/>
-      <c r="J609" s="23"/>
-      <c r="K609" s="23"/>
+      <c r="G609" s="42"/>
+      <c r="H609" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I609" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J609" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K609" s="11"/>
       <c r="L609" s="22"/>
     </row>
     <row r="610" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19899,11 +21008,11 @@
       <c r="D610" s="20"/>
       <c r="E610" s="21"/>
       <c r="F610" s="22"/>
-      <c r="G610" s="23"/>
-      <c r="H610" s="23"/>
-      <c r="I610" s="23"/>
-      <c r="J610" s="23"/>
-      <c r="K610" s="23"/>
+      <c r="G610" s="42"/>
+      <c r="H610" s="42"/>
+      <c r="I610" s="42"/>
+      <c r="J610" s="42"/>
+      <c r="K610" s="11"/>
       <c r="L610" s="22"/>
     </row>
     <row r="611" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19917,10 +21026,10 @@
       <c r="D611" s="8"/>
       <c r="E611" s="9"/>
       <c r="F611" s="10"/>
-      <c r="G611" s="11"/>
-      <c r="H611" s="11"/>
-      <c r="I611" s="11"/>
-      <c r="J611" s="11"/>
+      <c r="G611" s="42"/>
+      <c r="H611" s="42"/>
+      <c r="I611" s="42"/>
+      <c r="J611" s="42"/>
       <c r="K611" s="11"/>
       <c r="L611" s="10"/>
     </row>
@@ -19933,10 +21042,10 @@
       <c r="D612" s="8"/>
       <c r="E612" s="9"/>
       <c r="F612" s="10"/>
-      <c r="G612" s="11"/>
-      <c r="H612" s="11"/>
-      <c r="I612" s="11"/>
-      <c r="J612" s="11"/>
+      <c r="G612" s="42"/>
+      <c r="H612" s="42"/>
+      <c r="I612" s="42"/>
+      <c r="J612" s="42"/>
       <c r="K612" s="11"/>
       <c r="L612" s="10"/>
     </row>
@@ -19951,11 +21060,17 @@
       </c>
       <c r="E613" s="21"/>
       <c r="F613" s="22"/>
-      <c r="G613" s="23"/>
-      <c r="H613" s="23"/>
-      <c r="I613" s="23"/>
-      <c r="J613" s="23"/>
-      <c r="K613" s="23"/>
+      <c r="G613" s="42"/>
+      <c r="H613" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I613" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J613" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K613" s="11"/>
       <c r="L613" s="22"/>
     </row>
     <row r="614" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19969,11 +21084,17 @@
       <c r="D614" s="20"/>
       <c r="E614" s="21"/>
       <c r="F614" s="22"/>
-      <c r="G614" s="23"/>
-      <c r="H614" s="23"/>
-      <c r="I614" s="23"/>
-      <c r="J614" s="23"/>
-      <c r="K614" s="23"/>
+      <c r="G614" s="42"/>
+      <c r="H614" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I614" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J614" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K614" s="11"/>
       <c r="L614" s="22"/>
     </row>
     <row r="615" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19987,11 +21108,17 @@
       <c r="D615" s="20"/>
       <c r="E615" s="21"/>
       <c r="F615" s="22"/>
-      <c r="G615" s="23"/>
-      <c r="H615" s="23"/>
-      <c r="I615" s="23"/>
-      <c r="J615" s="23"/>
-      <c r="K615" s="23"/>
+      <c r="G615" s="42"/>
+      <c r="H615" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I615" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J615" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K615" s="11"/>
       <c r="L615" s="22"/>
     </row>
     <row r="616" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20005,11 +21132,17 @@
       <c r="D616" s="20"/>
       <c r="E616" s="21"/>
       <c r="F616" s="22"/>
-      <c r="G616" s="23"/>
-      <c r="H616" s="23"/>
-      <c r="I616" s="23"/>
-      <c r="J616" s="23"/>
-      <c r="K616" s="23"/>
+      <c r="G616" s="42"/>
+      <c r="H616" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I616" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J616" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K616" s="11"/>
       <c r="L616" s="22"/>
     </row>
     <row r="617" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20025,11 +21158,17 @@
       <c r="F617" s="64">
         <v>1</v>
       </c>
-      <c r="G617" s="23"/>
-      <c r="H617" s="23"/>
-      <c r="I617" s="23"/>
-      <c r="J617" s="23"/>
-      <c r="K617" s="23"/>
+      <c r="G617" s="42"/>
+      <c r="H617" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I617" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J617" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K617" s="11"/>
       <c r="L617" s="64"/>
     </row>
     <row r="618" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20043,11 +21182,17 @@
       <c r="D618" s="20"/>
       <c r="E618" s="21"/>
       <c r="F618" s="64"/>
-      <c r="G618" s="23"/>
-      <c r="H618" s="23"/>
-      <c r="I618" s="23"/>
-      <c r="J618" s="23"/>
-      <c r="K618" s="23"/>
+      <c r="G618" s="42"/>
+      <c r="H618" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I618" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J618" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K618" s="11"/>
       <c r="L618" s="64"/>
     </row>
     <row r="619" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20061,11 +21206,17 @@
       <c r="D619" s="20"/>
       <c r="E619" s="21"/>
       <c r="F619" s="64"/>
-      <c r="G619" s="23"/>
-      <c r="H619" s="23"/>
-      <c r="I619" s="23"/>
-      <c r="J619" s="23"/>
-      <c r="K619" s="23"/>
+      <c r="G619" s="42"/>
+      <c r="H619" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I619" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J619" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K619" s="11"/>
       <c r="L619" s="64"/>
     </row>
     <row r="620" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20079,11 +21230,17 @@
       <c r="D620" s="20"/>
       <c r="E620" s="21"/>
       <c r="F620" s="64"/>
-      <c r="G620" s="23"/>
-      <c r="H620" s="23"/>
-      <c r="I620" s="23"/>
-      <c r="J620" s="23"/>
-      <c r="K620" s="23"/>
+      <c r="G620" s="42"/>
+      <c r="H620" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I620" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J620" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K620" s="11"/>
       <c r="L620" s="64"/>
     </row>
     <row r="621" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20099,11 +21256,17 @@
       <c r="F621" s="64">
         <v>1</v>
       </c>
-      <c r="G621" s="23"/>
-      <c r="H621" s="23"/>
-      <c r="I621" s="23"/>
-      <c r="J621" s="23"/>
-      <c r="K621" s="23"/>
+      <c r="G621" s="42"/>
+      <c r="H621" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I621" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J621" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K621" s="11"/>
       <c r="L621" s="64"/>
     </row>
     <row r="622" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20117,11 +21280,17 @@
       <c r="D622" s="20"/>
       <c r="E622" s="21"/>
       <c r="F622" s="22"/>
-      <c r="G622" s="23"/>
-      <c r="H622" s="23"/>
-      <c r="I622" s="23"/>
-      <c r="J622" s="23"/>
-      <c r="K622" s="23"/>
+      <c r="G622" s="42"/>
+      <c r="H622" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I622" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J622" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K622" s="11"/>
       <c r="L622" s="22"/>
     </row>
     <row r="623" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20135,11 +21304,17 @@
       <c r="D623" s="20"/>
       <c r="E623" s="21"/>
       <c r="F623" s="22"/>
-      <c r="G623" s="23"/>
-      <c r="H623" s="23"/>
-      <c r="I623" s="23"/>
-      <c r="J623" s="23"/>
-      <c r="K623" s="23"/>
+      <c r="G623" s="42"/>
+      <c r="H623" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I623" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J623" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K623" s="11"/>
       <c r="L623" s="22"/>
     </row>
     <row r="624" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20153,11 +21328,17 @@
       <c r="D624" s="20"/>
       <c r="E624" s="21"/>
       <c r="F624" s="22"/>
-      <c r="G624" s="23"/>
-      <c r="H624" s="23"/>
-      <c r="I624" s="23"/>
-      <c r="J624" s="23"/>
-      <c r="K624" s="23"/>
+      <c r="G624" s="42"/>
+      <c r="H624" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I624" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J624" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K624" s="11"/>
       <c r="L624" s="22"/>
     </row>
     <row r="625" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20167,11 +21348,11 @@
       <c r="D625" s="20"/>
       <c r="E625" s="21"/>
       <c r="F625" s="22"/>
-      <c r="G625" s="23"/>
-      <c r="H625" s="23"/>
-      <c r="I625" s="23"/>
-      <c r="J625" s="23"/>
-      <c r="K625" s="23"/>
+      <c r="G625" s="42"/>
+      <c r="H625" s="42"/>
+      <c r="I625" s="42"/>
+      <c r="J625" s="42"/>
+      <c r="K625" s="11"/>
       <c r="L625" s="22"/>
     </row>
     <row r="626" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20185,10 +21366,10 @@
       <c r="D626" s="8"/>
       <c r="E626" s="9"/>
       <c r="F626" s="10"/>
-      <c r="G626" s="11"/>
-      <c r="H626" s="11"/>
-      <c r="I626" s="11"/>
-      <c r="J626" s="11"/>
+      <c r="G626" s="42"/>
+      <c r="H626" s="42"/>
+      <c r="I626" s="42"/>
+      <c r="J626" s="42"/>
       <c r="K626" s="11"/>
       <c r="L626" s="10"/>
     </row>
@@ -20201,10 +21382,10 @@
       <c r="D627" s="8"/>
       <c r="E627" s="9"/>
       <c r="F627" s="10"/>
-      <c r="G627" s="11"/>
-      <c r="H627" s="11"/>
-      <c r="I627" s="11"/>
-      <c r="J627" s="11"/>
+      <c r="G627" s="42"/>
+      <c r="H627" s="42"/>
+      <c r="I627" s="42"/>
+      <c r="J627" s="42"/>
       <c r="K627" s="11"/>
       <c r="L627" s="10"/>
     </row>
@@ -20219,11 +21400,17 @@
       <c r="D628" s="41"/>
       <c r="E628" s="42"/>
       <c r="F628" s="43"/>
-      <c r="G628" s="23"/>
-      <c r="H628" s="23"/>
-      <c r="I628" s="23"/>
-      <c r="J628" s="23"/>
-      <c r="K628" s="23"/>
+      <c r="G628" s="42"/>
+      <c r="H628" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I628" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J628" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K628" s="11"/>
       <c r="L628" s="43"/>
     </row>
     <row r="629" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -20237,11 +21424,17 @@
       <c r="D629" s="41"/>
       <c r="E629" s="42"/>
       <c r="F629" s="43"/>
-      <c r="G629" s="23"/>
-      <c r="H629" s="23"/>
-      <c r="I629" s="23"/>
-      <c r="J629" s="23"/>
-      <c r="K629" s="23"/>
+      <c r="G629" s="42"/>
+      <c r="H629" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I629" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J629" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K629" s="11"/>
       <c r="L629" s="43"/>
     </row>
     <row r="630" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20251,11 +21444,11 @@
       <c r="D630" s="29"/>
       <c r="E630" s="30"/>
       <c r="F630" s="31"/>
-      <c r="G630" s="32"/>
-      <c r="H630" s="32"/>
-      <c r="I630" s="32"/>
-      <c r="J630" s="32"/>
-      <c r="K630" s="32"/>
+      <c r="G630" s="42"/>
+      <c r="H630" s="42"/>
+      <c r="I630" s="42"/>
+      <c r="J630" s="42"/>
+      <c r="K630" s="11"/>
       <c r="L630" s="31"/>
     </row>
     <row r="631" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20269,10 +21462,10 @@
       <c r="D631" s="8"/>
       <c r="E631" s="9"/>
       <c r="F631" s="10"/>
-      <c r="G631" s="11"/>
-      <c r="H631" s="11"/>
-      <c r="I631" s="11"/>
-      <c r="J631" s="11"/>
+      <c r="G631" s="42"/>
+      <c r="H631" s="42"/>
+      <c r="I631" s="42"/>
+      <c r="J631" s="42"/>
       <c r="K631" s="11"/>
       <c r="L631" s="10"/>
     </row>
@@ -20285,10 +21478,10 @@
       <c r="D632" s="8"/>
       <c r="E632" s="9"/>
       <c r="F632" s="10"/>
-      <c r="G632" s="11"/>
-      <c r="H632" s="11"/>
-      <c r="I632" s="11"/>
-      <c r="J632" s="11"/>
+      <c r="G632" s="42"/>
+      <c r="H632" s="42"/>
+      <c r="I632" s="42"/>
+      <c r="J632" s="42"/>
       <c r="K632" s="11"/>
       <c r="L632" s="10"/>
     </row>
@@ -20303,11 +21496,17 @@
       <c r="D633" s="41"/>
       <c r="E633" s="42"/>
       <c r="F633" s="43"/>
-      <c r="G633" s="23"/>
-      <c r="H633" s="23"/>
-      <c r="I633" s="23"/>
-      <c r="J633" s="23"/>
-      <c r="K633" s="23"/>
+      <c r="G633" s="42"/>
+      <c r="H633" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I633" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J633" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K633" s="11"/>
       <c r="L633" s="43"/>
     </row>
     <row r="634" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20321,11 +21520,17 @@
       <c r="D634" s="41"/>
       <c r="E634" s="42"/>
       <c r="F634" s="43"/>
-      <c r="G634" s="23"/>
-      <c r="H634" s="23"/>
-      <c r="I634" s="23"/>
-      <c r="J634" s="23"/>
-      <c r="K634" s="23"/>
+      <c r="G634" s="42"/>
+      <c r="H634" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I634" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J634" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K634" s="11"/>
       <c r="L634" s="43"/>
     </row>
     <row r="635" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20335,11 +21540,11 @@
       <c r="D635" s="29"/>
       <c r="E635" s="30"/>
       <c r="F635" s="31"/>
-      <c r="G635" s="32"/>
-      <c r="H635" s="32"/>
-      <c r="I635" s="32"/>
-      <c r="J635" s="32"/>
-      <c r="K635" s="32"/>
+      <c r="G635" s="42"/>
+      <c r="H635" s="42"/>
+      <c r="I635" s="42"/>
+      <c r="J635" s="42"/>
+      <c r="K635" s="11"/>
       <c r="L635" s="31"/>
     </row>
     <row r="636" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -20353,10 +21558,10 @@
       <c r="D636" s="8"/>
       <c r="E636" s="9"/>
       <c r="F636" s="10"/>
-      <c r="G636" s="11"/>
-      <c r="H636" s="11"/>
-      <c r="I636" s="11"/>
-      <c r="J636" s="11"/>
+      <c r="G636" s="42"/>
+      <c r="H636" s="42"/>
+      <c r="I636" s="42"/>
+      <c r="J636" s="42"/>
       <c r="K636" s="11"/>
       <c r="L636" s="10"/>
     </row>
@@ -20367,10 +21572,10 @@
       <c r="D637" s="8"/>
       <c r="E637" s="9"/>
       <c r="F637" s="10"/>
-      <c r="G637" s="11"/>
-      <c r="H637" s="11"/>
-      <c r="I637" s="11"/>
-      <c r="J637" s="11"/>
+      <c r="G637" s="42"/>
+      <c r="H637" s="42"/>
+      <c r="I637" s="42"/>
+      <c r="J637" s="42"/>
       <c r="K637" s="11"/>
       <c r="L637" s="10"/>
     </row>
@@ -20385,11 +21590,17 @@
         <v>2</v>
       </c>
       <c r="F638" s="43"/>
-      <c r="G638" s="23"/>
-      <c r="H638" s="23"/>
-      <c r="I638" s="23"/>
-      <c r="J638" s="23"/>
-      <c r="K638" s="23"/>
+      <c r="G638" s="42"/>
+      <c r="H638" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="I638" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="J638" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="K638" s="11"/>
       <c r="L638" s="43"/>
     </row>
     <row r="639" spans="1:12" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20399,11 +21610,11 @@
       <c r="D639" s="29"/>
       <c r="E639" s="30"/>
       <c r="F639" s="31"/>
-      <c r="G639" s="32"/>
-      <c r="H639" s="32"/>
-      <c r="I639" s="32"/>
-      <c r="J639" s="32"/>
-      <c r="K639" s="32"/>
+      <c r="G639" s="42"/>
+      <c r="H639" s="42"/>
+      <c r="I639" s="42"/>
+      <c r="J639" s="42"/>
+      <c r="K639" s="11"/>
       <c r="L639" s="31"/>
     </row>
     <row r="640" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20429,7 +21640,7 @@
       </c>
       <c r="G640" s="46">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H640" s="46"/>
       <c r="I640" s="46"/>
@@ -20458,17 +21669,17 @@
       <c r="B642" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C642" s="90" t="s">
+      <c r="C642" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D642" s="90"/>
-      <c r="E642" s="90"/>
-      <c r="F642" s="90"/>
-      <c r="G642" s="90"/>
-      <c r="H642" s="95"/>
-      <c r="I642" s="95"/>
-      <c r="J642" s="95"/>
-      <c r="K642" s="95"/>
+      <c r="D642" s="98"/>
+      <c r="E642" s="98"/>
+      <c r="F642" s="98"/>
+      <c r="G642" s="98"/>
+      <c r="H642" s="89"/>
+      <c r="I642" s="89"/>
+      <c r="J642" s="89"/>
+      <c r="K642" s="89"/>
       <c r="L642" s="15"/>
     </row>
     <row r="643" spans="1:12" s="24" customFormat="1" ht="106.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -21581,17 +22792,17 @@
       <c r="B705" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C705" s="90" t="s">
+      <c r="C705" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D705" s="90"/>
-      <c r="E705" s="90"/>
-      <c r="F705" s="90"/>
-      <c r="G705" s="90"/>
-      <c r="H705" s="95"/>
-      <c r="I705" s="95"/>
-      <c r="J705" s="95"/>
-      <c r="K705" s="95"/>
+      <c r="D705" s="98"/>
+      <c r="E705" s="98"/>
+      <c r="F705" s="98"/>
+      <c r="G705" s="98"/>
+      <c r="H705" s="89"/>
+      <c r="I705" s="89"/>
+      <c r="J705" s="89"/>
+      <c r="K705" s="89"/>
     </row>
     <row r="706" spans="1:12" s="24" customFormat="1" ht="93.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="1"/>
@@ -22416,17 +23627,17 @@
       <c r="B754" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C754" s="90" t="s">
+      <c r="C754" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D754" s="90"/>
-      <c r="E754" s="90"/>
-      <c r="F754" s="90"/>
-      <c r="G754" s="90"/>
-      <c r="H754" s="95"/>
-      <c r="I754" s="95"/>
-      <c r="J754" s="95"/>
-      <c r="K754" s="95"/>
+      <c r="D754" s="98"/>
+      <c r="E754" s="98"/>
+      <c r="F754" s="98"/>
+      <c r="G754" s="98"/>
+      <c r="H754" s="89"/>
+      <c r="I754" s="89"/>
+      <c r="J754" s="89"/>
+      <c r="K754" s="89"/>
       <c r="L754" s="15"/>
     </row>
     <row r="755" spans="1:12" s="24" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.25">
@@ -23651,17 +24862,17 @@
       <c r="B825" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C825" s="90" t="s">
+      <c r="C825" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D825" s="90"/>
-      <c r="E825" s="90"/>
-      <c r="F825" s="90"/>
-      <c r="G825" s="90"/>
-      <c r="H825" s="95"/>
-      <c r="I825" s="95"/>
-      <c r="J825" s="95"/>
-      <c r="K825" s="95"/>
+      <c r="D825" s="98"/>
+      <c r="E825" s="98"/>
+      <c r="F825" s="98"/>
+      <c r="G825" s="98"/>
+      <c r="H825" s="89"/>
+      <c r="I825" s="89"/>
+      <c r="J825" s="89"/>
+      <c r="K825" s="89"/>
     </row>
     <row r="826" spans="1:12" s="24" customFormat="1" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="1"/>
@@ -24804,17 +26015,17 @@
       <c r="B892" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C892" s="90" t="s">
+      <c r="C892" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D892" s="90"/>
-      <c r="E892" s="90"/>
-      <c r="F892" s="90"/>
-      <c r="G892" s="90"/>
-      <c r="H892" s="95"/>
-      <c r="I892" s="95"/>
-      <c r="J892" s="95"/>
-      <c r="K892" s="95"/>
+      <c r="D892" s="98"/>
+      <c r="E892" s="98"/>
+      <c r="F892" s="98"/>
+      <c r="G892" s="98"/>
+      <c r="H892" s="89"/>
+      <c r="I892" s="89"/>
+      <c r="J892" s="89"/>
+      <c r="K892" s="89"/>
       <c r="L892" s="15"/>
     </row>
     <row r="893" spans="1:12" s="24" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.25">
@@ -25250,30 +26461,30 @@
       <c r="B918" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="C918" s="91"/>
-      <c r="D918" s="92"/>
-      <c r="E918" s="93"/>
-      <c r="F918" s="89"/>
-      <c r="G918" s="94"/>
+      <c r="C918" s="100"/>
+      <c r="D918" s="101"/>
+      <c r="E918" s="102"/>
+      <c r="F918" s="97"/>
+      <c r="G918" s="99"/>
       <c r="H918" s="76"/>
       <c r="I918" s="76"/>
       <c r="J918" s="76"/>
       <c r="K918" s="76"/>
-      <c r="L918" s="89"/>
+      <c r="L918" s="97"/>
     </row>
     <row r="919" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A919" s="59"/>
       <c r="B919" s="66"/>
-      <c r="C919" s="91"/>
-      <c r="D919" s="92"/>
-      <c r="E919" s="93"/>
-      <c r="F919" s="89"/>
-      <c r="G919" s="94"/>
+      <c r="C919" s="100"/>
+      <c r="D919" s="101"/>
+      <c r="E919" s="102"/>
+      <c r="F919" s="97"/>
+      <c r="G919" s="99"/>
       <c r="H919" s="76"/>
       <c r="I919" s="76"/>
       <c r="J919" s="76"/>
       <c r="K919" s="76"/>
-      <c r="L919" s="89"/>
+      <c r="L919" s="97"/>
     </row>
     <row r="920" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="59"/>
@@ -25454,17 +26665,17 @@
       <c r="B929" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C929" s="90" t="s">
+      <c r="C929" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D929" s="90"/>
-      <c r="E929" s="90"/>
-      <c r="F929" s="90"/>
-      <c r="G929" s="90"/>
-      <c r="H929" s="95"/>
-      <c r="I929" s="95"/>
-      <c r="J929" s="95"/>
-      <c r="K929" s="95"/>
+      <c r="D929" s="98"/>
+      <c r="E929" s="98"/>
+      <c r="F929" s="98"/>
+      <c r="G929" s="98"/>
+      <c r="H929" s="89"/>
+      <c r="I929" s="89"/>
+      <c r="J929" s="89"/>
+      <c r="K929" s="89"/>
     </row>
     <row r="930" spans="1:12" s="33" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="1"/>
@@ -25719,30 +26930,30 @@
       <c r="B944" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="C944" s="91"/>
-      <c r="D944" s="92"/>
-      <c r="E944" s="93"/>
-      <c r="F944" s="89"/>
-      <c r="G944" s="94"/>
+      <c r="C944" s="100"/>
+      <c r="D944" s="101"/>
+      <c r="E944" s="102"/>
+      <c r="F944" s="97"/>
+      <c r="G944" s="99"/>
       <c r="H944" s="76"/>
       <c r="I944" s="76"/>
       <c r="J944" s="76"/>
       <c r="K944" s="76"/>
-      <c r="L944" s="89"/>
+      <c r="L944" s="97"/>
     </row>
     <row r="945" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A945" s="59"/>
       <c r="B945" s="66"/>
-      <c r="C945" s="91"/>
-      <c r="D945" s="92"/>
-      <c r="E945" s="93"/>
-      <c r="F945" s="89"/>
-      <c r="G945" s="94"/>
+      <c r="C945" s="100"/>
+      <c r="D945" s="101"/>
+      <c r="E945" s="102"/>
+      <c r="F945" s="97"/>
+      <c r="G945" s="99"/>
       <c r="H945" s="76"/>
       <c r="I945" s="76"/>
       <c r="J945" s="76"/>
       <c r="K945" s="76"/>
-      <c r="L945" s="89"/>
+      <c r="L945" s="97"/>
     </row>
     <row r="946" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="59"/>
@@ -25886,17 +27097,17 @@
       <c r="B953" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C953" s="90" t="s">
+      <c r="C953" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D953" s="90"/>
-      <c r="E953" s="90"/>
-      <c r="F953" s="90"/>
-      <c r="G953" s="90"/>
-      <c r="H953" s="95"/>
-      <c r="I953" s="95"/>
-      <c r="J953" s="95"/>
-      <c r="K953" s="95"/>
+      <c r="D953" s="98"/>
+      <c r="E953" s="98"/>
+      <c r="F953" s="98"/>
+      <c r="G953" s="98"/>
+      <c r="H953" s="89"/>
+      <c r="I953" s="89"/>
+      <c r="J953" s="89"/>
+      <c r="K953" s="89"/>
     </row>
     <row r="954" spans="1:12" s="33" customFormat="1" ht="94.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="1"/>
@@ -25931,30 +27142,30 @@
       <c r="B955" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="C955" s="91"/>
-      <c r="D955" s="92"/>
-      <c r="E955" s="93"/>
-      <c r="F955" s="89"/>
-      <c r="G955" s="94"/>
+      <c r="C955" s="100"/>
+      <c r="D955" s="101"/>
+      <c r="E955" s="102"/>
+      <c r="F955" s="97"/>
+      <c r="G955" s="99"/>
       <c r="H955" s="76"/>
       <c r="I955" s="76"/>
       <c r="J955" s="76"/>
       <c r="K955" s="76"/>
-      <c r="L955" s="89"/>
+      <c r="L955" s="97"/>
     </row>
     <row r="956" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A956" s="59"/>
       <c r="B956" s="66"/>
-      <c r="C956" s="91"/>
-      <c r="D956" s="92"/>
-      <c r="E956" s="93"/>
-      <c r="F956" s="89"/>
-      <c r="G956" s="94"/>
+      <c r="C956" s="100"/>
+      <c r="D956" s="101"/>
+      <c r="E956" s="102"/>
+      <c r="F956" s="97"/>
+      <c r="G956" s="99"/>
       <c r="H956" s="76"/>
       <c r="I956" s="76"/>
       <c r="J956" s="76"/>
       <c r="K956" s="76"/>
-      <c r="L956" s="89"/>
+      <c r="L956" s="97"/>
     </row>
     <row r="957" spans="1:12" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="59"/>
@@ -26098,17 +27309,17 @@
       <c r="B964" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C964" s="90" t="s">
+      <c r="C964" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D964" s="90"/>
-      <c r="E964" s="90"/>
-      <c r="F964" s="90"/>
-      <c r="G964" s="90"/>
-      <c r="H964" s="95"/>
-      <c r="I964" s="95"/>
-      <c r="J964" s="95"/>
-      <c r="K964" s="95"/>
+      <c r="D964" s="98"/>
+      <c r="E964" s="98"/>
+      <c r="F964" s="98"/>
+      <c r="G964" s="98"/>
+      <c r="H964" s="89"/>
+      <c r="I964" s="89"/>
+      <c r="J964" s="89"/>
+      <c r="K964" s="89"/>
       <c r="L964" s="15"/>
     </row>
     <row r="965" spans="1:12" ht="55.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -26144,30 +27355,30 @@
       <c r="B966" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="C966" s="91"/>
-      <c r="D966" s="92"/>
-      <c r="E966" s="93"/>
-      <c r="F966" s="89"/>
-      <c r="G966" s="94"/>
+      <c r="C966" s="100"/>
+      <c r="D966" s="101"/>
+      <c r="E966" s="102"/>
+      <c r="F966" s="97"/>
+      <c r="G966" s="99"/>
       <c r="H966" s="76"/>
       <c r="I966" s="76"/>
       <c r="J966" s="76"/>
       <c r="K966" s="76"/>
-      <c r="L966" s="89"/>
+      <c r="L966" s="97"/>
     </row>
     <row r="967" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A967" s="59"/>
       <c r="B967" s="66"/>
-      <c r="C967" s="91"/>
-      <c r="D967" s="92"/>
-      <c r="E967" s="93"/>
-      <c r="F967" s="89"/>
-      <c r="G967" s="94"/>
+      <c r="C967" s="100"/>
+      <c r="D967" s="101"/>
+      <c r="E967" s="102"/>
+      <c r="F967" s="97"/>
+      <c r="G967" s="99"/>
       <c r="H967" s="76"/>
       <c r="I967" s="76"/>
       <c r="J967" s="76"/>
       <c r="K967" s="76"/>
-      <c r="L967" s="89"/>
+      <c r="L967" s="97"/>
     </row>
     <row r="968" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A968" s="59"/>
@@ -26310,17 +27521,17 @@
       <c r="B975" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C975" s="90" t="s">
+      <c r="C975" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D975" s="90"/>
-      <c r="E975" s="90"/>
-      <c r="F975" s="90"/>
-      <c r="G975" s="90"/>
-      <c r="H975" s="95"/>
-      <c r="I975" s="95"/>
-      <c r="J975" s="95"/>
-      <c r="K975" s="95"/>
+      <c r="D975" s="98"/>
+      <c r="E975" s="98"/>
+      <c r="F975" s="98"/>
+      <c r="G975" s="98"/>
+      <c r="H975" s="89"/>
+      <c r="I975" s="89"/>
+      <c r="J975" s="89"/>
+      <c r="K975" s="89"/>
     </row>
     <row r="976" spans="1:12" s="33" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="1"/>
@@ -27712,38 +28923,6 @@
   </sheetData>
   <autoFilter ref="A11:BO987"/>
   <mergeCells count="48">
-    <mergeCell ref="H192:K192"/>
-    <mergeCell ref="H166:K166"/>
-    <mergeCell ref="F944:F945"/>
-    <mergeCell ref="C929:G929"/>
-    <mergeCell ref="G944:G945"/>
-    <mergeCell ref="C964:G964"/>
-    <mergeCell ref="C966:C967"/>
-    <mergeCell ref="D966:D967"/>
-    <mergeCell ref="E966:E967"/>
-    <mergeCell ref="F966:F967"/>
-    <mergeCell ref="G966:G967"/>
-    <mergeCell ref="C825:G825"/>
-    <mergeCell ref="C975:G975"/>
-    <mergeCell ref="C918:C919"/>
-    <mergeCell ref="D918:D919"/>
-    <mergeCell ref="E918:E919"/>
-    <mergeCell ref="F918:F919"/>
-    <mergeCell ref="G918:G919"/>
-    <mergeCell ref="C953:G953"/>
-    <mergeCell ref="C955:C956"/>
-    <mergeCell ref="D955:D956"/>
-    <mergeCell ref="E955:E956"/>
-    <mergeCell ref="F955:F956"/>
-    <mergeCell ref="G955:G956"/>
-    <mergeCell ref="C944:C945"/>
-    <mergeCell ref="D944:D945"/>
-    <mergeCell ref="E944:E945"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C126:G126"/>
     <mergeCell ref="L918:L919"/>
     <mergeCell ref="L944:L945"/>
     <mergeCell ref="L955:L956"/>
@@ -27760,9 +28939,41 @@
     <mergeCell ref="C642:G642"/>
     <mergeCell ref="C705:G705"/>
     <mergeCell ref="C754:G754"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C126:G126"/>
+    <mergeCell ref="C975:G975"/>
+    <mergeCell ref="C918:C919"/>
+    <mergeCell ref="D918:D919"/>
+    <mergeCell ref="E918:E919"/>
+    <mergeCell ref="F918:F919"/>
+    <mergeCell ref="G918:G919"/>
+    <mergeCell ref="C953:G953"/>
+    <mergeCell ref="C955:C956"/>
+    <mergeCell ref="D955:D956"/>
+    <mergeCell ref="E955:E956"/>
+    <mergeCell ref="F955:F956"/>
+    <mergeCell ref="G955:G956"/>
+    <mergeCell ref="C944:C945"/>
+    <mergeCell ref="D944:D945"/>
+    <mergeCell ref="E944:E945"/>
+    <mergeCell ref="C964:G964"/>
+    <mergeCell ref="C966:C967"/>
+    <mergeCell ref="D966:D967"/>
+    <mergeCell ref="E966:E967"/>
+    <mergeCell ref="F966:F967"/>
+    <mergeCell ref="G966:G967"/>
+    <mergeCell ref="H192:K192"/>
+    <mergeCell ref="H166:K166"/>
+    <mergeCell ref="F944:F945"/>
+    <mergeCell ref="C929:G929"/>
+    <mergeCell ref="G944:G945"/>
+    <mergeCell ref="C825:G825"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.49" bottom="0.31" header="0.35" footer="0.3"/>
-  <pageSetup paperSize="9" scale="56" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="55" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="889" max="7" man="1"/>
     <brk id="928" max="7" man="1"/>
@@ -27928,13 +29139,13 @@
       <c r="B11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="90" t="s">
+      <c r="C11" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="90"/>
-      <c r="E11" s="90"/>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
     </row>
     <row r="12" spans="1:7" s="12" customFormat="1" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="37"/>
@@ -28342,13 +29553,13 @@
       <c r="B42" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C42" s="90" t="s">
+      <c r="C42" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D42" s="90"/>
-      <c r="E42" s="90"/>
-      <c r="F42" s="90"/>
-      <c r="G42" s="90"/>
+      <c r="D42" s="98"/>
+      <c r="E42" s="98"/>
+      <c r="F42" s="98"/>
+      <c r="G42" s="98"/>
     </row>
     <row r="43" spans="1:8" s="12" customFormat="1" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
@@ -28874,13 +30085,13 @@
       <c r="B84" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C84" s="90" t="s">
+      <c r="C84" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D84" s="90"/>
-      <c r="E84" s="90"/>
-      <c r="F84" s="90"/>
-      <c r="G84" s="90"/>
+      <c r="D84" s="98"/>
+      <c r="E84" s="98"/>
+      <c r="F84" s="98"/>
+      <c r="G84" s="98"/>
     </row>
     <row r="85" spans="1:7" s="24" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
@@ -29452,13 +30663,13 @@
       <c r="B133" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C133" s="90" t="s">
+      <c r="C133" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D133" s="90"/>
-      <c r="E133" s="90"/>
-      <c r="F133" s="90"/>
-      <c r="G133" s="90"/>
+      <c r="D133" s="98"/>
+      <c r="E133" s="98"/>
+      <c r="F133" s="98"/>
+      <c r="G133" s="98"/>
     </row>
     <row r="134" spans="1:7" s="24" customFormat="1" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
@@ -29856,13 +31067,13 @@
       <c r="B166" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C166" s="90" t="s">
+      <c r="C166" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D166" s="90"/>
-      <c r="E166" s="90"/>
-      <c r="F166" s="90"/>
-      <c r="G166" s="90"/>
+      <c r="D166" s="98"/>
+      <c r="E166" s="98"/>
+      <c r="F166" s="98"/>
+      <c r="G166" s="98"/>
     </row>
     <row r="167" spans="1:7" customFormat="1" ht="103.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
@@ -30482,13 +31693,13 @@
       <c r="B218" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C218" s="90" t="s">
+      <c r="C218" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D218" s="90"/>
-      <c r="E218" s="90"/>
-      <c r="F218" s="90"/>
-      <c r="G218" s="90"/>
+      <c r="D218" s="98"/>
+      <c r="E218" s="98"/>
+      <c r="F218" s="98"/>
+      <c r="G218" s="98"/>
     </row>
     <row r="219" spans="1:7" s="24" customFormat="1" ht="106.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
@@ -30826,13 +32037,13 @@
       <c r="B246" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C246" s="90" t="s">
+      <c r="C246" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D246" s="90"/>
-      <c r="E246" s="90"/>
-      <c r="F246" s="90"/>
-      <c r="G246" s="90"/>
+      <c r="D246" s="98"/>
+      <c r="E246" s="98"/>
+      <c r="F246" s="98"/>
+      <c r="G246" s="98"/>
     </row>
     <row r="247" spans="1:7" s="24" customFormat="1" ht="89.4" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
@@ -31211,13 +32422,13 @@
       <c r="B277" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C277" s="90" t="s">
+      <c r="C277" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D277" s="90"/>
-      <c r="E277" s="90"/>
-      <c r="F277" s="90"/>
-      <c r="G277" s="90"/>
+      <c r="D277" s="98"/>
+      <c r="E277" s="98"/>
+      <c r="F277" s="98"/>
+      <c r="G277" s="98"/>
     </row>
     <row r="278" spans="1:7" s="24" customFormat="1" ht="93.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
@@ -32511,13 +33722,13 @@
       <c r="B377" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C377" s="90" t="s">
+      <c r="C377" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D377" s="90"/>
-      <c r="E377" s="90"/>
-      <c r="F377" s="90"/>
-      <c r="G377" s="90"/>
+      <c r="D377" s="98"/>
+      <c r="E377" s="98"/>
+      <c r="F377" s="98"/>
+      <c r="G377" s="98"/>
     </row>
     <row r="378" spans="1:7" s="24" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
@@ -33280,13 +34491,13 @@
       <c r="B437" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C437" s="90" t="s">
+      <c r="C437" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D437" s="90"/>
-      <c r="E437" s="90"/>
-      <c r="F437" s="90"/>
-      <c r="G437" s="90"/>
+      <c r="D437" s="98"/>
+      <c r="E437" s="98"/>
+      <c r="F437" s="98"/>
+      <c r="G437" s="98"/>
     </row>
     <row r="438" spans="1:7" s="24" customFormat="1" ht="117.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
@@ -34027,13 +35238,13 @@
       <c r="B495" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C495" s="90" t="s">
+      <c r="C495" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D495" s="90"/>
-      <c r="E495" s="90"/>
-      <c r="F495" s="90"/>
-      <c r="G495" s="90"/>
+      <c r="D495" s="98"/>
+      <c r="E495" s="98"/>
+      <c r="F495" s="98"/>
+      <c r="G495" s="98"/>
     </row>
     <row r="496" spans="1:7" s="24" customFormat="1" ht="103.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
@@ -35222,13 +36433,13 @@
       <c r="B587" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C587" s="90" t="s">
+      <c r="C587" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D587" s="90"/>
-      <c r="E587" s="90"/>
-      <c r="F587" s="90"/>
-      <c r="G587" s="90"/>
+      <c r="D587" s="98"/>
+      <c r="E587" s="98"/>
+      <c r="F587" s="98"/>
+      <c r="G587" s="98"/>
     </row>
     <row r="588" spans="1:7" s="24" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1"/>
@@ -36232,13 +37443,13 @@
       <c r="B673" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C673" s="90" t="s">
+      <c r="C673" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D673" s="90"/>
-      <c r="E673" s="90"/>
-      <c r="F673" s="90"/>
-      <c r="G673" s="90"/>
+      <c r="D673" s="98"/>
+      <c r="E673" s="98"/>
+      <c r="F673" s="98"/>
+      <c r="G673" s="98"/>
     </row>
     <row r="674" spans="1:7" s="24" customFormat="1" ht="97.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="1"/>
@@ -37213,13 +38424,13 @@
       <c r="B751" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C751" s="90" t="s">
+      <c r="C751" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D751" s="90"/>
-      <c r="E751" s="90"/>
-      <c r="F751" s="90"/>
-      <c r="G751" s="90"/>
+      <c r="D751" s="98"/>
+      <c r="E751" s="98"/>
+      <c r="F751" s="98"/>
+      <c r="G751" s="98"/>
     </row>
     <row r="752" spans="1:7" s="24" customFormat="1" ht="89.4" x14ac:dyDescent="0.25">
       <c r="A752" s="1"/>
@@ -38056,13 +39267,13 @@
       <c r="B817" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C817" s="90" t="s">
+      <c r="C817" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D817" s="90"/>
-      <c r="E817" s="90"/>
-      <c r="F817" s="90"/>
-      <c r="G817" s="90"/>
+      <c r="D817" s="98"/>
+      <c r="E817" s="98"/>
+      <c r="F817" s="98"/>
+      <c r="G817" s="98"/>
     </row>
     <row r="818" spans="1:7" s="24" customFormat="1" ht="89.4" x14ac:dyDescent="0.25">
       <c r="A818" s="1"/>
@@ -38602,13 +39813,13 @@
       <c r="B862" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C862" s="90" t="s">
+      <c r="C862" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D862" s="90"/>
-      <c r="E862" s="90"/>
-      <c r="F862" s="90"/>
-      <c r="G862" s="90"/>
+      <c r="D862" s="98"/>
+      <c r="E862" s="98"/>
+      <c r="F862" s="98"/>
+      <c r="G862" s="98"/>
     </row>
     <row r="863" spans="1:7" s="24" customFormat="1" ht="89.4" x14ac:dyDescent="0.25">
       <c r="A863" s="1"/>
@@ -39941,13 +41152,13 @@
       <c r="B970" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C970" s="90" t="s">
+      <c r="C970" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D970" s="90"/>
-      <c r="E970" s="90"/>
-      <c r="F970" s="90"/>
-      <c r="G970" s="90"/>
+      <c r="D970" s="98"/>
+      <c r="E970" s="98"/>
+      <c r="F970" s="98"/>
+      <c r="G970" s="98"/>
     </row>
     <row r="971" spans="1:7" customFormat="1" ht="89.4" x14ac:dyDescent="0.25">
       <c r="A971" s="1"/>
@@ -40793,13 +42004,13 @@
       <c r="B1040" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1040" s="90" t="s">
+      <c r="C1040" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D1040" s="90"/>
-      <c r="E1040" s="90"/>
-      <c r="F1040" s="90"/>
-      <c r="G1040" s="90"/>
+      <c r="D1040" s="98"/>
+      <c r="E1040" s="98"/>
+      <c r="F1040" s="98"/>
+      <c r="G1040" s="98"/>
     </row>
     <row r="1041" spans="1:7" s="24" customFormat="1" ht="117.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1041" s="1"/>
@@ -41340,20 +42551,20 @@
       <c r="B1086" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="C1086" s="91"/>
-      <c r="D1086" s="92"/>
-      <c r="E1086" s="93"/>
-      <c r="F1086" s="89"/>
-      <c r="G1086" s="94"/>
+      <c r="C1086" s="100"/>
+      <c r="D1086" s="101"/>
+      <c r="E1086" s="102"/>
+      <c r="F1086" s="97"/>
+      <c r="G1086" s="99"/>
     </row>
     <row r="1087" spans="1:7" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1087" s="59"/>
       <c r="B1087" s="66"/>
-      <c r="C1087" s="91"/>
-      <c r="D1087" s="92"/>
-      <c r="E1087" s="93"/>
-      <c r="F1087" s="89"/>
-      <c r="G1087" s="94"/>
+      <c r="C1087" s="100"/>
+      <c r="D1087" s="101"/>
+      <c r="E1087" s="102"/>
+      <c r="F1087" s="97"/>
+      <c r="G1087" s="99"/>
     </row>
     <row r="1088" spans="1:7" s="33" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1088" s="59"/>
@@ -41581,13 +42792,13 @@
       <c r="B1105" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1105" s="90" t="s">
+      <c r="C1105" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D1105" s="90"/>
-      <c r="E1105" s="90"/>
-      <c r="F1105" s="90"/>
-      <c r="G1105" s="90"/>
+      <c r="D1105" s="98"/>
+      <c r="E1105" s="98"/>
+      <c r="F1105" s="98"/>
+      <c r="G1105" s="98"/>
     </row>
     <row r="1106" spans="1:7" s="33" customFormat="1" ht="89.4" x14ac:dyDescent="0.25">
       <c r="A1106" s="1"/>
@@ -41705,20 +42916,20 @@
       <c r="B1115" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="C1115" s="91"/>
-      <c r="D1115" s="92"/>
-      <c r="E1115" s="93"/>
-      <c r="F1115" s="89"/>
-      <c r="G1115" s="94"/>
+      <c r="C1115" s="100"/>
+      <c r="D1115" s="101"/>
+      <c r="E1115" s="102"/>
+      <c r="F1115" s="97"/>
+      <c r="G1115" s="99"/>
     </row>
     <row r="1116" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1116" s="59"/>
       <c r="B1116" s="66"/>
-      <c r="C1116" s="91"/>
-      <c r="D1116" s="92"/>
-      <c r="E1116" s="93"/>
-      <c r="F1116" s="89"/>
-      <c r="G1116" s="94"/>
+      <c r="C1116" s="100"/>
+      <c r="D1116" s="101"/>
+      <c r="E1116" s="102"/>
+      <c r="F1116" s="97"/>
+      <c r="G1116" s="99"/>
     </row>
     <row r="1117" spans="1:7" s="24" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1117" s="59"/>
@@ -41853,13 +43064,13 @@
       <c r="B1126" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1126" s="90" t="s">
+      <c r="C1126" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="D1126" s="90"/>
-      <c r="E1126" s="90"/>
-      <c r="F1126" s="90"/>
-      <c r="G1126" s="90"/>
+      <c r="D1126" s="98"/>
+      <c r="E1126" s="98"/>
+      <c r="F1126" s="98"/>
+      <c r="G1126" s="98"/>
     </row>
     <row r="1127" spans="1:7" s="24" customFormat="1" ht="89.4" x14ac:dyDescent="0.25">
       <c r="A1127" s="1"/>
@@ -43111,12 +44322,18 @@
   </sheetData>
   <autoFilter ref="A11:BK1231"/>
   <mergeCells count="30">
-    <mergeCell ref="C218:G218"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C133:G133"/>
-    <mergeCell ref="C166:G166"/>
+    <mergeCell ref="C1126:G1126"/>
+    <mergeCell ref="C1086:C1087"/>
+    <mergeCell ref="D1086:D1087"/>
+    <mergeCell ref="E1086:E1087"/>
+    <mergeCell ref="F1086:F1087"/>
+    <mergeCell ref="G1086:G1087"/>
+    <mergeCell ref="C1105:G1105"/>
+    <mergeCell ref="C1115:C1116"/>
+    <mergeCell ref="D1115:D1116"/>
+    <mergeCell ref="E1115:E1116"/>
+    <mergeCell ref="F1115:F1116"/>
+    <mergeCell ref="G1115:G1116"/>
     <mergeCell ref="C1040:G1040"/>
     <mergeCell ref="C246:G246"/>
     <mergeCell ref="C277:G277"/>
@@ -43129,18 +44346,12 @@
     <mergeCell ref="C817:G817"/>
     <mergeCell ref="C862:G862"/>
     <mergeCell ref="C970:G970"/>
-    <mergeCell ref="C1126:G1126"/>
-    <mergeCell ref="C1086:C1087"/>
-    <mergeCell ref="D1086:D1087"/>
-    <mergeCell ref="E1086:E1087"/>
-    <mergeCell ref="F1086:F1087"/>
-    <mergeCell ref="G1086:G1087"/>
-    <mergeCell ref="C1105:G1105"/>
-    <mergeCell ref="C1115:C1116"/>
-    <mergeCell ref="D1115:D1116"/>
-    <mergeCell ref="E1115:E1116"/>
-    <mergeCell ref="F1115:F1116"/>
-    <mergeCell ref="G1115:G1116"/>
+    <mergeCell ref="C218:G218"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C133:G133"/>
+    <mergeCell ref="C166:G166"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.49" bottom="0.31" header="0.35" footer="0.3"/>
   <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="portrait" r:id="rId1"/>
